--- a/research/traditional_assets/database/data/mauritius/mauritius_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_beverage_soft.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="muse_qbl_i0000" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,73 +590,70 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.0286060606060606</v>
+        <v>0.04798099762470309</v>
       </c>
       <c r="H2">
-        <v>0.0286060606060606</v>
+        <v>0.04798099762470309</v>
       </c>
       <c r="I2">
-        <v>-0.05</v>
+        <v>0.05558194774346793</v>
       </c>
       <c r="J2">
-        <v>-0.05</v>
+        <v>0.04361256790762211</v>
       </c>
       <c r="K2">
-        <v>-1.06</v>
+        <v>1.59</v>
       </c>
       <c r="L2">
-        <v>-0.03212121212121212</v>
+        <v>0.03776722090261283</v>
       </c>
       <c r="M2">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.07064220183486239</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.7264150943396226</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.07064220183486239</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.7264150943396226</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>0.512</v>
+        <v>0.668</v>
       </c>
       <c r="V2">
-        <v>0.04697247706422018</v>
+        <v>0.07136752136752138</v>
       </c>
       <c r="W2">
-        <v>-0.08346456692913387</v>
+        <v>0.2020330368487929</v>
       </c>
       <c r="X2">
-        <v>0.06310106573164015</v>
+        <v>0.1160977296833985</v>
       </c>
       <c r="Y2">
-        <v>-0.146565632660774</v>
+        <v>0.08593530716539441</v>
       </c>
       <c r="Z2">
-        <v>2.598425196850394</v>
+        <v>5.721663495515085</v>
       </c>
       <c r="AA2">
-        <v>-0.1299212598425197</v>
+        <v>0.2495364377427142</v>
       </c>
       <c r="AB2">
-        <v>0.06310106573164015</v>
+        <v>0.1160977296833985</v>
       </c>
       <c r="AC2">
-        <v>-0.1930223255741598</v>
+        <v>0.1334387080593157</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -666,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.512</v>
+        <v>-0.668</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -675,22 +674,28 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.04928763958413554</v>
+        <v>-0.07685227795674184</v>
       </c>
       <c r="AK2">
-        <v>-0.06958412612122859</v>
+        <v>-0.05645706558485463</v>
       </c>
       <c r="AL2">
-        <v>0.387</v>
+        <v>0.533</v>
       </c>
       <c r="AM2">
-        <v>0.353</v>
+        <v>0.533</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>-4.263565891472868</v>
+        <v>4.390243902439024</v>
+      </c>
+      <c r="AP2">
+        <v>-0.1712820512820513</v>
       </c>
       <c r="AQ2">
-        <v>-4.674220963172805</v>
+        <v>4.390243902439024</v>
       </c>
     </row>
     <row r="3">
@@ -710,109 +715,8824 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.0286060606060606</v>
+        <v>0.04798099762470309</v>
       </c>
       <c r="H3">
-        <v>0.0286060606060606</v>
+        <v>0.04798099762470309</v>
       </c>
       <c r="I3">
-        <v>-0.05</v>
+        <v>0.05558194774346793</v>
       </c>
       <c r="J3">
-        <v>-0.05</v>
+        <v>0.04361256790762211</v>
       </c>
       <c r="K3">
-        <v>-1.06</v>
+        <v>1.59</v>
       </c>
       <c r="L3">
-        <v>-0.03212121212121212</v>
+        <v>0.03776722090261283</v>
       </c>
       <c r="M3">
+        <v>-0</v>
+      </c>
+      <c r="N3">
+        <v>-0</v>
+      </c>
+      <c r="O3">
+        <v>-0</v>
+      </c>
+      <c r="P3">
+        <v>-0</v>
+      </c>
+      <c r="Q3">
+        <v>-0</v>
+      </c>
+      <c r="R3">
+        <v>-0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0.668</v>
+      </c>
+      <c r="V3">
+        <v>0.07136752136752138</v>
+      </c>
+      <c r="W3">
+        <v>0.2020330368487929</v>
+      </c>
+      <c r="X3">
+        <v>0.1160977296833985</v>
+      </c>
+      <c r="Y3">
+        <v>0.08593530716539441</v>
+      </c>
+      <c r="Z3">
+        <v>5.721663495515085</v>
+      </c>
+      <c r="AA3">
+        <v>0.2495364377427142</v>
+      </c>
+      <c r="AB3">
+        <v>0.1160977296833985</v>
+      </c>
+      <c r="AC3">
+        <v>0.1334387080593157</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>-0.668</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.07685227795674184</v>
+      </c>
+      <c r="AK3">
+        <v>-0.05645706558485463</v>
+      </c>
+      <c r="AL3">
+        <v>0.533</v>
+      </c>
+      <c r="AM3">
+        <v>0.533</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>4.390243902439024</v>
+      </c>
+      <c r="AP3">
+        <v>-0.1712820512820513</v>
+      </c>
+      <c r="AQ3">
+        <v>4.390243902439024</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Quality Beverages Limited (MUSE:QBL.I0000)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MUSE:QBL.I0000</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Beverage (Soft)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mauritius</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0.51</v>
+      </c>
+      <c r="G2">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H2">
+        <v>5.2128815061317</v>
+      </c>
+      <c r="I2">
+        <v>8.692</v>
+      </c>
+      <c r="J2">
+        <v>9.3184815061317</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>4.7736</v>
+      </c>
+      <c r="M2">
+        <v>0.116097729683398</v>
+      </c>
+      <c r="N2">
+        <v>0.110901003362618</v>
+      </c>
+      <c r="O2">
+        <v>0.0630631766055046</v>
+      </c>
+      <c r="P2">
+        <v>0.040205</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.116097729683398</v>
+      </c>
+      <c r="T2">
+        <v>0.184482557882895</v>
+      </c>
+      <c r="U2">
+        <v>0.796252711070395</v>
+      </c>
+      <c r="V2">
+        <v>1.50069260953777</v>
+      </c>
+      <c r="W2">
+        <v>10.36355345520872</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="AB2">
+        <v>0.09707688100614176</v>
+      </c>
+      <c r="AC2">
+        <v>0.07419197247706423</v>
+      </c>
+      <c r="AD2">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>3.9</v>
+      </c>
+      <c r="AH2">
+        <v>1.56</v>
+      </c>
+      <c r="AI2">
+        <v>4.98</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0.533</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0.668</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1160977296833985</v>
+      </c>
+      <c r="C2">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="D2">
+        <v>8.692</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.668</v>
+      </c>
+      <c r="H2">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>3.9</v>
+      </c>
+      <c r="K2">
+        <v>1.56</v>
+      </c>
+      <c r="L2">
+        <v>2.34</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2.34</v>
+      </c>
+      <c r="O2">
+        <v>0.3510000000000003</v>
+      </c>
+      <c r="P2">
+        <v>1.988999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>3.548999999999999</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1160977296833985</v>
+      </c>
+      <c r="T2">
+        <v>0.7962527110703947</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W2">
+        <v>0.038845</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1159822330888734</v>
+      </c>
+      <c r="C3">
+        <v>9.279406832783089</v>
+      </c>
+      <c r="D3">
+        <v>8.70500683278309</v>
+      </c>
+      <c r="E3">
+        <v>0.0936</v>
+      </c>
+      <c r="F3">
+        <v>0.0936</v>
+      </c>
+      <c r="G3">
+        <v>0.668</v>
+      </c>
+      <c r="H3">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>3.9</v>
+      </c>
+      <c r="K3">
+        <v>1.56</v>
+      </c>
+      <c r="L3">
+        <v>2.34</v>
+      </c>
+      <c r="M3">
+        <v>0.004277520000000001</v>
+      </c>
+      <c r="N3">
+        <v>2.33572248</v>
+      </c>
+      <c r="O3">
+        <v>0.3503583720000003</v>
+      </c>
+      <c r="P3">
+        <v>1.985364108</v>
+      </c>
+      <c r="Q3">
+        <v>3.545364107999999</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1167613970594681</v>
+      </c>
+      <c r="T3">
+        <v>0.8030892242462516</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W3">
+        <v>0.038845</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>547.0459518599561</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1158667364943483</v>
+      </c>
+      <c r="C4">
+        <v>9.198852651124932</v>
+      </c>
+      <c r="D4">
+        <v>8.718052651124934</v>
+      </c>
+      <c r="E4">
+        <v>0.1872</v>
+      </c>
+      <c r="F4">
+        <v>0.1872</v>
+      </c>
+      <c r="G4">
+        <v>0.668</v>
+      </c>
+      <c r="H4">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>3.9</v>
+      </c>
+      <c r="K4">
+        <v>1.56</v>
+      </c>
+      <c r="L4">
+        <v>2.34</v>
+      </c>
+      <c r="M4">
+        <v>0.008555040000000002</v>
+      </c>
+      <c r="N4">
+        <v>2.33144496</v>
+      </c>
+      <c r="O4">
+        <v>0.3497167440000003</v>
+      </c>
+      <c r="P4">
+        <v>1.981728216</v>
+      </c>
+      <c r="Q4">
+        <v>3.541728216</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1174386086677023</v>
+      </c>
+      <c r="T4">
+        <v>0.810065258099167</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W4">
+        <v>0.038845</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>273.522975929978</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1157512398998232</v>
+      </c>
+      <c r="C5">
+        <v>9.118337630566542</v>
+      </c>
+      <c r="D5">
+        <v>8.731137630566542</v>
+      </c>
+      <c r="E5">
+        <v>0.2808</v>
+      </c>
+      <c r="F5">
+        <v>0.2808</v>
+      </c>
+      <c r="G5">
+        <v>0.668</v>
+      </c>
+      <c r="H5">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>3.9</v>
+      </c>
+      <c r="K5">
+        <v>1.56</v>
+      </c>
+      <c r="L5">
+        <v>2.34</v>
+      </c>
+      <c r="M5">
+        <v>0.01283256</v>
+      </c>
+      <c r="N5">
+        <v>2.32716744</v>
+      </c>
+      <c r="O5">
+        <v>0.3490751160000003</v>
+      </c>
+      <c r="P5">
+        <v>1.978092323999999</v>
+      </c>
+      <c r="Q5">
+        <v>3.538092324</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1181297834018796</v>
+      </c>
+      <c r="T5">
+        <v>0.8171851277016267</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W5">
+        <v>0.038845</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>182.3486506199854</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1156357433052981</v>
+      </c>
+      <c r="C6">
+        <v>9.037861947704382</v>
+      </c>
+      <c r="D6">
+        <v>8.744261947704382</v>
+      </c>
+      <c r="E6">
+        <v>0.3744</v>
+      </c>
+      <c r="F6">
+        <v>0.3744</v>
+      </c>
+      <c r="G6">
+        <v>0.668</v>
+      </c>
+      <c r="H6">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>3.9</v>
+      </c>
+      <c r="K6">
+        <v>1.56</v>
+      </c>
+      <c r="L6">
+        <v>2.34</v>
+      </c>
+      <c r="M6">
+        <v>0.01711008</v>
+      </c>
+      <c r="N6">
+        <v>2.32288992</v>
+      </c>
+      <c r="O6">
+        <v>0.3484334880000003</v>
+      </c>
+      <c r="P6">
+        <v>1.974456431999999</v>
+      </c>
+      <c r="Q6">
+        <v>3.534456431999999</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1188353576096855</v>
+      </c>
+      <c r="T6">
+        <v>0.8244533279208045</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W6">
+        <v>0.038845</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>136.761487964989</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.115520246710773</v>
+      </c>
+      <c r="C7">
+        <v>8.95742578019833</v>
+      </c>
+      <c r="D7">
+        <v>8.75742578019833</v>
+      </c>
+      <c r="E7">
+        <v>0.468</v>
+      </c>
+      <c r="F7">
+        <v>0.468</v>
+      </c>
+      <c r="G7">
+        <v>0.668</v>
+      </c>
+      <c r="H7">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3.9</v>
+      </c>
+      <c r="K7">
+        <v>1.56</v>
+      </c>
+      <c r="L7">
+        <v>2.34</v>
+      </c>
+      <c r="M7">
+        <v>0.0213876</v>
+      </c>
+      <c r="N7">
+        <v>2.3186124</v>
+      </c>
+      <c r="O7">
+        <v>0.3477918600000003</v>
+      </c>
+      <c r="P7">
+        <v>1.970820539999999</v>
+      </c>
+      <c r="Q7">
+        <v>3.53082054</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.11955578601134</v>
+      </c>
+      <c r="T7">
+        <v>0.8318745428814387</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W7">
+        <v>0.038845</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>109.4091903719912</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1154047501162479</v>
+      </c>
+      <c r="C8">
+        <v>8.877029306779702</v>
+      </c>
+      <c r="D8">
+        <v>8.770629306779703</v>
+      </c>
+      <c r="E8">
+        <v>0.5616</v>
+      </c>
+      <c r="F8">
+        <v>0.5616</v>
+      </c>
+      <c r="G8">
+        <v>0.668</v>
+      </c>
+      <c r="H8">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>3.9</v>
+      </c>
+      <c r="K8">
+        <v>1.56</v>
+      </c>
+      <c r="L8">
+        <v>2.34</v>
+      </c>
+      <c r="M8">
+        <v>0.02566512</v>
+      </c>
+      <c r="N8">
+        <v>2.31433488</v>
+      </c>
+      <c r="O8">
+        <v>0.3471502320000003</v>
+      </c>
+      <c r="P8">
+        <v>1.967184647999999</v>
+      </c>
+      <c r="Q8">
+        <v>3.527184648</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1202915426768595</v>
+      </c>
+      <c r="T8">
+        <v>0.8394536560327246</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W8">
+        <v>0.038845</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>91.17432530999268</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1152892535217228</v>
+      </c>
+      <c r="C9">
+        <v>8.796672707259319</v>
+      </c>
+      <c r="D9">
+        <v>8.78387270725932</v>
+      </c>
+      <c r="E9">
+        <v>0.6552</v>
+      </c>
+      <c r="F9">
+        <v>0.6552</v>
+      </c>
+      <c r="G9">
+        <v>0.668</v>
+      </c>
+      <c r="H9">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>3.9</v>
+      </c>
+      <c r="K9">
+        <v>1.56</v>
+      </c>
+      <c r="L9">
+        <v>2.34</v>
+      </c>
+      <c r="M9">
+        <v>0.02994264</v>
+      </c>
+      <c r="N9">
+        <v>2.31005736</v>
+      </c>
+      <c r="O9">
+        <v>0.3465086040000003</v>
+      </c>
+      <c r="P9">
+        <v>1.963548756</v>
+      </c>
+      <c r="Q9">
+        <v>3.523548756</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1210431220663686</v>
+      </c>
+      <c r="T9">
+        <v>0.8471957608646834</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W9">
+        <v>0.038845</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>78.14942169427945</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1151737569271977</v>
+      </c>
+      <c r="C10">
+        <v>8.716356162535684</v>
+      </c>
+      <c r="D10">
+        <v>8.797156162535684</v>
+      </c>
+      <c r="E10">
+        <v>0.7488</v>
+      </c>
+      <c r="F10">
+        <v>0.7488</v>
+      </c>
+      <c r="G10">
+        <v>0.668</v>
+      </c>
+      <c r="H10">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>3.9</v>
+      </c>
+      <c r="K10">
+        <v>1.56</v>
+      </c>
+      <c r="L10">
+        <v>2.34</v>
+      </c>
+      <c r="M10">
+        <v>0.03422016000000001</v>
+      </c>
+      <c r="N10">
+        <v>2.30577984</v>
+      </c>
+      <c r="O10">
+        <v>0.3458669760000003</v>
+      </c>
+      <c r="P10">
+        <v>1.959912864</v>
+      </c>
+      <c r="Q10">
+        <v>3.519912864</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1218110401382584</v>
+      </c>
+      <c r="T10">
+        <v>0.8551061723234239</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W10">
+        <v>0.038845</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>68.38074398249452</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1150582603326726</v>
+      </c>
+      <c r="C11">
+        <v>8.636079854603217</v>
+      </c>
+      <c r="D11">
+        <v>8.810479854603217</v>
+      </c>
+      <c r="E11">
+        <v>0.8423999999999999</v>
+      </c>
+      <c r="F11">
+        <v>0.8423999999999999</v>
+      </c>
+      <c r="G11">
+        <v>0.668</v>
+      </c>
+      <c r="H11">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>3.9</v>
+      </c>
+      <c r="K11">
+        <v>1.56</v>
+      </c>
+      <c r="L11">
+        <v>2.34</v>
+      </c>
+      <c r="M11">
+        <v>0.03849768</v>
+      </c>
+      <c r="N11">
+        <v>2.30150232</v>
+      </c>
+      <c r="O11">
+        <v>0.3452253480000003</v>
+      </c>
+      <c r="P11">
+        <v>1.956276972</v>
+      </c>
+      <c r="Q11">
+        <v>3.516276972</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1225958355304095</v>
+      </c>
+      <c r="T11">
+        <v>0.8631904389790598</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W11">
+        <v>0.038845</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>60.78288353999514</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1149427637381475</v>
+      </c>
+      <c r="C12">
+        <v>8.555843966560564</v>
+      </c>
+      <c r="D12">
+        <v>8.823843966560565</v>
+      </c>
+      <c r="E12">
+        <v>0.9359999999999999</v>
+      </c>
+      <c r="F12">
+        <v>0.9359999999999999</v>
+      </c>
+      <c r="G12">
+        <v>0.668</v>
+      </c>
+      <c r="H12">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>3.9</v>
+      </c>
+      <c r="K12">
+        <v>1.56</v>
+      </c>
+      <c r="L12">
+        <v>2.34</v>
+      </c>
+      <c r="M12">
+        <v>0.0427752</v>
+      </c>
+      <c r="N12">
+        <v>2.2972248</v>
+      </c>
+      <c r="O12">
+        <v>0.3445837200000003</v>
+      </c>
+      <c r="P12">
+        <v>1.95264108</v>
+      </c>
+      <c r="Q12">
+        <v>3.51264108</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1233980708201639</v>
+      </c>
+      <c r="T12">
+        <v>0.871454356004821</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W12">
+        <v>0.038845</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>54.70459518599562</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1148272671436224</v>
+      </c>
+      <c r="C13">
+        <v>8.475648682618994</v>
+      </c>
+      <c r="D13">
+        <v>8.837248682618995</v>
+      </c>
+      <c r="E13">
+        <v>1.0296</v>
+      </c>
+      <c r="F13">
+        <v>1.0296</v>
+      </c>
+      <c r="G13">
+        <v>0.668</v>
+      </c>
+      <c r="H13">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>3.9</v>
+      </c>
+      <c r="K13">
+        <v>1.56</v>
+      </c>
+      <c r="L13">
+        <v>2.34</v>
+      </c>
+      <c r="M13">
+        <v>0.04705272</v>
+      </c>
+      <c r="N13">
+        <v>2.29294728</v>
+      </c>
+      <c r="O13">
+        <v>0.3439420920000003</v>
+      </c>
+      <c r="P13">
+        <v>1.949005188</v>
+      </c>
+      <c r="Q13">
+        <v>3.509005188</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1242183338692387</v>
+      </c>
+      <c r="T13">
+        <v>0.8799039790311609</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W13">
+        <v>0.038845</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>49.73145016908693</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1147117705490973</v>
+      </c>
+      <c r="C14">
+        <v>8.395494188110845</v>
+      </c>
+      <c r="D14">
+        <v>8.850694188110847</v>
+      </c>
+      <c r="E14">
+        <v>1.1232</v>
+      </c>
+      <c r="F14">
+        <v>1.1232</v>
+      </c>
+      <c r="G14">
+        <v>0.668</v>
+      </c>
+      <c r="H14">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>3.9</v>
+      </c>
+      <c r="K14">
+        <v>1.56</v>
+      </c>
+      <c r="L14">
+        <v>2.34</v>
+      </c>
+      <c r="M14">
+        <v>0.05133024000000001</v>
+      </c>
+      <c r="N14">
+        <v>2.28866976</v>
+      </c>
+      <c r="O14">
+        <v>0.3433004640000003</v>
+      </c>
+      <c r="P14">
+        <v>1.945369296</v>
+      </c>
+      <c r="Q14">
+        <v>3.505369296</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1250572392603378</v>
+      </c>
+      <c r="T14">
+        <v>0.8885456389444633</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W14">
+        <v>0.038845</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>45.58716265499635</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1145962739545722</v>
+      </c>
+      <c r="C15">
+        <v>8.315380669498079</v>
+      </c>
+      <c r="D15">
+        <v>8.864180669498079</v>
+      </c>
+      <c r="E15">
+        <v>1.2168</v>
+      </c>
+      <c r="F15">
+        <v>1.2168</v>
+      </c>
+      <c r="G15">
+        <v>0.668</v>
+      </c>
+      <c r="H15">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>3.9</v>
+      </c>
+      <c r="K15">
+        <v>1.56</v>
+      </c>
+      <c r="L15">
+        <v>2.34</v>
+      </c>
+      <c r="M15">
+        <v>0.05560776</v>
+      </c>
+      <c r="N15">
+        <v>2.28439224</v>
+      </c>
+      <c r="O15">
+        <v>0.3426588360000003</v>
+      </c>
+      <c r="P15">
+        <v>1.941733404</v>
+      </c>
+      <c r="Q15">
+        <v>3.501733403999999</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1259154298328416</v>
+      </c>
+      <c r="T15">
+        <v>0.8973859577063471</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W15">
+        <v>0.038845</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>42.08045783538125</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1144807773600471</v>
+      </c>
+      <c r="C16">
+        <v>8.235308314380895</v>
+      </c>
+      <c r="D16">
+        <v>8.877708314380895</v>
+      </c>
+      <c r="E16">
+        <v>1.3104</v>
+      </c>
+      <c r="F16">
+        <v>1.3104</v>
+      </c>
+      <c r="G16">
+        <v>0.668</v>
+      </c>
+      <c r="H16">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>3.9</v>
+      </c>
+      <c r="K16">
+        <v>1.56</v>
+      </c>
+      <c r="L16">
+        <v>2.34</v>
+      </c>
+      <c r="M16">
+        <v>0.05988528000000001</v>
+      </c>
+      <c r="N16">
+        <v>2.28011472</v>
+      </c>
+      <c r="O16">
+        <v>0.3420172080000003</v>
+      </c>
+      <c r="P16">
+        <v>1.938097511999999</v>
+      </c>
+      <c r="Q16">
+        <v>3.498097511999999</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1267935783256362</v>
+      </c>
+      <c r="T16">
+        <v>0.906431865276647</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W16">
+        <v>0.038845</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>39.07471084713973</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.114365280765522</v>
+      </c>
+      <c r="C17">
+        <v>8.155277311506437</v>
+      </c>
+      <c r="D17">
+        <v>8.891277311506437</v>
+      </c>
+      <c r="E17">
+        <v>1.404</v>
+      </c>
+      <c r="F17">
+        <v>1.404</v>
+      </c>
+      <c r="G17">
+        <v>0.668</v>
+      </c>
+      <c r="H17">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>3.9</v>
+      </c>
+      <c r="K17">
+        <v>1.56</v>
+      </c>
+      <c r="L17">
+        <v>2.34</v>
+      </c>
+      <c r="M17">
+        <v>0.06416280000000001</v>
+      </c>
+      <c r="N17">
+        <v>2.2758372</v>
+      </c>
+      <c r="O17">
+        <v>0.3413755800000003</v>
+      </c>
+      <c r="P17">
+        <v>1.93446162</v>
+      </c>
+      <c r="Q17">
+        <v>3.49446162</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1276923891359082</v>
+      </c>
+      <c r="T17">
+        <v>0.9156906177309538</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W17">
+        <v>0.038845</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>36.46973012399707</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1142497841709969</v>
+      </c>
+      <c r="C18">
+        <v>8.075287850777563</v>
+      </c>
+      <c r="D18">
+        <v>8.904887850777564</v>
+      </c>
+      <c r="E18">
+        <v>1.4976</v>
+      </c>
+      <c r="F18">
+        <v>1.4976</v>
+      </c>
+      <c r="G18">
+        <v>0.668</v>
+      </c>
+      <c r="H18">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>3.9</v>
+      </c>
+      <c r="K18">
+        <v>1.56</v>
+      </c>
+      <c r="L18">
+        <v>2.34</v>
+      </c>
+      <c r="M18">
+        <v>0.06844032000000001</v>
+      </c>
+      <c r="N18">
+        <v>2.27155968</v>
+      </c>
+      <c r="O18">
+        <v>0.3407339520000003</v>
+      </c>
+      <c r="P18">
+        <v>1.930825727999999</v>
+      </c>
+      <c r="Q18">
+        <v>3.490825727999999</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1286126002035677</v>
+      </c>
+      <c r="T18">
+        <v>0.9251698166722681</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W18">
+        <v>0.038845</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>34.19037199124725</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1141342875764718</v>
+      </c>
+      <c r="C19">
+        <v>7.995340123261701</v>
+      </c>
+      <c r="D19">
+        <v>8.918540123261701</v>
+      </c>
+      <c r="E19">
+        <v>1.5912</v>
+      </c>
+      <c r="F19">
+        <v>1.5912</v>
+      </c>
+      <c r="G19">
+        <v>0.668</v>
+      </c>
+      <c r="H19">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>3.9</v>
+      </c>
+      <c r="K19">
+        <v>1.56</v>
+      </c>
+      <c r="L19">
+        <v>2.34</v>
+      </c>
+      <c r="M19">
+        <v>0.07271784000000001</v>
+      </c>
+      <c r="N19">
+        <v>2.26728216</v>
+      </c>
+      <c r="O19">
+        <v>0.3400923240000003</v>
+      </c>
+      <c r="P19">
+        <v>1.927189835999999</v>
+      </c>
+      <c r="Q19">
+        <v>3.487189836</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1295549850318938</v>
+      </c>
+      <c r="T19">
+        <v>0.9348774300459032</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W19">
+        <v>0.038845</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>32.17917363882095</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1140187909819467</v>
+      </c>
+      <c r="C20">
+        <v>7.915434321199814</v>
+      </c>
+      <c r="D20">
+        <v>8.932234321199815</v>
+      </c>
+      <c r="E20">
+        <v>1.6848</v>
+      </c>
+      <c r="F20">
+        <v>1.6848</v>
+      </c>
+      <c r="G20">
+        <v>0.668</v>
+      </c>
+      <c r="H20">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>3.9</v>
+      </c>
+      <c r="K20">
+        <v>1.56</v>
+      </c>
+      <c r="L20">
+        <v>2.34</v>
+      </c>
+      <c r="M20">
+        <v>0.07699536</v>
+      </c>
+      <c r="N20">
+        <v>2.26300464</v>
+      </c>
+      <c r="O20">
+        <v>0.3394506960000003</v>
+      </c>
+      <c r="P20">
+        <v>1.923553943999999</v>
+      </c>
+      <c r="Q20">
+        <v>3.483553944</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1305203548560326</v>
+      </c>
+      <c r="T20">
+        <v>0.9448218144774317</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W20">
+        <v>0.038845</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>30.39144176999757</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1139032943874216</v>
+      </c>
+      <c r="C21">
+        <v>7.835570638015387</v>
+      </c>
+      <c r="D21">
+        <v>8.945970638015387</v>
+      </c>
+      <c r="E21">
+        <v>1.7784</v>
+      </c>
+      <c r="F21">
+        <v>1.7784</v>
+      </c>
+      <c r="G21">
+        <v>0.668</v>
+      </c>
+      <c r="H21">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>3.9</v>
+      </c>
+      <c r="K21">
+        <v>1.56</v>
+      </c>
+      <c r="L21">
+        <v>2.34</v>
+      </c>
+      <c r="M21">
+        <v>0.08127288000000001</v>
+      </c>
+      <c r="N21">
+        <v>2.25872712</v>
+      </c>
+      <c r="O21">
+        <v>0.3388090680000003</v>
+      </c>
+      <c r="P21">
+        <v>1.919918051999999</v>
+      </c>
+      <c r="Q21">
+        <v>3.479918051999999</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1315095609721255</v>
+      </c>
+      <c r="T21">
+        <v>0.9550117392652944</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W21">
+        <v>0.038845</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>28.79189220315558</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1137877977928965</v>
+      </c>
+      <c r="C22">
+        <v>7.755749268323559</v>
+      </c>
+      <c r="D22">
+        <v>8.959749268323559</v>
+      </c>
+      <c r="E22">
+        <v>1.872</v>
+      </c>
+      <c r="F22">
+        <v>1.872</v>
+      </c>
+      <c r="G22">
+        <v>0.668</v>
+      </c>
+      <c r="H22">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>3.9</v>
+      </c>
+      <c r="K22">
+        <v>1.56</v>
+      </c>
+      <c r="L22">
+        <v>2.34</v>
+      </c>
+      <c r="M22">
+        <v>0.0855504</v>
+      </c>
+      <c r="N22">
+        <v>2.2544496</v>
+      </c>
+      <c r="O22">
+        <v>0.3381674400000003</v>
+      </c>
+      <c r="P22">
+        <v>1.91628216</v>
+      </c>
+      <c r="Q22">
+        <v>3.47628216</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1325234972411207</v>
+      </c>
+      <c r="T22">
+        <v>0.9654564121728536</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W22">
+        <v>0.038845</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>27.35229759299781</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1136723011983714</v>
+      </c>
+      <c r="C23">
+        <v>7.675970407940309</v>
+      </c>
+      <c r="D23">
+        <v>8.97357040794031</v>
+      </c>
+      <c r="E23">
+        <v>1.9656</v>
+      </c>
+      <c r="F23">
+        <v>1.9656</v>
+      </c>
+      <c r="G23">
+        <v>0.668</v>
+      </c>
+      <c r="H23">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>3.9</v>
+      </c>
+      <c r="K23">
+        <v>1.56</v>
+      </c>
+      <c r="L23">
+        <v>2.34</v>
+      </c>
+      <c r="M23">
+        <v>0.08982792000000001</v>
+      </c>
+      <c r="N23">
+        <v>2.25017208</v>
+      </c>
+      <c r="O23">
+        <v>0.3375258120000003</v>
+      </c>
+      <c r="P23">
+        <v>1.912646268</v>
+      </c>
+      <c r="Q23">
+        <v>3.472646268</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1335631027827486</v>
+      </c>
+      <c r="T23">
+        <v>0.9761655071793383</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W23">
+        <v>0.038845</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>26.04980723142648</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1135568046038463</v>
+      </c>
+      <c r="C24">
+        <v>7.596234253891734</v>
+      </c>
+      <c r="D24">
+        <v>8.987434253891735</v>
+      </c>
+      <c r="E24">
+        <v>2.0592</v>
+      </c>
+      <c r="F24">
+        <v>2.0592</v>
+      </c>
+      <c r="G24">
+        <v>0.668</v>
+      </c>
+      <c r="H24">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>3.9</v>
+      </c>
+      <c r="K24">
+        <v>1.56</v>
+      </c>
+      <c r="L24">
+        <v>2.34</v>
+      </c>
+      <c r="M24">
+        <v>0.09410544</v>
+      </c>
+      <c r="N24">
+        <v>2.24589456</v>
+      </c>
+      <c r="O24">
+        <v>0.3368841840000003</v>
+      </c>
+      <c r="P24">
+        <v>1.909010376</v>
+      </c>
+      <c r="Q24">
+        <v>3.469010376</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1346293648767261</v>
+      </c>
+      <c r="T24">
+        <v>0.9871491943654765</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W24">
+        <v>0.038845</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>24.86572508454347</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1134413080093212</v>
+      </c>
+      <c r="C25">
+        <v>7.516541004423396</v>
+      </c>
+      <c r="D25">
+        <v>9.001341004423397</v>
+      </c>
+      <c r="E25">
+        <v>2.1528</v>
+      </c>
+      <c r="F25">
+        <v>2.1528</v>
+      </c>
+      <c r="G25">
+        <v>0.668</v>
+      </c>
+      <c r="H25">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>3.9</v>
+      </c>
+      <c r="K25">
+        <v>1.56</v>
+      </c>
+      <c r="L25">
+        <v>2.34</v>
+      </c>
+      <c r="M25">
+        <v>0.09838296000000001</v>
+      </c>
+      <c r="N25">
+        <v>2.24161704</v>
+      </c>
+      <c r="O25">
+        <v>0.3362425560000003</v>
+      </c>
+      <c r="P25">
+        <v>1.905374484</v>
+      </c>
+      <c r="Q25">
+        <v>3.465374484</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1357233220900276</v>
+      </c>
+      <c r="T25">
+        <v>0.9984181721278781</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W25">
+        <v>0.038845</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>23.78460660260679</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1133258114147961</v>
+      </c>
+      <c r="C26">
+        <v>7.436890859009797</v>
+      </c>
+      <c r="D26">
+        <v>9.015290859009797</v>
+      </c>
+      <c r="E26">
+        <v>2.2464</v>
+      </c>
+      <c r="F26">
+        <v>2.2464</v>
+      </c>
+      <c r="G26">
+        <v>0.668</v>
+      </c>
+      <c r="H26">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>3.9</v>
+      </c>
+      <c r="K26">
+        <v>1.56</v>
+      </c>
+      <c r="L26">
+        <v>2.34</v>
+      </c>
+      <c r="M26">
+        <v>0.10266048</v>
+      </c>
+      <c r="N26">
+        <v>2.23733952</v>
+      </c>
+      <c r="O26">
+        <v>0.3356009280000003</v>
+      </c>
+      <c r="P26">
+        <v>1.901738592</v>
+      </c>
+      <c r="Q26">
+        <v>3.461738592</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1368460676510476</v>
+      </c>
+      <c r="T26">
+        <v>1.009983701936659</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W26">
+        <v>0.038845</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>22.79358132749817</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1132103148202711</v>
+      </c>
+      <c r="C27">
+        <v>7.357284018363897</v>
+      </c>
+      <c r="D27">
+        <v>9.029284018363898</v>
+      </c>
+      <c r="E27">
+        <v>2.34</v>
+      </c>
+      <c r="F27">
+        <v>2.34</v>
+      </c>
+      <c r="G27">
+        <v>0.668</v>
+      </c>
+      <c r="H27">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>3.9</v>
+      </c>
+      <c r="K27">
+        <v>1.56</v>
+      </c>
+      <c r="L27">
+        <v>2.34</v>
+      </c>
+      <c r="M27">
+        <v>0.106938</v>
+      </c>
+      <c r="N27">
+        <v>2.233062</v>
+      </c>
+      <c r="O27">
+        <v>0.3349593000000003</v>
+      </c>
+      <c r="P27">
+        <v>1.898102699999999</v>
+      </c>
+      <c r="Q27">
+        <v>3.4581027</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1379987530936947</v>
+      </c>
+      <c r="T27">
+        <v>1.021857645873673</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W27">
+        <v>0.038845</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>21.88183807439825</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1130948182257459</v>
+      </c>
+      <c r="C28">
+        <v>7.277720684446747</v>
+      </c>
+      <c r="D28">
+        <v>9.043320684446748</v>
+      </c>
+      <c r="E28">
+        <v>2.4336</v>
+      </c>
+      <c r="F28">
+        <v>2.4336</v>
+      </c>
+      <c r="G28">
+        <v>0.668</v>
+      </c>
+      <c r="H28">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>3.9</v>
+      </c>
+      <c r="K28">
+        <v>1.56</v>
+      </c>
+      <c r="L28">
+        <v>2.34</v>
+      </c>
+      <c r="M28">
+        <v>0.11121552</v>
+      </c>
+      <c r="N28">
+        <v>2.22878448</v>
+      </c>
+      <c r="O28">
+        <v>0.3343176720000003</v>
+      </c>
+      <c r="P28">
+        <v>1.894466808</v>
+      </c>
+      <c r="Q28">
+        <v>3.454466807999999</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.139182592196954</v>
+      </c>
+      <c r="T28">
+        <v>1.034052507214391</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W28">
+        <v>0.038845</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>21.04022891769062</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1129793216312208</v>
+      </c>
+      <c r="C29">
+        <v>7.198201060477208</v>
+      </c>
+      <c r="D29">
+        <v>9.057401060477209</v>
+      </c>
+      <c r="E29">
+        <v>2.5272</v>
+      </c>
+      <c r="F29">
+        <v>2.5272</v>
+      </c>
+      <c r="G29">
+        <v>0.668</v>
+      </c>
+      <c r="H29">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>3.9</v>
+      </c>
+      <c r="K29">
+        <v>1.56</v>
+      </c>
+      <c r="L29">
+        <v>2.34</v>
+      </c>
+      <c r="M29">
+        <v>0.11549304</v>
+      </c>
+      <c r="N29">
+        <v>2.22450696</v>
+      </c>
+      <c r="O29">
+        <v>0.3336760440000003</v>
+      </c>
+      <c r="P29">
+        <v>1.890830916</v>
+      </c>
+      <c r="Q29">
+        <v>3.450830916</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1403988652482477</v>
+      </c>
+      <c r="T29">
+        <v>1.046581474345265</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W29">
+        <v>0.038845</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>20.26096117999838</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1128638250366957</v>
+      </c>
+      <c r="C30">
+        <v>7.118725350941747</v>
+      </c>
+      <c r="D30">
+        <v>9.071525350941748</v>
+      </c>
+      <c r="E30">
+        <v>2.6208</v>
+      </c>
+      <c r="F30">
+        <v>2.6208</v>
+      </c>
+      <c r="G30">
+        <v>0.668</v>
+      </c>
+      <c r="H30">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>3.9</v>
+      </c>
+      <c r="K30">
+        <v>1.56</v>
+      </c>
+      <c r="L30">
+        <v>2.34</v>
+      </c>
+      <c r="M30">
+        <v>0.11977056</v>
+      </c>
+      <c r="N30">
+        <v>2.22022944</v>
+      </c>
+      <c r="O30">
+        <v>0.3330344160000003</v>
+      </c>
+      <c r="P30">
+        <v>1.887195023999999</v>
+      </c>
+      <c r="Q30">
+        <v>3.447195024</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1416489236620774</v>
+      </c>
+      <c r="T30">
+        <v>1.059458468340886</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W30">
+        <v>0.038845</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>19.53735542356986</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1127483284421706</v>
+      </c>
+      <c r="C31">
+        <v>7.039293761604355</v>
+      </c>
+      <c r="D31">
+        <v>9.085693761604356</v>
+      </c>
+      <c r="E31">
+        <v>2.714399999999999</v>
+      </c>
+      <c r="F31">
+        <v>2.714399999999999</v>
+      </c>
+      <c r="G31">
+        <v>0.668</v>
+      </c>
+      <c r="H31">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>3.9</v>
+      </c>
+      <c r="K31">
+        <v>1.56</v>
+      </c>
+      <c r="L31">
+        <v>2.34</v>
+      </c>
+      <c r="M31">
+        <v>0.12404808</v>
+      </c>
+      <c r="N31">
+        <v>2.21595192</v>
+      </c>
+      <c r="O31">
+        <v>0.3323927880000003</v>
+      </c>
+      <c r="P31">
+        <v>1.883559131999999</v>
+      </c>
+      <c r="Q31">
+        <v>3.443559131999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1429341949889728</v>
+      </c>
+      <c r="T31">
+        <v>1.072698194561736</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W31">
+        <v>0.038845</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>18.86365351241228</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1126328318476455</v>
+      </c>
+      <c r="C32">
+        <v>6.959906499516515</v>
+      </c>
+      <c r="D32">
+        <v>9.099906499516516</v>
+      </c>
+      <c r="E32">
+        <v>2.808</v>
+      </c>
+      <c r="F32">
+        <v>2.808</v>
+      </c>
+      <c r="G32">
+        <v>0.668</v>
+      </c>
+      <c r="H32">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>3.9</v>
+      </c>
+      <c r="K32">
+        <v>1.56</v>
+      </c>
+      <c r="L32">
+        <v>2.34</v>
+      </c>
+      <c r="M32">
+        <v>0.1283256</v>
+      </c>
+      <c r="N32">
+        <v>2.2116744</v>
+      </c>
+      <c r="O32">
+        <v>0.3317511600000003</v>
+      </c>
+      <c r="P32">
+        <v>1.879923239999999</v>
+      </c>
+      <c r="Q32">
+        <v>3.43992324</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1442561883537793</v>
+      </c>
+      <c r="T32">
+        <v>1.08631619867461</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W32">
+        <v>0.038845</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>18.23486506199854</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1125173352531204</v>
+      </c>
+      <c r="C33">
+        <v>6.880563773027314</v>
+      </c>
+      <c r="D33">
+        <v>9.114163773027315</v>
+      </c>
+      <c r="E33">
+        <v>2.9016</v>
+      </c>
+      <c r="F33">
+        <v>2.9016</v>
+      </c>
+      <c r="G33">
+        <v>0.668</v>
+      </c>
+      <c r="H33">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>3.9</v>
+      </c>
+      <c r="K33">
+        <v>1.56</v>
+      </c>
+      <c r="L33">
+        <v>2.34</v>
+      </c>
+      <c r="M33">
+        <v>0.13260312</v>
+      </c>
+      <c r="N33">
+        <v>2.20739688</v>
+      </c>
+      <c r="O33">
+        <v>0.3311095320000003</v>
+      </c>
+      <c r="P33">
+        <v>1.876287348</v>
+      </c>
+      <c r="Q33">
+        <v>3.436287348</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1456165003668412</v>
+      </c>
+      <c r="T33">
+        <v>1.100328927544379</v>
+      </c>
+      <c r="U33">
+        <v>0.0457</v>
+      </c>
+      <c r="V33">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W33">
+        <v>0.038845</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>17.64664360838568</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1124018386585953</v>
+      </c>
+      <c r="C34">
+        <v>6.801265791793604</v>
+      </c>
+      <c r="D34">
+        <v>9.128465791793605</v>
+      </c>
+      <c r="E34">
+        <v>2.9952</v>
+      </c>
+      <c r="F34">
+        <v>2.9952</v>
+      </c>
+      <c r="G34">
+        <v>0.668</v>
+      </c>
+      <c r="H34">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>3.9</v>
+      </c>
+      <c r="K34">
+        <v>1.56</v>
+      </c>
+      <c r="L34">
+        <v>2.34</v>
+      </c>
+      <c r="M34">
+        <v>0.13688064</v>
+      </c>
+      <c r="N34">
+        <v>2.20311936</v>
+      </c>
+      <c r="O34">
+        <v>0.3304679040000003</v>
+      </c>
+      <c r="P34">
+        <v>1.872651455999999</v>
+      </c>
+      <c r="Q34">
+        <v>3.432651455999999</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1470168215567579</v>
+      </c>
+      <c r="T34">
+        <v>1.114753795498552</v>
+      </c>
+      <c r="U34">
+        <v>0.0457</v>
+      </c>
+      <c r="V34">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W34">
+        <v>0.038845</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>17.09518599562363</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1122863420640703</v>
+      </c>
+      <c r="C35">
+        <v>6.722012766790287</v>
+      </c>
+      <c r="D35">
+        <v>9.142812766790287</v>
+      </c>
+      <c r="E35">
+        <v>3.0888</v>
+      </c>
+      <c r="F35">
+        <v>3.0888</v>
+      </c>
+      <c r="G35">
+        <v>0.668</v>
+      </c>
+      <c r="H35">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>3.9</v>
+      </c>
+      <c r="K35">
+        <v>1.56</v>
+      </c>
+      <c r="L35">
+        <v>2.34</v>
+      </c>
+      <c r="M35">
+        <v>0.14115816</v>
+      </c>
+      <c r="N35">
+        <v>2.19884184</v>
+      </c>
+      <c r="O35">
+        <v>0.3298262760000003</v>
+      </c>
+      <c r="P35">
+        <v>1.869015564</v>
+      </c>
+      <c r="Q35">
+        <v>3.429015564</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1484589433792093</v>
+      </c>
+      <c r="T35">
+        <v>1.129609256525985</v>
+      </c>
+      <c r="U35">
+        <v>0.0457</v>
+      </c>
+      <c r="V35">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W35">
+        <v>0.038845</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>16.57715005636231</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1121708454695452</v>
+      </c>
+      <c r="C36">
+        <v>6.642804910320692</v>
+      </c>
+      <c r="D36">
+        <v>9.157204910320692</v>
+      </c>
+      <c r="E36">
+        <v>3.1824</v>
+      </c>
+      <c r="F36">
+        <v>3.1824</v>
+      </c>
+      <c r="G36">
+        <v>0.668</v>
+      </c>
+      <c r="H36">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>3.9</v>
+      </c>
+      <c r="K36">
+        <v>1.56</v>
+      </c>
+      <c r="L36">
+        <v>2.34</v>
+      </c>
+      <c r="M36">
+        <v>0.14543568</v>
+      </c>
+      <c r="N36">
+        <v>2.19456432</v>
+      </c>
+      <c r="O36">
+        <v>0.3291846480000003</v>
+      </c>
+      <c r="P36">
+        <v>1.865379672</v>
+      </c>
+      <c r="Q36">
+        <v>3.425379672</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1499447658629472</v>
+      </c>
+      <c r="T36">
+        <v>1.144914883039098</v>
+      </c>
+      <c r="U36">
+        <v>0.0457</v>
+      </c>
+      <c r="V36">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W36">
+        <v>0.038845</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>16.08958681941048</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.11205534887502</v>
+      </c>
+      <c r="C37">
+        <v>6.563642436027042</v>
+      </c>
+      <c r="D37">
+        <v>9.171642436027042</v>
+      </c>
+      <c r="E37">
+        <v>3.276</v>
+      </c>
+      <c r="F37">
+        <v>3.276</v>
+      </c>
+      <c r="G37">
+        <v>0.668</v>
+      </c>
+      <c r="H37">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>3.9</v>
+      </c>
+      <c r="K37">
+        <v>1.56</v>
+      </c>
+      <c r="L37">
+        <v>2.34</v>
+      </c>
+      <c r="M37">
+        <v>0.1497132</v>
+      </c>
+      <c r="N37">
+        <v>2.1902868</v>
+      </c>
+      <c r="O37">
+        <v>0.3285430200000003</v>
+      </c>
+      <c r="P37">
+        <v>1.86174378</v>
+      </c>
+      <c r="Q37">
+        <v>3.42174378</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1514763059615693</v>
+      </c>
+      <c r="T37">
+        <v>1.16069145190646</v>
+      </c>
+      <c r="U37">
+        <v>0.0457</v>
+      </c>
+      <c r="V37">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W37">
+        <v>0.038845</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>15.62988433885589</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.111939852280495</v>
+      </c>
+      <c r="C38">
+        <v>6.484525558901014</v>
+      </c>
+      <c r="D38">
+        <v>9.186125558901015</v>
+      </c>
+      <c r="E38">
+        <v>3.3696</v>
+      </c>
+      <c r="F38">
+        <v>3.3696</v>
+      </c>
+      <c r="G38">
+        <v>0.668</v>
+      </c>
+      <c r="H38">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>3.9</v>
+      </c>
+      <c r="K38">
+        <v>1.56</v>
+      </c>
+      <c r="L38">
+        <v>2.34</v>
+      </c>
+      <c r="M38">
+        <v>0.15399072</v>
+      </c>
+      <c r="N38">
+        <v>2.18600928</v>
+      </c>
+      <c r="O38">
+        <v>0.3279013920000003</v>
+      </c>
+      <c r="P38">
+        <v>1.858107888</v>
+      </c>
+      <c r="Q38">
+        <v>3.418107888</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1530557066882734</v>
+      </c>
+      <c r="T38">
+        <v>1.176961038550927</v>
+      </c>
+      <c r="U38">
+        <v>0.0457</v>
+      </c>
+      <c r="V38">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W38">
+        <v>0.038845</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>15.19572088499879</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1118243556859699</v>
+      </c>
+      <c r="C39">
+        <v>6.405454495294452</v>
+      </c>
+      <c r="D39">
+        <v>9.200654495294453</v>
+      </c>
+      <c r="E39">
+        <v>3.4632</v>
+      </c>
+      <c r="F39">
+        <v>3.4632</v>
+      </c>
+      <c r="G39">
+        <v>0.668</v>
+      </c>
+      <c r="H39">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>3.9</v>
+      </c>
+      <c r="K39">
+        <v>1.56</v>
+      </c>
+      <c r="L39">
+        <v>2.34</v>
+      </c>
+      <c r="M39">
+        <v>0.15826824</v>
+      </c>
+      <c r="N39">
+        <v>2.18173176</v>
+      </c>
+      <c r="O39">
+        <v>0.3272597640000003</v>
+      </c>
+      <c r="P39">
+        <v>1.854471996</v>
+      </c>
+      <c r="Q39">
+        <v>3.414471996</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1546852471205871</v>
+      </c>
+      <c r="T39">
+        <v>1.193747120009504</v>
+      </c>
+      <c r="U39">
+        <v>0.0457</v>
+      </c>
+      <c r="V39">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W39">
+        <v>0.038845</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>14.78502572594476</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1117088590914448</v>
+      </c>
+      <c r="C40">
+        <v>6.32642946293008</v>
+      </c>
+      <c r="D40">
+        <v>9.215229462930081</v>
+      </c>
+      <c r="E40">
+        <v>3.5568</v>
+      </c>
+      <c r="F40">
+        <v>3.5568</v>
+      </c>
+      <c r="G40">
+        <v>0.668</v>
+      </c>
+      <c r="H40">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>3.9</v>
+      </c>
+      <c r="K40">
+        <v>1.56</v>
+      </c>
+      <c r="L40">
+        <v>2.34</v>
+      </c>
+      <c r="M40">
+        <v>0.16254576</v>
+      </c>
+      <c r="N40">
+        <v>2.17745424</v>
+      </c>
+      <c r="O40">
+        <v>0.3266181360000003</v>
+      </c>
+      <c r="P40">
+        <v>1.850836104</v>
+      </c>
+      <c r="Q40">
+        <v>3.410836103999999</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.156367353373298</v>
+      </c>
+      <c r="T40">
+        <v>1.211074687966746</v>
+      </c>
+      <c r="U40">
+        <v>0.0457</v>
+      </c>
+      <c r="V40">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W40">
+        <v>0.038845</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>14.39594610157779</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1115933624969197</v>
+      </c>
+      <c r="C41">
+        <v>6.247450680912435</v>
+      </c>
+      <c r="D41">
+        <v>9.229850680912435</v>
+      </c>
+      <c r="E41">
+        <v>3.6504</v>
+      </c>
+      <c r="F41">
+        <v>3.6504</v>
+      </c>
+      <c r="G41">
+        <v>0.668</v>
+      </c>
+      <c r="H41">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>3.9</v>
+      </c>
+      <c r="K41">
+        <v>1.56</v>
+      </c>
+      <c r="L41">
+        <v>2.34</v>
+      </c>
+      <c r="M41">
+        <v>0.16682328</v>
+      </c>
+      <c r="N41">
+        <v>2.17317672</v>
+      </c>
+      <c r="O41">
+        <v>0.3259765080000003</v>
+      </c>
+      <c r="P41">
+        <v>1.847200212</v>
+      </c>
+      <c r="Q41">
+        <v>3.407200211999999</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.158104610650688</v>
+      </c>
+      <c r="T41">
+        <v>1.228970372906191</v>
+      </c>
+      <c r="U41">
+        <v>0.0457</v>
+      </c>
+      <c r="V41">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W41">
+        <v>0.038845</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>14.02681927846041</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1114778659023946</v>
+      </c>
+      <c r="C42">
+        <v>6.168518369738797</v>
+      </c>
+      <c r="D42">
+        <v>9.244518369738797</v>
+      </c>
+      <c r="E42">
+        <v>3.744</v>
+      </c>
+      <c r="F42">
+        <v>3.744</v>
+      </c>
+      <c r="G42">
+        <v>0.668</v>
+      </c>
+      <c r="H42">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>3.9</v>
+      </c>
+      <c r="K42">
+        <v>1.56</v>
+      </c>
+      <c r="L42">
+        <v>2.34</v>
+      </c>
+      <c r="M42">
+        <v>0.1711008</v>
+      </c>
+      <c r="N42">
+        <v>2.1688992</v>
+      </c>
+      <c r="O42">
+        <v>0.3253348800000003</v>
+      </c>
+      <c r="P42">
+        <v>1.84356432</v>
+      </c>
+      <c r="Q42">
+        <v>3.40356432</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.159899776503991</v>
+      </c>
+      <c r="T42">
+        <v>1.247462580676952</v>
+      </c>
+      <c r="U42">
+        <v>0.0457</v>
+      </c>
+      <c r="V42">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W42">
+        <v>0.038845</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>13.67614879649891</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1113623693078695</v>
+      </c>
+      <c r="C43">
+        <v>6.089632751310319</v>
+      </c>
+      <c r="D43">
+        <v>9.25923275131032</v>
+      </c>
+      <c r="E43">
+        <v>3.8376</v>
+      </c>
+      <c r="F43">
+        <v>3.8376</v>
+      </c>
+      <c r="G43">
+        <v>0.668</v>
+      </c>
+      <c r="H43">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>3.9</v>
+      </c>
+      <c r="K43">
+        <v>1.56</v>
+      </c>
+      <c r="L43">
+        <v>2.34</v>
+      </c>
+      <c r="M43">
+        <v>0.17537832</v>
+      </c>
+      <c r="N43">
+        <v>2.16462168</v>
+      </c>
+      <c r="O43">
+        <v>0.3246932520000003</v>
+      </c>
+      <c r="P43">
+        <v>1.839928427999999</v>
+      </c>
+      <c r="Q43">
+        <v>3.399928428</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1617557954370669</v>
+      </c>
+      <c r="T43">
+        <v>1.266581642948416</v>
+      </c>
+      <c r="U43">
+        <v>0.0457</v>
+      </c>
+      <c r="V43">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W43">
+        <v>0.038845</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>13.34258419170625</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1112468727133444</v>
+      </c>
+      <c r="C44">
+        <v>6.010794048943178</v>
+      </c>
+      <c r="D44">
+        <v>9.273994048943178</v>
+      </c>
+      <c r="E44">
+        <v>3.9312</v>
+      </c>
+      <c r="F44">
+        <v>3.9312</v>
+      </c>
+      <c r="G44">
+        <v>0.668</v>
+      </c>
+      <c r="H44">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>3.9</v>
+      </c>
+      <c r="K44">
+        <v>1.56</v>
+      </c>
+      <c r="L44">
+        <v>2.34</v>
+      </c>
+      <c r="M44">
+        <v>0.17965584</v>
+      </c>
+      <c r="N44">
+        <v>2.16034416</v>
+      </c>
+      <c r="O44">
+        <v>0.3240516240000003</v>
+      </c>
+      <c r="P44">
+        <v>1.836292536</v>
+      </c>
+      <c r="Q44">
+        <v>3.396292536</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1636758150230075</v>
+      </c>
+      <c r="T44">
+        <v>1.286359983229241</v>
+      </c>
+      <c r="U44">
+        <v>0.0457</v>
+      </c>
+      <c r="V44">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W44">
+        <v>0.038845</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>13.02490361571324</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1117161761188193</v>
+      </c>
+      <c r="C45">
+        <v>5.857504728669022</v>
+      </c>
+      <c r="D45">
+        <v>9.214304728669022</v>
+      </c>
+      <c r="E45">
+        <v>4.0248</v>
+      </c>
+      <c r="F45">
+        <v>4.0248</v>
+      </c>
+      <c r="G45">
+        <v>0.668</v>
+      </c>
+      <c r="H45">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>3.9</v>
+      </c>
+      <c r="K45">
+        <v>1.56</v>
+      </c>
+      <c r="L45">
+        <v>2.34</v>
+      </c>
+      <c r="M45">
+        <v>0.19037304</v>
+      </c>
+      <c r="N45">
+        <v>2.14962696</v>
+      </c>
+      <c r="O45">
+        <v>0.3224440440000003</v>
+      </c>
+      <c r="P45">
+        <v>1.827182916</v>
+      </c>
+      <c r="Q45">
+        <v>3.387182916</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1656632037172268</v>
+      </c>
+      <c r="T45">
+        <v>1.306832300362025</v>
+      </c>
+      <c r="U45">
+        <v>0.0473</v>
+      </c>
+      <c r="V45">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W45">
+        <v>0.040205</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>12.29165642361965</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1116142795242942</v>
+      </c>
+      <c r="C46">
+        <v>5.776799263627023</v>
+      </c>
+      <c r="D46">
+        <v>9.227199263627023</v>
+      </c>
+      <c r="E46">
+        <v>4.118399999999999</v>
+      </c>
+      <c r="F46">
+        <v>4.118399999999999</v>
+      </c>
+      <c r="G46">
+        <v>0.668</v>
+      </c>
+      <c r="H46">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>3.9</v>
+      </c>
+      <c r="K46">
+        <v>1.56</v>
+      </c>
+      <c r="L46">
+        <v>2.34</v>
+      </c>
+      <c r="M46">
+        <v>0.19480032</v>
+      </c>
+      <c r="N46">
+        <v>2.14519968</v>
+      </c>
+      <c r="O46">
+        <v>0.3217799520000003</v>
+      </c>
+      <c r="P46">
+        <v>1.823419728</v>
+      </c>
+      <c r="Q46">
+        <v>3.383419728</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1677215705790968</v>
+      </c>
+      <c r="T46">
+        <v>1.328035771678123</v>
+      </c>
+      <c r="U46">
+        <v>0.0473</v>
+      </c>
+      <c r="V46">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W46">
+        <v>0.040205</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>12.01230059581011</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1115123829297691</v>
+      </c>
+      <c r="C47">
+        <v>5.696129938487125</v>
+      </c>
+      <c r="D47">
+        <v>9.240129938487126</v>
+      </c>
+      <c r="E47">
+        <v>4.212</v>
+      </c>
+      <c r="F47">
+        <v>4.212</v>
+      </c>
+      <c r="G47">
+        <v>0.668</v>
+      </c>
+      <c r="H47">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>3.9</v>
+      </c>
+      <c r="K47">
+        <v>1.56</v>
+      </c>
+      <c r="L47">
+        <v>2.34</v>
+      </c>
+      <c r="M47">
+        <v>0.1992276</v>
+      </c>
+      <c r="N47">
+        <v>2.1407724</v>
+      </c>
+      <c r="O47">
+        <v>0.3211158600000003</v>
+      </c>
+      <c r="P47">
+        <v>1.81965654</v>
+      </c>
+      <c r="Q47">
+        <v>3.37965654</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1698547871450347</v>
+      </c>
+      <c r="T47">
+        <v>1.350010278314806</v>
+      </c>
+      <c r="U47">
+        <v>0.0473</v>
+      </c>
+      <c r="V47">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W47">
+        <v>0.040205</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>11.74536058256988</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.111410486335244</v>
+      </c>
+      <c r="C48">
+        <v>5.61549690539813</v>
+      </c>
+      <c r="D48">
+        <v>9.253096905398131</v>
+      </c>
+      <c r="E48">
+        <v>4.3056</v>
+      </c>
+      <c r="F48">
+        <v>4.3056</v>
+      </c>
+      <c r="G48">
+        <v>0.668</v>
+      </c>
+      <c r="H48">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>3.9</v>
+      </c>
+      <c r="K48">
+        <v>1.56</v>
+      </c>
+      <c r="L48">
+        <v>2.34</v>
+      </c>
+      <c r="M48">
+        <v>0.20365488</v>
+      </c>
+      <c r="N48">
+        <v>2.13634512</v>
+      </c>
+      <c r="O48">
+        <v>0.3204517680000002</v>
+      </c>
+      <c r="P48">
+        <v>1.815893351999999</v>
+      </c>
+      <c r="Q48">
+        <v>3.375893351999999</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1720670117319333</v>
+      </c>
+      <c r="T48">
+        <v>1.372798655567662</v>
+      </c>
+      <c r="U48">
+        <v>0.0473</v>
+      </c>
+      <c r="V48">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W48">
+        <v>0.040205</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>11.49002665686184</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1113085897407189</v>
+      </c>
+      <c r="C49">
+        <v>5.534900317364114</v>
+      </c>
+      <c r="D49">
+        <v>9.266100317364115</v>
+      </c>
+      <c r="E49">
+        <v>4.3992</v>
+      </c>
+      <c r="F49">
+        <v>4.3992</v>
+      </c>
+      <c r="G49">
+        <v>0.668</v>
+      </c>
+      <c r="H49">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>3.9</v>
+      </c>
+      <c r="K49">
+        <v>1.56</v>
+      </c>
+      <c r="L49">
+        <v>2.34</v>
+      </c>
+      <c r="M49">
+        <v>0.20808216</v>
+      </c>
+      <c r="N49">
+        <v>2.13191784</v>
+      </c>
+      <c r="O49">
+        <v>0.3197876760000002</v>
+      </c>
+      <c r="P49">
+        <v>1.812130164</v>
+      </c>
+      <c r="Q49">
+        <v>3.372130164</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1743627164919224</v>
+      </c>
+      <c r="T49">
+        <v>1.396446971584777</v>
+      </c>
+      <c r="U49">
+        <v>0.0473</v>
+      </c>
+      <c r="V49">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W49">
+        <v>0.040205</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>11.24555800458819</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1112066931461938</v>
+      </c>
+      <c r="C50">
+        <v>5.454340328250411</v>
+      </c>
+      <c r="D50">
+        <v>9.279140328250412</v>
+      </c>
+      <c r="E50">
+        <v>4.4928</v>
+      </c>
+      <c r="F50">
+        <v>4.4928</v>
+      </c>
+      <c r="G50">
+        <v>0.668</v>
+      </c>
+      <c r="H50">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>3.9</v>
+      </c>
+      <c r="K50">
+        <v>1.56</v>
+      </c>
+      <c r="L50">
+        <v>2.34</v>
+      </c>
+      <c r="M50">
+        <v>0.21250944</v>
+      </c>
+      <c r="N50">
+        <v>2.12749056</v>
+      </c>
+      <c r="O50">
+        <v>0.3191235840000003</v>
+      </c>
+      <c r="P50">
+        <v>1.808366976</v>
+      </c>
+      <c r="Q50">
+        <v>3.368366976</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1767467175888342</v>
+      </c>
+      <c r="T50">
+        <v>1.421004838217935</v>
+      </c>
+      <c r="U50">
+        <v>0.0473</v>
+      </c>
+      <c r="V50">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W50">
+        <v>0.040205</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>11.01127554615927</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1111047965516687</v>
+      </c>
+      <c r="C51">
+        <v>5.373817092789729</v>
+      </c>
+      <c r="D51">
+        <v>9.292217092789729</v>
+      </c>
+      <c r="E51">
+        <v>4.586399999999999</v>
+      </c>
+      <c r="F51">
+        <v>4.586399999999999</v>
+      </c>
+      <c r="G51">
+        <v>0.668</v>
+      </c>
+      <c r="H51">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>3.9</v>
+      </c>
+      <c r="K51">
+        <v>1.56</v>
+      </c>
+      <c r="L51">
+        <v>2.34</v>
+      </c>
+      <c r="M51">
+        <v>0.21693672</v>
+      </c>
+      <c r="N51">
+        <v>2.12306328</v>
+      </c>
+      <c r="O51">
+        <v>0.3184594920000002</v>
+      </c>
+      <c r="P51">
+        <v>1.804603788</v>
+      </c>
+      <c r="Q51">
+        <v>3.364603788</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1792242089248406</v>
+      </c>
+      <c r="T51">
+        <v>1.44652575844455</v>
+      </c>
+      <c r="U51">
+        <v>0.0473</v>
+      </c>
+      <c r="V51">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W51">
+        <v>0.040205</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>10.78655563705398</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1110028999571436</v>
+      </c>
+      <c r="C52">
+        <v>5.293330766588221</v>
+      </c>
+      <c r="D52">
+        <v>9.305330766588222</v>
+      </c>
+      <c r="E52">
+        <v>4.68</v>
+      </c>
+      <c r="F52">
+        <v>4.68</v>
+      </c>
+      <c r="G52">
+        <v>0.668</v>
+      </c>
+      <c r="H52">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>3.9</v>
+      </c>
+      <c r="K52">
+        <v>1.56</v>
+      </c>
+      <c r="L52">
+        <v>2.34</v>
+      </c>
+      <c r="M52">
+        <v>0.221364</v>
+      </c>
+      <c r="N52">
+        <v>2.118636</v>
+      </c>
+      <c r="O52">
+        <v>0.3177954000000003</v>
+      </c>
+      <c r="P52">
+        <v>1.8008406</v>
+      </c>
+      <c r="Q52">
+        <v>3.3608406</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1818007999142872</v>
+      </c>
+      <c r="T52">
+        <v>1.47306751548023</v>
+      </c>
+      <c r="U52">
+        <v>0.0473</v>
+      </c>
+      <c r="V52">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W52">
+        <v>0.040205</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>10.5708245243129</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1109010033626185</v>
+      </c>
+      <c r="C53">
+        <v>5.212881506131696</v>
+      </c>
+      <c r="D53">
+        <v>9.318481506131697</v>
+      </c>
+      <c r="E53">
+        <v>4.7736</v>
+      </c>
+      <c r="F53">
+        <v>4.7736</v>
+      </c>
+      <c r="G53">
+        <v>0.668</v>
+      </c>
+      <c r="H53">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>3.9</v>
+      </c>
+      <c r="K53">
+        <v>1.56</v>
+      </c>
+      <c r="L53">
+        <v>2.34</v>
+      </c>
+      <c r="M53">
+        <v>0.22579128</v>
+      </c>
+      <c r="N53">
+        <v>2.11420872</v>
+      </c>
+      <c r="O53">
+        <v>0.3171313080000002</v>
+      </c>
+      <c r="P53">
+        <v>1.797077411999999</v>
+      </c>
+      <c r="Q53">
+        <v>3.357077412</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1844825578828949</v>
+      </c>
+      <c r="T53">
+        <v>1.500692609537774</v>
+      </c>
+      <c r="U53">
+        <v>0.0473</v>
+      </c>
+      <c r="V53">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W53">
+        <v>0.040205</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>10.36355345520872</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1124787067680934</v>
+      </c>
+      <c r="C54">
+        <v>4.919742173114446</v>
+      </c>
+      <c r="D54">
+        <v>9.118942173114446</v>
+      </c>
+      <c r="E54">
+        <v>4.8672</v>
+      </c>
+      <c r="F54">
+        <v>4.8672</v>
+      </c>
+      <c r="G54">
+        <v>0.668</v>
+      </c>
+      <c r="H54">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>3.9</v>
+      </c>
+      <c r="K54">
+        <v>1.56</v>
+      </c>
+      <c r="L54">
+        <v>2.34</v>
+      </c>
+      <c r="M54">
+        <v>0.24871392</v>
+      </c>
+      <c r="N54">
+        <v>2.09128608</v>
+      </c>
+      <c r="O54">
+        <v>0.3136929120000002</v>
+      </c>
+      <c r="P54">
+        <v>1.777593167999999</v>
+      </c>
+      <c r="Q54">
+        <v>3.337593168</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1872760557668613</v>
+      </c>
+      <c r="T54">
+        <v>1.52946874918105</v>
+      </c>
+      <c r="U54">
+        <v>0.0511</v>
+      </c>
+      <c r="V54">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W54">
+        <v>0.04343499999999999</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>9.408399819358722</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1124091101735683</v>
+      </c>
+      <c r="C55">
+        <v>4.834764031460831</v>
+      </c>
+      <c r="D55">
+        <v>9.127564031460832</v>
+      </c>
+      <c r="E55">
+        <v>4.9608</v>
+      </c>
+      <c r="F55">
+        <v>4.9608</v>
+      </c>
+      <c r="G55">
+        <v>0.668</v>
+      </c>
+      <c r="H55">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>3.9</v>
+      </c>
+      <c r="K55">
+        <v>1.56</v>
+      </c>
+      <c r="L55">
+        <v>2.34</v>
+      </c>
+      <c r="M55">
+        <v>0.25349688</v>
+      </c>
+      <c r="N55">
+        <v>2.08650312</v>
+      </c>
+      <c r="O55">
+        <v>0.3129754680000003</v>
+      </c>
+      <c r="P55">
+        <v>1.773527651999999</v>
+      </c>
+      <c r="Q55">
+        <v>3.333527651999999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1901884259012092</v>
+      </c>
+      <c r="T55">
+        <v>1.55946940540489</v>
+      </c>
+      <c r="U55">
+        <v>0.0511</v>
+      </c>
+      <c r="V55">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W55">
+        <v>0.04343499999999999</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>9.230882841634973</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1123395135790432</v>
+      </c>
+      <c r="C56">
+        <v>4.749802208979054</v>
+      </c>
+      <c r="D56">
+        <v>9.136202208979055</v>
+      </c>
+      <c r="E56">
+        <v>5.0544</v>
+      </c>
+      <c r="F56">
+        <v>5.0544</v>
+      </c>
+      <c r="G56">
+        <v>0.668</v>
+      </c>
+      <c r="H56">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>3.9</v>
+      </c>
+      <c r="K56">
+        <v>1.56</v>
+      </c>
+      <c r="L56">
+        <v>2.34</v>
+      </c>
+      <c r="M56">
+        <v>0.25827984</v>
+      </c>
+      <c r="N56">
+        <v>2.08172016</v>
+      </c>
+      <c r="O56">
+        <v>0.3122580240000002</v>
+      </c>
+      <c r="P56">
+        <v>1.769462136</v>
+      </c>
+      <c r="Q56">
+        <v>3.329462136</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.193227420824007</v>
+      </c>
+      <c r="T56">
+        <v>1.590774437986288</v>
+      </c>
+      <c r="U56">
+        <v>0.0511</v>
+      </c>
+      <c r="V56">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W56">
+        <v>0.04343499999999999</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>9.059940566789882</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1122699169845181</v>
+      </c>
+      <c r="C57">
+        <v>4.664856752045596</v>
+      </c>
+      <c r="D57">
+        <v>9.144856752045596</v>
+      </c>
+      <c r="E57">
+        <v>5.148</v>
+      </c>
+      <c r="F57">
+        <v>5.148</v>
+      </c>
+      <c r="G57">
+        <v>0.668</v>
+      </c>
+      <c r="H57">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>3.9</v>
+      </c>
+      <c r="K57">
+        <v>1.56</v>
+      </c>
+      <c r="L57">
+        <v>2.34</v>
+      </c>
+      <c r="M57">
+        <v>0.2630628</v>
+      </c>
+      <c r="N57">
+        <v>2.0769372</v>
+      </c>
+      <c r="O57">
+        <v>0.3115405800000002</v>
+      </c>
+      <c r="P57">
+        <v>1.76539662</v>
+      </c>
+      <c r="Q57">
+        <v>3.325396619999999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.196401482187818</v>
+      </c>
+      <c r="T57">
+        <v>1.623470805349083</v>
+      </c>
+      <c r="U57">
+        <v>0.0511</v>
+      </c>
+      <c r="V57">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W57">
+        <v>0.04343499999999999</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>8.895214374666429</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.112200320389993</v>
+      </c>
+      <c r="C58">
+        <v>4.579927707212825</v>
+      </c>
+      <c r="D58">
+        <v>9.153527707212826</v>
+      </c>
+      <c r="E58">
+        <v>5.2416</v>
+      </c>
+      <c r="F58">
+        <v>5.2416</v>
+      </c>
+      <c r="G58">
+        <v>0.668</v>
+      </c>
+      <c r="H58">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>3.9</v>
+      </c>
+      <c r="K58">
+        <v>1.56</v>
+      </c>
+      <c r="L58">
+        <v>2.34</v>
+      </c>
+      <c r="M58">
+        <v>0.26784576</v>
+      </c>
+      <c r="N58">
+        <v>2.07215424</v>
+      </c>
+      <c r="O58">
+        <v>0.3108231360000002</v>
+      </c>
+      <c r="P58">
+        <v>1.761331103999999</v>
+      </c>
+      <c r="Q58">
+        <v>3.321331104</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.199719819068166</v>
+      </c>
+      <c r="T58">
+        <v>1.657653371228367</v>
+      </c>
+      <c r="U58">
+        <v>0.0511</v>
+      </c>
+      <c r="V58">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W58">
+        <v>0.04343499999999999</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>8.736371260833099</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1121307237954679</v>
+      </c>
+      <c r="C59">
+        <v>4.495015121209855</v>
+      </c>
+      <c r="D59">
+        <v>9.162215121209856</v>
+      </c>
+      <c r="E59">
+        <v>5.3352</v>
+      </c>
+      <c r="F59">
+        <v>5.3352</v>
+      </c>
+      <c r="G59">
+        <v>0.668</v>
+      </c>
+      <c r="H59">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>3.9</v>
+      </c>
+      <c r="K59">
+        <v>1.56</v>
+      </c>
+      <c r="L59">
+        <v>2.34</v>
+      </c>
+      <c r="M59">
+        <v>0.27262872</v>
+      </c>
+      <c r="N59">
+        <v>2.06737128</v>
+      </c>
+      <c r="O59">
+        <v>0.3101056920000002</v>
+      </c>
+      <c r="P59">
+        <v>1.757265587999999</v>
+      </c>
+      <c r="Q59">
+        <v>3.317265588</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2031924971987626</v>
+      </c>
+      <c r="T59">
+        <v>1.693425823892735</v>
+      </c>
+      <c r="U59">
+        <v>0.0511</v>
+      </c>
+      <c r="V59">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W59">
+        <v>0.04343499999999999</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>8.583101589590413</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1120611272009428</v>
+      </c>
+      <c r="C60">
+        <v>4.410119040943359</v>
+      </c>
+      <c r="D60">
+        <v>9.170919040943359</v>
+      </c>
+      <c r="E60">
+        <v>5.428799999999999</v>
+      </c>
+      <c r="F60">
+        <v>5.428799999999999</v>
+      </c>
+      <c r="G60">
+        <v>0.668</v>
+      </c>
+      <c r="H60">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>3.9</v>
+      </c>
+      <c r="K60">
+        <v>1.56</v>
+      </c>
+      <c r="L60">
+        <v>2.34</v>
+      </c>
+      <c r="M60">
+        <v>0.2774116799999999</v>
+      </c>
+      <c r="N60">
+        <v>2.06258832</v>
+      </c>
+      <c r="O60">
+        <v>0.3093882480000003</v>
+      </c>
+      <c r="P60">
+        <v>1.753200071999999</v>
+      </c>
+      <c r="Q60">
+        <v>3.313200071999999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2068305409546257</v>
+      </c>
+      <c r="T60">
+        <v>1.730901726683977</v>
+      </c>
+      <c r="U60">
+        <v>0.0511</v>
+      </c>
+      <c r="V60">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W60">
+        <v>0.04343499999999999</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>8.435117079425062</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1119915306064177</v>
+      </c>
+      <c r="C61">
+        <v>4.325239513498405</v>
+      </c>
+      <c r="D61">
+        <v>9.179639513498405</v>
+      </c>
+      <c r="E61">
+        <v>5.522399999999999</v>
+      </c>
+      <c r="F61">
+        <v>5.522399999999999</v>
+      </c>
+      <c r="G61">
+        <v>0.668</v>
+      </c>
+      <c r="H61">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>3.9</v>
+      </c>
+      <c r="K61">
+        <v>1.56</v>
+      </c>
+      <c r="L61">
+        <v>2.34</v>
+      </c>
+      <c r="M61">
+        <v>0.2821946399999999</v>
+      </c>
+      <c r="N61">
+        <v>2.05780536</v>
+      </c>
+      <c r="O61">
+        <v>0.3086708040000002</v>
+      </c>
+      <c r="P61">
+        <v>1.749134556</v>
+      </c>
+      <c r="Q61">
+        <v>3.309134556</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2106460502595554</v>
+      </c>
+      <c r="T61">
+        <v>1.770205722294304</v>
+      </c>
+      <c r="U61">
+        <v>0.0511</v>
+      </c>
+      <c r="V61">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W61">
+        <v>0.04343499999999999</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>8.292148993333113</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1119219340118926</v>
+      </c>
+      <c r="C62">
+        <v>4.240376586139336</v>
+      </c>
+      <c r="D62">
+        <v>9.188376586139336</v>
+      </c>
+      <c r="E62">
+        <v>5.616</v>
+      </c>
+      <c r="F62">
+        <v>5.616</v>
+      </c>
+      <c r="G62">
+        <v>0.668</v>
+      </c>
+      <c r="H62">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>3.9</v>
+      </c>
+      <c r="K62">
+        <v>1.56</v>
+      </c>
+      <c r="L62">
+        <v>2.34</v>
+      </c>
+      <c r="M62">
+        <v>0.2869776</v>
+      </c>
+      <c r="N62">
+        <v>2.0530224</v>
+      </c>
+      <c r="O62">
+        <v>0.3079533600000002</v>
+      </c>
+      <c r="P62">
+        <v>1.74506904</v>
+      </c>
+      <c r="Q62">
+        <v>3.305069039999999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2146523350297315</v>
+      </c>
+      <c r="T62">
+        <v>1.811474917685148</v>
+      </c>
+      <c r="U62">
+        <v>0.0511</v>
+      </c>
+      <c r="V62">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W62">
+        <v>0.04343499999999999</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>8.153946510110892</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1118523374173675</v>
+      </c>
+      <c r="C63">
+        <v>4.155530306310614</v>
+      </c>
+      <c r="D63">
+        <v>9.197130306310614</v>
+      </c>
+      <c r="E63">
+        <v>5.709599999999999</v>
+      </c>
+      <c r="F63">
+        <v>5.709599999999999</v>
+      </c>
+      <c r="G63">
+        <v>0.668</v>
+      </c>
+      <c r="H63">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>3.9</v>
+      </c>
+      <c r="K63">
+        <v>1.56</v>
+      </c>
+      <c r="L63">
+        <v>2.34</v>
+      </c>
+      <c r="M63">
+        <v>0.2917605599999999</v>
+      </c>
+      <c r="N63">
+        <v>2.04823944</v>
+      </c>
+      <c r="O63">
+        <v>0.3072359160000002</v>
+      </c>
+      <c r="P63">
+        <v>1.741003523999999</v>
+      </c>
+      <c r="Q63">
+        <v>3.301003524</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2188640703009423</v>
+      </c>
+      <c r="T63">
+        <v>1.854860482070394</v>
+      </c>
+      <c r="U63">
+        <v>0.0511</v>
+      </c>
+      <c r="V63">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W63">
+        <v>0.04343499999999999</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>8.02027525584678</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1117827408228424</v>
+      </c>
+      <c r="C64">
+        <v>4.070700721637661</v>
+      </c>
+      <c r="D64">
+        <v>9.205900721637661</v>
+      </c>
+      <c r="E64">
+        <v>5.803199999999999</v>
+      </c>
+      <c r="F64">
+        <v>5.803199999999999</v>
+      </c>
+      <c r="G64">
+        <v>0.668</v>
+      </c>
+      <c r="H64">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>3.9</v>
+      </c>
+      <c r="K64">
+        <v>1.56</v>
+      </c>
+      <c r="L64">
+        <v>2.34</v>
+      </c>
+      <c r="M64">
+        <v>0.2965435199999999</v>
+      </c>
+      <c r="N64">
+        <v>2.04345648</v>
+      </c>
+      <c r="O64">
+        <v>0.3065184720000002</v>
+      </c>
+      <c r="P64">
+        <v>1.736938007999999</v>
+      </c>
+      <c r="Q64">
+        <v>3.296938008</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2232974758495853</v>
+      </c>
+      <c r="T64">
+        <v>1.900529497212758</v>
+      </c>
+      <c r="U64">
+        <v>0.0511</v>
+      </c>
+      <c r="V64">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W64">
+        <v>0.04343499999999999</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>7.890915977526672</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1127305942283173</v>
+      </c>
+      <c r="C65">
+        <v>3.859073206228813</v>
+      </c>
+      <c r="D65">
+        <v>9.087873206228814</v>
+      </c>
+      <c r="E65">
+        <v>5.8968</v>
+      </c>
+      <c r="F65">
+        <v>5.8968</v>
+      </c>
+      <c r="G65">
+        <v>0.668</v>
+      </c>
+      <c r="H65">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>3.9</v>
+      </c>
+      <c r="K65">
+        <v>1.56</v>
+      </c>
+      <c r="L65">
+        <v>2.34</v>
+      </c>
+      <c r="M65">
+        <v>0.3125304</v>
+      </c>
+      <c r="N65">
+        <v>2.0274696</v>
+      </c>
+      <c r="O65">
+        <v>0.3041204400000003</v>
+      </c>
+      <c r="P65">
+        <v>1.72334916</v>
+      </c>
+      <c r="Q65">
+        <v>3.28334916</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2279705249413982</v>
+      </c>
+      <c r="T65">
+        <v>1.948667107768222</v>
+      </c>
+      <c r="U65">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V65">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W65">
+        <v>0.04505</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>7.487271638215033</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1126771476337922</v>
+      </c>
+      <c r="C66">
+        <v>3.77204784926669</v>
+      </c>
+      <c r="D66">
+        <v>9.094447849266691</v>
+      </c>
+      <c r="E66">
+        <v>5.9904</v>
+      </c>
+      <c r="F66">
+        <v>5.9904</v>
+      </c>
+      <c r="G66">
+        <v>0.668</v>
+      </c>
+      <c r="H66">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>3.9</v>
+      </c>
+      <c r="K66">
+        <v>1.56</v>
+      </c>
+      <c r="L66">
+        <v>2.34</v>
+      </c>
+      <c r="M66">
+        <v>0.3174912</v>
+      </c>
+      <c r="N66">
+        <v>2.0225088</v>
+      </c>
+      <c r="O66">
+        <v>0.3033763200000003</v>
+      </c>
+      <c r="P66">
+        <v>1.719132479999999</v>
+      </c>
+      <c r="Q66">
+        <v>3.279132479999999</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2329031878716451</v>
+      </c>
+      <c r="T66">
+        <v>1.999479030021214</v>
+      </c>
+      <c r="U66">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V66">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W66">
+        <v>0.04505</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>7.370283018867923</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1126237010392671</v>
+      </c>
+      <c r="C67">
+        <v>3.685032012073311</v>
+      </c>
+      <c r="D67">
+        <v>9.101032012073311</v>
+      </c>
+      <c r="E67">
+        <v>6.084</v>
+      </c>
+      <c r="F67">
+        <v>6.084</v>
+      </c>
+      <c r="G67">
+        <v>0.668</v>
+      </c>
+      <c r="H67">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>3.9</v>
+      </c>
+      <c r="K67">
+        <v>1.56</v>
+      </c>
+      <c r="L67">
+        <v>2.34</v>
+      </c>
+      <c r="M67">
+        <v>0.322452</v>
+      </c>
+      <c r="N67">
+        <v>2.017548</v>
+      </c>
+      <c r="O67">
+        <v>0.3026322000000002</v>
+      </c>
+      <c r="P67">
+        <v>1.7149158</v>
+      </c>
+      <c r="Q67">
+        <v>3.2749158</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2381177172550489</v>
+      </c>
+      <c r="T67">
+        <v>2.05319449068866</v>
+      </c>
+      <c r="U67">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V67">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W67">
+        <v>0.04505</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>7.256894049346879</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.112570254444742</v>
+      </c>
+      <c r="C68">
+        <v>3.598025715339894</v>
+      </c>
+      <c r="D68">
+        <v>9.107625715339895</v>
+      </c>
+      <c r="E68">
+        <v>6.1776</v>
+      </c>
+      <c r="F68">
+        <v>6.1776</v>
+      </c>
+      <c r="G68">
+        <v>0.668</v>
+      </c>
+      <c r="H68">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>3.9</v>
+      </c>
+      <c r="K68">
+        <v>1.56</v>
+      </c>
+      <c r="L68">
+        <v>2.34</v>
+      </c>
+      <c r="M68">
+        <v>0.3274128000000001</v>
+      </c>
+      <c r="N68">
+        <v>2.0125872</v>
+      </c>
+      <c r="O68">
+        <v>0.3018880800000002</v>
+      </c>
+      <c r="P68">
+        <v>1.710699119999999</v>
+      </c>
+      <c r="Q68">
+        <v>3.270699119999999</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.243638983661006</v>
+      </c>
+      <c r="T68">
+        <v>2.110069684336546</v>
+      </c>
+      <c r="U68">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V68">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W68">
+        <v>0.04505</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>7.146941109205258</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1125168078502169</v>
+      </c>
+      <c r="C69">
+        <v>3.511028979817693</v>
+      </c>
+      <c r="D69">
+        <v>9.114228979817694</v>
+      </c>
+      <c r="E69">
+        <v>6.2712</v>
+      </c>
+      <c r="F69">
+        <v>6.2712</v>
+      </c>
+      <c r="G69">
+        <v>0.668</v>
+      </c>
+      <c r="H69">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>3.9</v>
+      </c>
+      <c r="K69">
+        <v>1.56</v>
+      </c>
+      <c r="L69">
+        <v>2.34</v>
+      </c>
+      <c r="M69">
+        <v>0.3323736</v>
+      </c>
+      <c r="N69">
+        <v>2.0076264</v>
+      </c>
+      <c r="O69">
+        <v>0.3011439600000003</v>
+      </c>
+      <c r="P69">
+        <v>1.70648244</v>
+      </c>
+      <c r="Q69">
+        <v>3.26648244</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2494948722733847</v>
+      </c>
+      <c r="T69">
+        <v>2.170391859417637</v>
+      </c>
+      <c r="U69">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V69">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W69">
+        <v>0.04505</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>7.0402703463813</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1124633612556918</v>
+      </c>
+      <c r="C70">
+        <v>3.424041826318173</v>
+      </c>
+      <c r="D70">
+        <v>9.120841826318173</v>
+      </c>
+      <c r="E70">
+        <v>6.3648</v>
+      </c>
+      <c r="F70">
+        <v>6.3648</v>
+      </c>
+      <c r="G70">
+        <v>0.668</v>
+      </c>
+      <c r="H70">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>3.9</v>
+      </c>
+      <c r="K70">
+        <v>1.56</v>
+      </c>
+      <c r="L70">
+        <v>2.34</v>
+      </c>
+      <c r="M70">
+        <v>0.3373344</v>
+      </c>
+      <c r="N70">
+        <v>2.0026656</v>
+      </c>
+      <c r="O70">
+        <v>0.3003998400000003</v>
+      </c>
+      <c r="P70">
+        <v>1.70226576</v>
+      </c>
+      <c r="Q70">
+        <v>3.26226576</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.255716753924037</v>
+      </c>
+      <c r="T70">
+        <v>2.234484170441295</v>
+      </c>
+      <c r="U70">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V70">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W70">
+        <v>0.04505</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>6.936736958934516</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1124099146611667</v>
+      </c>
+      <c r="C71">
+        <v>3.337064275713238</v>
+      </c>
+      <c r="D71">
+        <v>9.127464275713239</v>
+      </c>
+      <c r="E71">
+        <v>6.4584</v>
+      </c>
+      <c r="F71">
+        <v>6.4584</v>
+      </c>
+      <c r="G71">
+        <v>0.668</v>
+      </c>
+      <c r="H71">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>3.9</v>
+      </c>
+      <c r="K71">
+        <v>1.56</v>
+      </c>
+      <c r="L71">
+        <v>2.34</v>
+      </c>
+      <c r="M71">
+        <v>0.3422952</v>
+      </c>
+      <c r="N71">
+        <v>1.9977048</v>
+      </c>
+      <c r="O71">
+        <v>0.2996557200000002</v>
+      </c>
+      <c r="P71">
+        <v>1.698049079999999</v>
+      </c>
+      <c r="Q71">
+        <v>3.258049079999999</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2623400472940863</v>
+      </c>
+      <c r="T71">
+        <v>2.302711469272932</v>
+      </c>
+      <c r="U71">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V71">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W71">
+        <v>0.04505</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>6.836204539239813</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1123564680666416</v>
+      </c>
+      <c r="C72">
+        <v>3.250096348935467</v>
+      </c>
+      <c r="D72">
+        <v>9.134096348935469</v>
+      </c>
+      <c r="E72">
+        <v>6.552</v>
+      </c>
+      <c r="F72">
+        <v>6.552</v>
+      </c>
+      <c r="G72">
+        <v>0.668</v>
+      </c>
+      <c r="H72">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>3.9</v>
+      </c>
+      <c r="K72">
+        <v>1.56</v>
+      </c>
+      <c r="L72">
+        <v>2.34</v>
+      </c>
+      <c r="M72">
+        <v>0.3472560000000001</v>
+      </c>
+      <c r="N72">
+        <v>1.992744</v>
+      </c>
+      <c r="O72">
+        <v>0.2989116000000002</v>
+      </c>
+      <c r="P72">
+        <v>1.6938324</v>
+      </c>
+      <c r="Q72">
+        <v>3.253832399999999</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2694048935554721</v>
+      </c>
+      <c r="T72">
+        <v>2.375487254693344</v>
+      </c>
+      <c r="U72">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V72">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W72">
+        <v>0.04505</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>6.73854447439353</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1123030214721166</v>
+      </c>
+      <c r="C73">
+        <v>3.163138066978308</v>
+      </c>
+      <c r="D73">
+        <v>9.140738066978308</v>
+      </c>
+      <c r="E73">
+        <v>6.645599999999999</v>
+      </c>
+      <c r="F73">
+        <v>6.645599999999999</v>
+      </c>
+      <c r="G73">
+        <v>0.668</v>
+      </c>
+      <c r="H73">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>3.9</v>
+      </c>
+      <c r="K73">
+        <v>1.56</v>
+      </c>
+      <c r="L73">
+        <v>2.34</v>
+      </c>
+      <c r="M73">
+        <v>0.3522168</v>
+      </c>
+      <c r="N73">
+        <v>1.9877832</v>
+      </c>
+      <c r="O73">
+        <v>0.2981674800000003</v>
+      </c>
+      <c r="P73">
+        <v>1.68961572</v>
+      </c>
+      <c r="Q73">
+        <v>3.24961572</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2769569705935053</v>
+      </c>
+      <c r="T73">
+        <v>2.453282059797923</v>
+      </c>
+      <c r="U73">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V73">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W73">
+        <v>0.04505</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>6.643635397289397</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1122495748775914</v>
+      </c>
+      <c r="C74">
+        <v>3.076189450896325</v>
+      </c>
+      <c r="D74">
+        <v>9.147389450896325</v>
+      </c>
+      <c r="E74">
+        <v>6.739199999999999</v>
+      </c>
+      <c r="F74">
+        <v>6.739199999999999</v>
+      </c>
+      <c r="G74">
+        <v>0.668</v>
+      </c>
+      <c r="H74">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>3.9</v>
+      </c>
+      <c r="K74">
+        <v>1.56</v>
+      </c>
+      <c r="L74">
+        <v>2.34</v>
+      </c>
+      <c r="M74">
+        <v>0.3571776</v>
+      </c>
+      <c r="N74">
+        <v>1.9828224</v>
+      </c>
+      <c r="O74">
+        <v>0.2974233600000002</v>
+      </c>
+      <c r="P74">
+        <v>1.68539904</v>
+      </c>
+      <c r="Q74">
+        <v>3.24539904</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2850484817056837</v>
+      </c>
+      <c r="T74">
+        <v>2.536633636695686</v>
+      </c>
+      <c r="U74">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V74">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W74">
+        <v>0.04505</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>6.551362683438155</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1121961282830663</v>
+      </c>
+      <c r="C75">
+        <v>2.989250521805402</v>
+      </c>
+      <c r="D75">
+        <v>9.154050521805402</v>
+      </c>
+      <c r="E75">
+        <v>6.8328</v>
+      </c>
+      <c r="F75">
+        <v>6.8328</v>
+      </c>
+      <c r="G75">
+        <v>0.668</v>
+      </c>
+      <c r="H75">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>3.9</v>
+      </c>
+      <c r="K75">
+        <v>1.56</v>
+      </c>
+      <c r="L75">
+        <v>2.34</v>
+      </c>
+      <c r="M75">
+        <v>0.3621384</v>
+      </c>
+      <c r="N75">
+        <v>1.9778616</v>
+      </c>
+      <c r="O75">
+        <v>0.2966792400000002</v>
+      </c>
+      <c r="P75">
+        <v>1.68118236</v>
+      </c>
+      <c r="Q75">
+        <v>3.24118236</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2937393640113568</v>
+      </c>
+      <c r="T75">
+        <v>2.626159404474764</v>
+      </c>
+      <c r="U75">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V75">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W75">
+        <v>0.04505</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>6.46161798914448</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1121426816885412</v>
+      </c>
+      <c r="C76">
+        <v>2.902321300882978</v>
+      </c>
+      <c r="D76">
+        <v>9.160721300882978</v>
+      </c>
+      <c r="E76">
+        <v>6.926399999999999</v>
+      </c>
+      <c r="F76">
+        <v>6.926399999999999</v>
+      </c>
+      <c r="G76">
+        <v>0.668</v>
+      </c>
+      <c r="H76">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>3.9</v>
+      </c>
+      <c r="K76">
+        <v>1.56</v>
+      </c>
+      <c r="L76">
+        <v>2.34</v>
+      </c>
+      <c r="M76">
+        <v>0.3670992</v>
+      </c>
+      <c r="N76">
+        <v>1.9729008</v>
+      </c>
+      <c r="O76">
+        <v>0.2959351200000003</v>
+      </c>
+      <c r="P76">
+        <v>1.67696568</v>
+      </c>
+      <c r="Q76">
+        <v>3.23696568</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3030987757251586</v>
+      </c>
+      <c r="T76">
+        <v>2.722571769775311</v>
+      </c>
+      <c r="U76">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V76">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W76">
+        <v>0.04505</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>6.374298827129016</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1120892350940162</v>
+      </c>
+      <c r="C77">
+        <v>2.815401809368263</v>
+      </c>
+      <c r="D77">
+        <v>9.167401809368263</v>
+      </c>
+      <c r="E77">
+        <v>7.02</v>
+      </c>
+      <c r="F77">
+        <v>7.02</v>
+      </c>
+      <c r="G77">
+        <v>0.668</v>
+      </c>
+      <c r="H77">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>3.9</v>
+      </c>
+      <c r="K77">
+        <v>1.56</v>
+      </c>
+      <c r="L77">
+        <v>2.34</v>
+      </c>
+      <c r="M77">
+        <v>0.37206</v>
+      </c>
+      <c r="N77">
+        <v>1.96794</v>
+      </c>
+      <c r="O77">
+        <v>0.2951910000000003</v>
+      </c>
+      <c r="P77">
+        <v>1.672749</v>
+      </c>
+      <c r="Q77">
+        <v>3.232749</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3132069403760646</v>
+      </c>
+      <c r="T77">
+        <v>2.826697124299901</v>
+      </c>
+      <c r="U77">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V77">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W77">
+        <v>0.04505</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>6.289308176100628</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.113327788499491</v>
+      </c>
+      <c r="C78">
+        <v>2.569451699980174</v>
+      </c>
+      <c r="D78">
+        <v>9.015051699980175</v>
+      </c>
+      <c r="E78">
+        <v>7.1136</v>
+      </c>
+      <c r="F78">
+        <v>7.1136</v>
+      </c>
+      <c r="G78">
+        <v>0.668</v>
+      </c>
+      <c r="H78">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>3.9</v>
+      </c>
+      <c r="K78">
+        <v>1.56</v>
+      </c>
+      <c r="L78">
+        <v>2.34</v>
+      </c>
+      <c r="M78">
+        <v>0.391248</v>
+      </c>
+      <c r="N78">
+        <v>1.948752</v>
+      </c>
+      <c r="O78">
+        <v>0.2923128000000002</v>
+      </c>
+      <c r="P78">
+        <v>1.6564392</v>
+      </c>
+      <c r="Q78">
+        <v>3.2164392</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3241574520812127</v>
+      </c>
+      <c r="T78">
+        <v>2.93949959170154</v>
+      </c>
+      <c r="U78">
+        <v>0.055</v>
+      </c>
+      <c r="V78">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W78">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>5.980861244019138</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
         <v>0.77</v>
       </c>
-      <c r="N3">
-        <v>0.07064220183486239</v>
-      </c>
-      <c r="O3">
-        <v>-0.7264150943396226</v>
-      </c>
-      <c r="P3">
-        <v>0.77</v>
-      </c>
-      <c r="Q3">
-        <v>0.07064220183486239</v>
-      </c>
-      <c r="R3">
-        <v>-0.7264150943396226</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0.512</v>
-      </c>
-      <c r="V3">
-        <v>0.04697247706422018</v>
-      </c>
-      <c r="W3">
-        <v>-0.08346456692913387</v>
-      </c>
-      <c r="X3">
-        <v>0.06310106573164015</v>
-      </c>
-      <c r="Y3">
-        <v>-0.146565632660774</v>
-      </c>
-      <c r="Z3">
-        <v>2.598425196850394</v>
-      </c>
-      <c r="AA3">
-        <v>-0.1299212598425197</v>
-      </c>
-      <c r="AB3">
-        <v>0.06310106573164015</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1930223255741598</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>-0.512</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.04928763958413554</v>
-      </c>
-      <c r="AK3">
-        <v>-0.06958412612122859</v>
-      </c>
-      <c r="AL3">
-        <v>0.387</v>
-      </c>
-      <c r="AM3">
-        <v>0.353</v>
-      </c>
-      <c r="AO3">
-        <v>-4.263565891472868</v>
-      </c>
-      <c r="AQ3">
-        <v>-4.674220963172805</v>
+      <c r="B79">
+        <v>0.113291341904966</v>
+      </c>
+      <c r="C79">
+        <v>2.480262520426275</v>
+      </c>
+      <c r="D79">
+        <v>9.019462520426275</v>
+      </c>
+      <c r="E79">
+        <v>7.207199999999999</v>
+      </c>
+      <c r="F79">
+        <v>7.207199999999999</v>
+      </c>
+      <c r="G79">
+        <v>0.668</v>
+      </c>
+      <c r="H79">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>3.9</v>
+      </c>
+      <c r="K79">
+        <v>1.56</v>
+      </c>
+      <c r="L79">
+        <v>2.34</v>
+      </c>
+      <c r="M79">
+        <v>0.396396</v>
+      </c>
+      <c r="N79">
+        <v>1.943604</v>
+      </c>
+      <c r="O79">
+        <v>0.2915406000000003</v>
+      </c>
+      <c r="P79">
+        <v>1.6520634</v>
+      </c>
+      <c r="Q79">
+        <v>3.2120634</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3360601821955042</v>
+      </c>
+      <c r="T79">
+        <v>3.062110969312018</v>
+      </c>
+      <c r="U79">
+        <v>0.055</v>
+      </c>
+      <c r="V79">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W79">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>5.90318772136954</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1132548953104408</v>
+      </c>
+      <c r="C80">
+        <v>2.391077659174987</v>
+      </c>
+      <c r="D80">
+        <v>9.023877659174987</v>
+      </c>
+      <c r="E80">
+        <v>7.3008</v>
+      </c>
+      <c r="F80">
+        <v>7.3008</v>
+      </c>
+      <c r="G80">
+        <v>0.668</v>
+      </c>
+      <c r="H80">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>3.9</v>
+      </c>
+      <c r="K80">
+        <v>1.56</v>
+      </c>
+      <c r="L80">
+        <v>2.34</v>
+      </c>
+      <c r="M80">
+        <v>0.401544</v>
+      </c>
+      <c r="N80">
+        <v>1.938456</v>
+      </c>
+      <c r="O80">
+        <v>0.2907684000000003</v>
+      </c>
+      <c r="P80">
+        <v>1.6476876</v>
+      </c>
+      <c r="Q80">
+        <v>3.2076876</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3490449786838221</v>
+      </c>
+      <c r="T80">
+        <v>3.195868835796175</v>
+      </c>
+      <c r="U80">
+        <v>0.055</v>
+      </c>
+      <c r="V80">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W80">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>5.827505827505827</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1132184487159158</v>
+      </c>
+      <c r="C81">
+        <v>2.301897122570998</v>
+      </c>
+      <c r="D81">
+        <v>9.028297122570999</v>
+      </c>
+      <c r="E81">
+        <v>7.3944</v>
+      </c>
+      <c r="F81">
+        <v>7.3944</v>
+      </c>
+      <c r="G81">
+        <v>0.668</v>
+      </c>
+      <c r="H81">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>3.9</v>
+      </c>
+      <c r="K81">
+        <v>1.56</v>
+      </c>
+      <c r="L81">
+        <v>2.34</v>
+      </c>
+      <c r="M81">
+        <v>0.406692</v>
+      </c>
+      <c r="N81">
+        <v>1.933308</v>
+      </c>
+      <c r="O81">
+        <v>0.2899962000000002</v>
+      </c>
+      <c r="P81">
+        <v>1.6433118</v>
+      </c>
+      <c r="Q81">
+        <v>3.2033118</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3632664224567418</v>
+      </c>
+      <c r="T81">
+        <v>3.342365546707395</v>
+      </c>
+      <c r="U81">
+        <v>0.055</v>
+      </c>
+      <c r="V81">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W81">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>5.75373993095512</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1131820021213907</v>
+      </c>
+      <c r="C82">
+        <v>2.212720916971444</v>
+      </c>
+      <c r="D82">
+        <v>9.032720916971444</v>
+      </c>
+      <c r="E82">
+        <v>7.488</v>
+      </c>
+      <c r="F82">
+        <v>7.488</v>
+      </c>
+      <c r="G82">
+        <v>0.668</v>
+      </c>
+      <c r="H82">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>3.9</v>
+      </c>
+      <c r="K82">
+        <v>1.56</v>
+      </c>
+      <c r="L82">
+        <v>2.34</v>
+      </c>
+      <c r="M82">
+        <v>0.41184</v>
+      </c>
+      <c r="N82">
+        <v>1.92816</v>
+      </c>
+      <c r="O82">
+        <v>0.2892240000000003</v>
+      </c>
+      <c r="P82">
+        <v>1.638936</v>
+      </c>
+      <c r="Q82">
+        <v>3.198936</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3789100106069533</v>
+      </c>
+      <c r="T82">
+        <v>3.503511928709737</v>
+      </c>
+      <c r="U82">
+        <v>0.055</v>
+      </c>
+      <c r="V82">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W82">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>5.681818181818182</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1131455555268655</v>
+      </c>
+      <c r="C83">
+        <v>2.123549048745915</v>
+      </c>
+      <c r="D83">
+        <v>9.037149048745915</v>
+      </c>
+      <c r="E83">
+        <v>7.5816</v>
+      </c>
+      <c r="F83">
+        <v>7.5816</v>
+      </c>
+      <c r="G83">
+        <v>0.668</v>
+      </c>
+      <c r="H83">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>3.9</v>
+      </c>
+      <c r="K83">
+        <v>1.56</v>
+      </c>
+      <c r="L83">
+        <v>2.34</v>
+      </c>
+      <c r="M83">
+        <v>0.416988</v>
+      </c>
+      <c r="N83">
+        <v>1.923012</v>
+      </c>
+      <c r="O83">
+        <v>0.2884518000000003</v>
+      </c>
+      <c r="P83">
+        <v>1.6345602</v>
+      </c>
+      <c r="Q83">
+        <v>3.1945602</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3962002922466609</v>
+      </c>
+      <c r="T83">
+        <v>3.681621087764957</v>
+      </c>
+      <c r="U83">
+        <v>0.055</v>
+      </c>
+      <c r="V83">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W83">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>5.611672278338945</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1131091089323405</v>
+      </c>
+      <c r="C84">
+        <v>2.034381524276503</v>
+      </c>
+      <c r="D84">
+        <v>9.041581524276504</v>
+      </c>
+      <c r="E84">
+        <v>7.6752</v>
+      </c>
+      <c r="F84">
+        <v>7.6752</v>
+      </c>
+      <c r="G84">
+        <v>0.668</v>
+      </c>
+      <c r="H84">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>3.9</v>
+      </c>
+      <c r="K84">
+        <v>1.56</v>
+      </c>
+      <c r="L84">
+        <v>2.34</v>
+      </c>
+      <c r="M84">
+        <v>0.422136</v>
+      </c>
+      <c r="N84">
+        <v>1.917864</v>
+      </c>
+      <c r="O84">
+        <v>0.2876796000000002</v>
+      </c>
+      <c r="P84">
+        <v>1.6301844</v>
+      </c>
+      <c r="Q84">
+        <v>3.1901844</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4154117162907805</v>
+      </c>
+      <c r="T84">
+        <v>3.879520153381869</v>
+      </c>
+      <c r="U84">
+        <v>0.055</v>
+      </c>
+      <c r="V84">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W84">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>5.543237250554323</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1130726623378153</v>
+      </c>
+      <c r="C85">
+        <v>1.945218349957832</v>
+      </c>
+      <c r="D85">
+        <v>9.046018349957833</v>
+      </c>
+      <c r="E85">
+        <v>7.768800000000001</v>
+      </c>
+      <c r="F85">
+        <v>7.768800000000001</v>
+      </c>
+      <c r="G85">
+        <v>0.668</v>
+      </c>
+      <c r="H85">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>3.9</v>
+      </c>
+      <c r="K85">
+        <v>1.56</v>
+      </c>
+      <c r="L85">
+        <v>2.34</v>
+      </c>
+      <c r="M85">
+        <v>0.4272840000000001</v>
+      </c>
+      <c r="N85">
+        <v>1.912716</v>
+      </c>
+      <c r="O85">
+        <v>0.2869074000000003</v>
+      </c>
+      <c r="P85">
+        <v>1.6258086</v>
+      </c>
+      <c r="Q85">
+        <v>3.1858086</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4368833078695023</v>
+      </c>
+      <c r="T85">
+        <v>4.100701462012534</v>
+      </c>
+      <c r="U85">
+        <v>0.055</v>
+      </c>
+      <c r="V85">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W85">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>5.476451259583789</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1130362157432903</v>
+      </c>
+      <c r="C86">
+        <v>1.856059532197072</v>
+      </c>
+      <c r="D86">
+        <v>9.050459532197072</v>
+      </c>
+      <c r="E86">
+        <v>7.862399999999999</v>
+      </c>
+      <c r="F86">
+        <v>7.862399999999999</v>
+      </c>
+      <c r="G86">
+        <v>0.668</v>
+      </c>
+      <c r="H86">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>3.9</v>
+      </c>
+      <c r="K86">
+        <v>1.56</v>
+      </c>
+      <c r="L86">
+        <v>2.34</v>
+      </c>
+      <c r="M86">
+        <v>0.432432</v>
+      </c>
+      <c r="N86">
+        <v>1.907568</v>
+      </c>
+      <c r="O86">
+        <v>0.2861352000000003</v>
+      </c>
+      <c r="P86">
+        <v>1.6214328</v>
+      </c>
+      <c r="Q86">
+        <v>3.1814328</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4610388483955641</v>
+      </c>
+      <c r="T86">
+        <v>4.34953043422203</v>
+      </c>
+      <c r="U86">
+        <v>0.055</v>
+      </c>
+      <c r="V86">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W86">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>5.411255411255412</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1129997691487652</v>
+      </c>
+      <c r="C87">
+        <v>1.766905077413989</v>
+      </c>
+      <c r="D87">
+        <v>9.05490507741399</v>
+      </c>
+      <c r="E87">
+        <v>7.956</v>
+      </c>
+      <c r="F87">
+        <v>7.956</v>
+      </c>
+      <c r="G87">
+        <v>0.668</v>
+      </c>
+      <c r="H87">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>3.9</v>
+      </c>
+      <c r="K87">
+        <v>1.56</v>
+      </c>
+      <c r="L87">
+        <v>2.34</v>
+      </c>
+      <c r="M87">
+        <v>0.43758</v>
+      </c>
+      <c r="N87">
+        <v>1.90242</v>
+      </c>
+      <c r="O87">
+        <v>0.2853630000000002</v>
+      </c>
+      <c r="P87">
+        <v>1.617057</v>
+      </c>
+      <c r="Q87">
+        <v>3.177057</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4884151276584344</v>
+      </c>
+      <c r="T87">
+        <v>4.631536602726128</v>
+      </c>
+      <c r="U87">
+        <v>0.055</v>
+      </c>
+      <c r="V87">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W87">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>5.347593582887701</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.11296332255424</v>
+      </c>
+      <c r="C88">
+        <v>1.677754992040976</v>
+      </c>
+      <c r="D88">
+        <v>9.059354992040976</v>
+      </c>
+      <c r="E88">
+        <v>8.0496</v>
+      </c>
+      <c r="F88">
+        <v>8.0496</v>
+      </c>
+      <c r="G88">
+        <v>0.668</v>
+      </c>
+      <c r="H88">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>3.9</v>
+      </c>
+      <c r="K88">
+        <v>1.56</v>
+      </c>
+      <c r="L88">
+        <v>2.34</v>
+      </c>
+      <c r="M88">
+        <v>0.442728</v>
+      </c>
+      <c r="N88">
+        <v>1.897272</v>
+      </c>
+      <c r="O88">
+        <v>0.2845908000000003</v>
+      </c>
+      <c r="P88">
+        <v>1.612681199999999</v>
+      </c>
+      <c r="Q88">
+        <v>3.1726812</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5197023039588575</v>
+      </c>
+      <c r="T88">
+        <v>4.953829366730812</v>
+      </c>
+      <c r="U88">
+        <v>0.055</v>
+      </c>
+      <c r="V88">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W88">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>5.285412262156448</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.112926875959715</v>
+      </c>
+      <c r="C89">
+        <v>1.588609282523054</v>
+      </c>
+      <c r="D89">
+        <v>9.063809282523055</v>
+      </c>
+      <c r="E89">
+        <v>8.1432</v>
+      </c>
+      <c r="F89">
+        <v>8.1432</v>
+      </c>
+      <c r="G89">
+        <v>0.668</v>
+      </c>
+      <c r="H89">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>3.9</v>
+      </c>
+      <c r="K89">
+        <v>1.56</v>
+      </c>
+      <c r="L89">
+        <v>2.34</v>
+      </c>
+      <c r="M89">
+        <v>0.447876</v>
+      </c>
+      <c r="N89">
+        <v>1.892124</v>
+      </c>
+      <c r="O89">
+        <v>0.2838186000000003</v>
+      </c>
+      <c r="P89">
+        <v>1.6083054</v>
+      </c>
+      <c r="Q89">
+        <v>3.168305399999999</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5558028919978075</v>
+      </c>
+      <c r="T89">
+        <v>5.325705632890062</v>
+      </c>
+      <c r="U89">
+        <v>0.055</v>
+      </c>
+      <c r="V89">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W89">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>5.22466039707419</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1128904293651899</v>
+      </c>
+      <c r="C90">
+        <v>1.499467955317954</v>
+      </c>
+      <c r="D90">
+        <v>9.068267955317953</v>
+      </c>
+      <c r="E90">
+        <v>8.236799999999999</v>
+      </c>
+      <c r="F90">
+        <v>8.236799999999999</v>
+      </c>
+      <c r="G90">
+        <v>0.668</v>
+      </c>
+      <c r="H90">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>3.9</v>
+      </c>
+      <c r="K90">
+        <v>1.56</v>
+      </c>
+      <c r="L90">
+        <v>2.34</v>
+      </c>
+      <c r="M90">
+        <v>0.4530239999999999</v>
+      </c>
+      <c r="N90">
+        <v>1.886976</v>
+      </c>
+      <c r="O90">
+        <v>0.2830464000000003</v>
+      </c>
+      <c r="P90">
+        <v>1.6039296</v>
+      </c>
+      <c r="Q90">
+        <v>3.1639296</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5979202447099157</v>
+      </c>
+      <c r="T90">
+        <v>5.759561276742521</v>
+      </c>
+      <c r="U90">
+        <v>0.055</v>
+      </c>
+      <c r="V90">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W90">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>5.165289256198347</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1128539827706648</v>
+      </c>
+      <c r="C91">
+        <v>1.4103310168961</v>
+      </c>
+      <c r="D91">
+        <v>9.0727310168961</v>
+      </c>
+      <c r="E91">
+        <v>8.330399999999999</v>
+      </c>
+      <c r="F91">
+        <v>8.330399999999999</v>
+      </c>
+      <c r="G91">
+        <v>0.668</v>
+      </c>
+      <c r="H91">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>3.9</v>
+      </c>
+      <c r="K91">
+        <v>1.56</v>
+      </c>
+      <c r="L91">
+        <v>2.34</v>
+      </c>
+      <c r="M91">
+        <v>0.458172</v>
+      </c>
+      <c r="N91">
+        <v>1.881828</v>
+      </c>
+      <c r="O91">
+        <v>0.2822742000000003</v>
+      </c>
+      <c r="P91">
+        <v>1.5995538</v>
+      </c>
+      <c r="Q91">
+        <v>3.159553799999999</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6476952979151345</v>
+      </c>
+      <c r="T91">
+        <v>6.272299764931791</v>
+      </c>
+      <c r="U91">
+        <v>0.055</v>
+      </c>
+      <c r="V91">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W91">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>5.107252298263534</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1128175361761397</v>
+      </c>
+      <c r="C92">
+        <v>1.321198473740671</v>
+      </c>
+      <c r="D92">
+        <v>9.077198473740671</v>
+      </c>
+      <c r="E92">
+        <v>8.423999999999999</v>
+      </c>
+      <c r="F92">
+        <v>8.423999999999999</v>
+      </c>
+      <c r="G92">
+        <v>0.668</v>
+      </c>
+      <c r="H92">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>3.9</v>
+      </c>
+      <c r="K92">
+        <v>1.56</v>
+      </c>
+      <c r="L92">
+        <v>2.34</v>
+      </c>
+      <c r="M92">
+        <v>0.46332</v>
+      </c>
+      <c r="N92">
+        <v>1.87668</v>
+      </c>
+      <c r="O92">
+        <v>0.2815020000000003</v>
+      </c>
+      <c r="P92">
+        <v>1.595178</v>
+      </c>
+      <c r="Q92">
+        <v>3.155178</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7074253617613968</v>
+      </c>
+      <c r="T92">
+        <v>6.887585950758915</v>
+      </c>
+      <c r="U92">
+        <v>0.055</v>
+      </c>
+      <c r="V92">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W92">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>5.050505050505051</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1127810895816146</v>
+      </c>
+      <c r="C93">
+        <v>1.232070332347606</v>
+      </c>
+      <c r="D93">
+        <v>9.081670332347606</v>
+      </c>
+      <c r="E93">
+        <v>8.5176</v>
+      </c>
+      <c r="F93">
+        <v>8.5176</v>
+      </c>
+      <c r="G93">
+        <v>0.668</v>
+      </c>
+      <c r="H93">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>3.9</v>
+      </c>
+      <c r="K93">
+        <v>1.56</v>
+      </c>
+      <c r="L93">
+        <v>2.34</v>
+      </c>
+      <c r="M93">
+        <v>0.468468</v>
+      </c>
+      <c r="N93">
+        <v>1.871532</v>
+      </c>
+      <c r="O93">
+        <v>0.2807298000000002</v>
+      </c>
+      <c r="P93">
+        <v>1.590802199999999</v>
+      </c>
+      <c r="Q93">
+        <v>3.150802199999999</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7804287731290511</v>
+      </c>
+      <c r="T93">
+        <v>7.639602400103176</v>
+      </c>
+      <c r="U93">
+        <v>0.055</v>
+      </c>
+      <c r="V93">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W93">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>4.995004995004995</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1127446429870895</v>
+      </c>
+      <c r="C94">
+        <v>1.142946599225672</v>
+      </c>
+      <c r="D94">
+        <v>9.086146599225673</v>
+      </c>
+      <c r="E94">
+        <v>8.6112</v>
+      </c>
+      <c r="F94">
+        <v>8.6112</v>
+      </c>
+      <c r="G94">
+        <v>0.668</v>
+      </c>
+      <c r="H94">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>3.9</v>
+      </c>
+      <c r="K94">
+        <v>1.56</v>
+      </c>
+      <c r="L94">
+        <v>2.34</v>
+      </c>
+      <c r="M94">
+        <v>0.473616</v>
+      </c>
+      <c r="N94">
+        <v>1.866384</v>
+      </c>
+      <c r="O94">
+        <v>0.2799576000000002</v>
+      </c>
+      <c r="P94">
+        <v>1.5864264</v>
+      </c>
+      <c r="Q94">
+        <v>3.1464264</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8716830373386191</v>
+      </c>
+      <c r="T94">
+        <v>8.579622961783507</v>
+      </c>
+      <c r="U94">
+        <v>0.055</v>
+      </c>
+      <c r="V94">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W94">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>4.940711462450592</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1127081963925644</v>
+      </c>
+      <c r="C95">
+        <v>1.053827280896467</v>
+      </c>
+      <c r="D95">
+        <v>9.090627280896468</v>
+      </c>
+      <c r="E95">
+        <v>8.704800000000001</v>
+      </c>
+      <c r="F95">
+        <v>8.704800000000001</v>
+      </c>
+      <c r="G95">
+        <v>0.668</v>
+      </c>
+      <c r="H95">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>3.9</v>
+      </c>
+      <c r="K95">
+        <v>1.56</v>
+      </c>
+      <c r="L95">
+        <v>2.34</v>
+      </c>
+      <c r="M95">
+        <v>0.478764</v>
+      </c>
+      <c r="N95">
+        <v>1.861236</v>
+      </c>
+      <c r="O95">
+        <v>0.2791854000000003</v>
+      </c>
+      <c r="P95">
+        <v>1.5820506</v>
+      </c>
+      <c r="Q95">
+        <v>3.1420506</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.9890099484652062</v>
+      </c>
+      <c r="T95">
+        <v>9.788220826801073</v>
+      </c>
+      <c r="U95">
+        <v>0.055</v>
+      </c>
+      <c r="V95">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W95">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>4.887585532746822</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1126717497980393</v>
+      </c>
+      <c r="C96">
+        <v>0.9647123838944527</v>
+      </c>
+      <c r="D96">
+        <v>9.095112383894454</v>
+      </c>
+      <c r="E96">
+        <v>8.798400000000001</v>
+      </c>
+      <c r="F96">
+        <v>8.798400000000001</v>
+      </c>
+      <c r="G96">
+        <v>0.668</v>
+      </c>
+      <c r="H96">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>3.9</v>
+      </c>
+      <c r="K96">
+        <v>1.56</v>
+      </c>
+      <c r="L96">
+        <v>2.34</v>
+      </c>
+      <c r="M96">
+        <v>0.4839120000000001</v>
+      </c>
+      <c r="N96">
+        <v>1.856088</v>
+      </c>
+      <c r="O96">
+        <v>0.2784132000000002</v>
+      </c>
+      <c r="P96">
+        <v>1.5776748</v>
+      </c>
+      <c r="Q96">
+        <v>3.1376748</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.145445829967322</v>
+      </c>
+      <c r="T96">
+        <v>11.39968464682449</v>
+      </c>
+      <c r="U96">
+        <v>0.055</v>
+      </c>
+      <c r="V96">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W96">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>4.83558994197292</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1126353032035142</v>
+      </c>
+      <c r="C97">
+        <v>0.8756019147670031</v>
+      </c>
+      <c r="D97">
+        <v>9.099601914767003</v>
+      </c>
+      <c r="E97">
+        <v>8.891999999999999</v>
+      </c>
+      <c r="F97">
+        <v>8.891999999999999</v>
+      </c>
+      <c r="G97">
+        <v>0.668</v>
+      </c>
+      <c r="H97">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>3.9</v>
+      </c>
+      <c r="K97">
+        <v>1.56</v>
+      </c>
+      <c r="L97">
+        <v>2.34</v>
+      </c>
+      <c r="M97">
+        <v>0.48906</v>
+      </c>
+      <c r="N97">
+        <v>1.85094</v>
+      </c>
+      <c r="O97">
+        <v>0.2776410000000002</v>
+      </c>
+      <c r="P97">
+        <v>1.573299</v>
+      </c>
+      <c r="Q97">
+        <v>3.133299</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.364456064070285</v>
+      </c>
+      <c r="T97">
+        <v>13.65573399485729</v>
+      </c>
+      <c r="U97">
+        <v>0.055</v>
+      </c>
+      <c r="V97">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W97">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>4.78468899521531</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1125988566089891</v>
+      </c>
+      <c r="C98">
+        <v>0.7864958800744084</v>
+      </c>
+      <c r="D98">
+        <v>9.104095880074409</v>
+      </c>
+      <c r="E98">
+        <v>8.9856</v>
+      </c>
+      <c r="F98">
+        <v>8.9856</v>
+      </c>
+      <c r="G98">
+        <v>0.668</v>
+      </c>
+      <c r="H98">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>3.9</v>
+      </c>
+      <c r="K98">
+        <v>1.56</v>
+      </c>
+      <c r="L98">
+        <v>2.34</v>
+      </c>
+      <c r="M98">
+        <v>0.494208</v>
+      </c>
+      <c r="N98">
+        <v>1.845792</v>
+      </c>
+      <c r="O98">
+        <v>0.2768688000000002</v>
+      </c>
+      <c r="P98">
+        <v>1.5689232</v>
+      </c>
+      <c r="Q98">
+        <v>3.1289232</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.692971415224726</v>
+      </c>
+      <c r="T98">
+        <v>17.03980801690643</v>
+      </c>
+      <c r="U98">
+        <v>0.055</v>
+      </c>
+      <c r="V98">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W98">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>4.734848484848484</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.112562410014464</v>
+      </c>
+      <c r="C99">
+        <v>0.6973942863899527</v>
+      </c>
+      <c r="D99">
+        <v>9.108594286389952</v>
+      </c>
+      <c r="E99">
+        <v>9.079199999999998</v>
+      </c>
+      <c r="F99">
+        <v>9.079199999999998</v>
+      </c>
+      <c r="G99">
+        <v>0.668</v>
+      </c>
+      <c r="H99">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>3.9</v>
+      </c>
+      <c r="K99">
+        <v>1.56</v>
+      </c>
+      <c r="L99">
+        <v>2.34</v>
+      </c>
+      <c r="M99">
+        <v>0.4993559999999999</v>
+      </c>
+      <c r="N99">
+        <v>1.840644</v>
+      </c>
+      <c r="O99">
+        <v>0.2760966000000002</v>
+      </c>
+      <c r="P99">
+        <v>1.5645474</v>
+      </c>
+      <c r="Q99">
+        <v>3.1245474</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.240497000482132</v>
+      </c>
+      <c r="T99">
+        <v>22.67993138698839</v>
+      </c>
+      <c r="U99">
+        <v>0.055</v>
+      </c>
+      <c r="V99">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W99">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>4.686035613870666</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1125259634199389</v>
+      </c>
+      <c r="C100">
+        <v>0.6082971402998911</v>
+      </c>
+      <c r="D100">
+        <v>9.113097140299891</v>
+      </c>
+      <c r="E100">
+        <v>9.172799999999999</v>
+      </c>
+      <c r="F100">
+        <v>9.172799999999999</v>
+      </c>
+      <c r="G100">
+        <v>0.668</v>
+      </c>
+      <c r="H100">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>3.9</v>
+      </c>
+      <c r="K100">
+        <v>1.56</v>
+      </c>
+      <c r="L100">
+        <v>2.34</v>
+      </c>
+      <c r="M100">
+        <v>0.504504</v>
+      </c>
+      <c r="N100">
+        <v>1.835496</v>
+      </c>
+      <c r="O100">
+        <v>0.2753244000000002</v>
+      </c>
+      <c r="P100">
+        <v>1.5601716</v>
+      </c>
+      <c r="Q100">
+        <v>3.1201716</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.335548170996943</v>
+      </c>
+      <c r="T100">
+        <v>33.9601781271523</v>
+      </c>
+      <c r="U100">
+        <v>0.055</v>
+      </c>
+      <c r="V100">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W100">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>4.63821892393321</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1124895168254138</v>
+      </c>
+      <c r="C101">
+        <v>0.5192044484035314</v>
+      </c>
+      <c r="D101">
+        <v>9.117604448403531</v>
+      </c>
+      <c r="E101">
+        <v>9.266399999999999</v>
+      </c>
+      <c r="F101">
+        <v>9.266399999999999</v>
+      </c>
+      <c r="G101">
+        <v>0.668</v>
+      </c>
+      <c r="H101">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>3.9</v>
+      </c>
+      <c r="K101">
+        <v>1.56</v>
+      </c>
+      <c r="L101">
+        <v>2.34</v>
+      </c>
+      <c r="M101">
+        <v>0.509652</v>
+      </c>
+      <c r="N101">
+        <v>1.830348</v>
+      </c>
+      <c r="O101">
+        <v>0.2745522000000002</v>
+      </c>
+      <c r="P101">
+        <v>1.5557958</v>
+      </c>
+      <c r="Q101">
+        <v>3.1157958</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.620701682541374</v>
+      </c>
+      <c r="T101">
+        <v>67.80091834764404</v>
+      </c>
+      <c r="U101">
+        <v>0.055</v>
+      </c>
+      <c r="V101">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="W101">
+        <v>0.04674999999999999</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>4.591368227731864</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/mauritius/mauritius_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_beverage_soft.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09347398848627837</v>
+        <v>0.09337202750354895</v>
       </c>
       <c r="C2">
-        <v>8.42</v>
+        <v>8.353846560544802</v>
       </c>
       <c r="D2">
-        <v>8.42</v>
+        <v>8.438046560544802</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.0842</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.0842</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>3.08</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.004235259999999999</v>
       </c>
       <c r="N2">
-        <v>3.08</v>
+        <v>3.07576474</v>
       </c>
       <c r="O2">
-        <v>0.462</v>
+        <v>0.461364711</v>
       </c>
       <c r="P2">
-        <v>2.618</v>
+        <v>2.614400029</v>
       </c>
       <c r="Q2">
-        <v>4.998</v>
+        <v>4.994400028999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09347398848627837</v>
+        <v>0.0938833106096454</v>
       </c>
       <c r="T2">
-        <v>0.6562503962404382</v>
+        <v>0.6618848693394722</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>727.2280804484259</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09337202750354895</v>
+        <v>0.09327006652081954</v>
       </c>
       <c r="C3">
-        <v>8.353846560544802</v>
+        <v>8.287770645524803</v>
       </c>
       <c r="D3">
-        <v>8.438046560544802</v>
+        <v>8.456170645524804</v>
       </c>
       <c r="E3">
-        <v>0.0842</v>
+        <v>0.1684</v>
       </c>
       <c r="F3">
-        <v>0.0842</v>
+        <v>0.1684</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1527,28 +1527,28 @@
         <v>3.08</v>
       </c>
       <c r="M3">
-        <v>0.004235259999999999</v>
+        <v>0.008470519999999999</v>
       </c>
       <c r="N3">
-        <v>3.07576474</v>
+        <v>3.07152948</v>
       </c>
       <c r="O3">
-        <v>0.461364711</v>
+        <v>0.460729422</v>
       </c>
       <c r="P3">
-        <v>2.614400029</v>
+        <v>2.610800058</v>
       </c>
       <c r="Q3">
-        <v>4.994400028999999</v>
+        <v>4.990800058</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0938833106096454</v>
+        <v>0.09430098624573423</v>
       </c>
       <c r="T3">
-        <v>0.6618848693394722</v>
+        <v>0.6676343316854255</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>727.2280804484259</v>
+        <v>363.614040224213</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09327006652081954</v>
+        <v>0.0931681055380901</v>
       </c>
       <c r="C4">
-        <v>8.287770645524803</v>
+        <v>8.221772755559629</v>
       </c>
       <c r="D4">
-        <v>8.456170645524804</v>
+        <v>8.474372755559628</v>
       </c>
       <c r="E4">
-        <v>0.1684</v>
+        <v>0.2526</v>
       </c>
       <c r="F4">
-        <v>0.1684</v>
+        <v>0.2526</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1609,28 +1609,28 @@
         <v>3.08</v>
       </c>
       <c r="M4">
-        <v>0.008470519999999999</v>
+        <v>0.01270578</v>
       </c>
       <c r="N4">
-        <v>3.07152948</v>
+        <v>3.06729422</v>
       </c>
       <c r="O4">
-        <v>0.460729422</v>
+        <v>0.460094133</v>
       </c>
       <c r="P4">
-        <v>2.610800058</v>
+        <v>2.607200087</v>
       </c>
       <c r="Q4">
-        <v>4.990800058</v>
+        <v>4.987200087</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09430098624573423</v>
+        <v>0.09472727375060835</v>
       </c>
       <c r="T4">
-        <v>0.6676343316854255</v>
+        <v>0.673502339646759</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>363.614040224213</v>
+        <v>242.4093601494753</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0931681055380901</v>
+        <v>0.09306614455536069</v>
       </c>
       <c r="C5">
-        <v>8.221772755559629</v>
+        <v>8.155853395588563</v>
       </c>
       <c r="D5">
-        <v>8.474372755559628</v>
+        <v>8.492653395588563</v>
       </c>
       <c r="E5">
-        <v>0.2526</v>
+        <v>0.3368</v>
       </c>
       <c r="F5">
-        <v>0.2526</v>
+        <v>0.3368</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1691,28 +1691,28 @@
         <v>3.08</v>
       </c>
       <c r="M5">
-        <v>0.01270578</v>
+        <v>0.01694104</v>
       </c>
       <c r="N5">
-        <v>3.06729422</v>
+        <v>3.06305896</v>
       </c>
       <c r="O5">
-        <v>0.460094133</v>
+        <v>0.459458844</v>
       </c>
       <c r="P5">
-        <v>2.607200087</v>
+        <v>2.603600116</v>
       </c>
       <c r="Q5">
-        <v>4.987200087</v>
+        <v>4.983600116</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09472727375060835</v>
+        <v>0.0951624422451674</v>
       </c>
       <c r="T5">
-        <v>0.673502339646759</v>
+        <v>0.6794925977739538</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>242.4093601494753</v>
+        <v>181.8070201121065</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09306614455536069</v>
+        <v>0.09296418357263127</v>
       </c>
       <c r="C6">
-        <v>8.155853395588563</v>
+        <v>8.090013074917289</v>
       </c>
       <c r="D6">
-        <v>8.492653395588563</v>
+        <v>8.511013074917289</v>
       </c>
       <c r="E6">
-        <v>0.3368</v>
+        <v>0.421</v>
       </c>
       <c r="F6">
-        <v>0.3368</v>
+        <v>0.421</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1773,28 +1773,28 @@
         <v>3.08</v>
       </c>
       <c r="M6">
-        <v>0.01694104</v>
+        <v>0.0211763</v>
       </c>
       <c r="N6">
-        <v>3.06305896</v>
+        <v>3.0588237</v>
       </c>
       <c r="O6">
-        <v>0.459458844</v>
+        <v>0.458823555</v>
       </c>
       <c r="P6">
-        <v>2.603600116</v>
+        <v>2.600000145</v>
       </c>
       <c r="Q6">
-        <v>4.983600116</v>
+        <v>4.980000145</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0951624422451674</v>
+        <v>0.09560677218171713</v>
       </c>
       <c r="T6">
-        <v>0.6794925977739538</v>
+        <v>0.6856089665985631</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>181.8070201121065</v>
+        <v>145.4456160896852</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09296418357263127</v>
+        <v>0.09286222258990186</v>
       </c>
       <c r="C7">
-        <v>8.090013074917289</v>
+        <v>8.024252307265138</v>
       </c>
       <c r="D7">
-        <v>8.511013074917289</v>
+        <v>8.529452307265139</v>
       </c>
       <c r="E7">
-        <v>0.421</v>
+        <v>0.5052</v>
       </c>
       <c r="F7">
-        <v>0.421</v>
+        <v>0.5052</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1855,28 +1855,28 @@
         <v>3.08</v>
       </c>
       <c r="M7">
-        <v>0.0211763</v>
+        <v>0.02541156</v>
       </c>
       <c r="N7">
-        <v>3.0588237</v>
+        <v>3.05458844</v>
       </c>
       <c r="O7">
-        <v>0.458823555</v>
+        <v>0.458188266</v>
       </c>
       <c r="P7">
-        <v>2.600000145</v>
+        <v>2.596400174</v>
       </c>
       <c r="Q7">
-        <v>4.980000145</v>
+        <v>4.976400174</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09560677218171713</v>
+        <v>0.09606055594670411</v>
       </c>
       <c r="T7">
-        <v>0.6856089665985631</v>
+        <v>0.691855470930079</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>145.4456160896852</v>
+        <v>121.2046800747377</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09286222258990184</v>
+        <v>0.09276026160717246</v>
       </c>
       <c r="C8">
-        <v>8.02425230726514</v>
+        <v>7.958571610813044</v>
       </c>
       <c r="D8">
-        <v>8.52945230726514</v>
+        <v>8.547971610813043</v>
       </c>
       <c r="E8">
-        <v>0.5052</v>
+        <v>0.5893999999999999</v>
       </c>
       <c r="F8">
-        <v>0.5052</v>
+        <v>0.5893999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1937,28 +1937,28 @@
         <v>3.08</v>
       </c>
       <c r="M8">
-        <v>0.02541156</v>
+        <v>0.02964681999999999</v>
       </c>
       <c r="N8">
-        <v>3.05458844</v>
+        <v>3.05035318</v>
       </c>
       <c r="O8">
-        <v>0.458188266</v>
+        <v>0.457552977</v>
       </c>
       <c r="P8">
-        <v>2.596400174</v>
+        <v>2.592800203</v>
       </c>
       <c r="Q8">
-        <v>4.976400174</v>
+        <v>4.972800203</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09606055594670411</v>
+        <v>0.09652409850233597</v>
       </c>
       <c r="T8">
-        <v>0.691855470930079</v>
+        <v>0.6982363086880792</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>121.2046800747377</v>
+        <v>103.8897257783466</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09276026160717245</v>
+        <v>0.09265830062444305</v>
       </c>
       <c r="C9">
-        <v>7.958571610813045</v>
+        <v>7.892971508252066</v>
       </c>
       <c r="D9">
-        <v>8.547971610813045</v>
+        <v>8.566571508252066</v>
       </c>
       <c r="E9">
-        <v>0.5894</v>
+        <v>0.6736</v>
       </c>
       <c r="F9">
-        <v>0.5894</v>
+        <v>0.6736</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2019,28 +2019,28 @@
         <v>3.08</v>
       </c>
       <c r="M9">
-        <v>0.02964682</v>
+        <v>0.03388207999999999</v>
       </c>
       <c r="N9">
-        <v>3.05035318</v>
+        <v>3.04611792</v>
       </c>
       <c r="O9">
-        <v>0.457552977</v>
+        <v>0.456917688</v>
       </c>
       <c r="P9">
-        <v>2.592800203</v>
+        <v>2.589200232</v>
       </c>
       <c r="Q9">
-        <v>4.972800203</v>
+        <v>4.969200232</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09652409850233597</v>
+        <v>0.09699771807004678</v>
       </c>
       <c r="T9">
-        <v>0.6982363086880792</v>
+        <v>0.7047558603103837</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>103.8897257783465</v>
+        <v>90.90351005605324</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09265830062444305</v>
+        <v>0.09255633964171361</v>
       </c>
       <c r="C10">
-        <v>7.892971508252066</v>
+        <v>7.827452526832575</v>
       </c>
       <c r="D10">
-        <v>8.566571508252066</v>
+        <v>8.585252526832575</v>
       </c>
       <c r="E10">
-        <v>0.6736</v>
+        <v>0.7577999999999999</v>
       </c>
       <c r="F10">
-        <v>0.6736</v>
+        <v>0.7577999999999999</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2101,28 +2101,28 @@
         <v>3.08</v>
       </c>
       <c r="M10">
-        <v>0.03388207999999999</v>
+        <v>0.03811733999999999</v>
       </c>
       <c r="N10">
-        <v>3.04611792</v>
+        <v>3.04188266</v>
       </c>
       <c r="O10">
-        <v>0.456917688</v>
+        <v>0.456282399</v>
       </c>
       <c r="P10">
-        <v>2.589200232</v>
+        <v>2.585600261</v>
       </c>
       <c r="Q10">
-        <v>4.969200232</v>
+        <v>4.965600261000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09699771807004678</v>
+        <v>0.09748174685902594</v>
       </c>
       <c r="T10">
-        <v>0.7047558603103837</v>
+        <v>0.71141869878153</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>90.90351005605324</v>
+        <v>80.80312004982511</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09255633964171361</v>
+        <v>0.09245437865898419</v>
       </c>
       <c r="C11">
-        <v>7.827452526832575</v>
+        <v>7.762015198414047</v>
       </c>
       <c r="D11">
-        <v>8.585252526832575</v>
+        <v>8.604015198414046</v>
       </c>
       <c r="E11">
-        <v>0.7577999999999999</v>
+        <v>0.842</v>
       </c>
       <c r="F11">
-        <v>0.7577999999999999</v>
+        <v>0.842</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2183,28 +2183,28 @@
         <v>3.08</v>
       </c>
       <c r="M11">
-        <v>0.03811733999999999</v>
+        <v>0.0423526</v>
       </c>
       <c r="N11">
-        <v>3.04188266</v>
+        <v>3.0376474</v>
       </c>
       <c r="O11">
-        <v>0.456282399</v>
+        <v>0.45564711</v>
       </c>
       <c r="P11">
-        <v>2.585600261</v>
+        <v>2.58200029</v>
       </c>
       <c r="Q11">
-        <v>4.965600261000001</v>
+        <v>4.96200029</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09748174685902594</v>
+        <v>0.09797653184331577</v>
       </c>
       <c r="T11">
-        <v>0.71141869878153</v>
+        <v>0.718229600329813</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>80.80312004982511</v>
+        <v>72.72280804484259</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09245437865898419</v>
+        <v>0.09235241767625478</v>
       </c>
       <c r="C12">
-        <v>7.762015198414046</v>
+        <v>7.696660059515569</v>
       </c>
       <c r="D12">
-        <v>8.604015198414046</v>
+        <v>8.622860059515569</v>
       </c>
       <c r="E12">
-        <v>0.8420000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F12">
-        <v>0.8420000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2265,28 +2265,28 @@
         <v>3.08</v>
       </c>
       <c r="M12">
-        <v>0.0423526</v>
+        <v>0.04658786</v>
       </c>
       <c r="N12">
-        <v>3.0376474</v>
+        <v>3.03341214</v>
       </c>
       <c r="O12">
-        <v>0.45564711</v>
+        <v>0.455011821</v>
       </c>
       <c r="P12">
-        <v>2.58200029</v>
+        <v>2.578400319</v>
       </c>
       <c r="Q12">
-        <v>4.96200029</v>
+        <v>4.958400319</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09797653184331577</v>
+        <v>0.0984824355912975</v>
       </c>
       <c r="T12">
-        <v>0.718229600329813</v>
+        <v>0.7251935558454731</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>72.72280804484258</v>
+        <v>66.11164367712962</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09235241767625478</v>
+        <v>0.09225045669352537</v>
       </c>
       <c r="C13">
-        <v>7.696660059515569</v>
+        <v>7.631387651366974</v>
       </c>
       <c r="D13">
-        <v>8.622860059515569</v>
+        <v>8.641787651366974</v>
       </c>
       <c r="E13">
-        <v>0.9262</v>
+        <v>1.0104</v>
       </c>
       <c r="F13">
-        <v>0.9262</v>
+        <v>1.0104</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2347,28 +2347,28 @@
         <v>3.08</v>
       </c>
       <c r="M13">
-        <v>0.04658786</v>
+        <v>0.05082311999999999</v>
       </c>
       <c r="N13">
-        <v>3.03341214</v>
+        <v>3.02917688</v>
       </c>
       <c r="O13">
-        <v>0.455011821</v>
+        <v>0.454376532</v>
       </c>
       <c r="P13">
-        <v>2.578400319</v>
+        <v>2.574800348</v>
       </c>
       <c r="Q13">
-        <v>4.958400319</v>
+        <v>4.954800348</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0984824355912975</v>
+        <v>0.09899983715173337</v>
       </c>
       <c r="T13">
-        <v>0.7251935558454731</v>
+        <v>0.7323157830773982</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>66.11164367712962</v>
+        <v>60.60234003736883</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09225045669352537</v>
+        <v>0.09214849571079593</v>
       </c>
       <c r="C14">
-        <v>7.631387651366974</v>
+        <v>7.566198519960649</v>
       </c>
       <c r="D14">
-        <v>8.641787651366974</v>
+        <v>8.660798519960649</v>
       </c>
       <c r="E14">
-        <v>1.0104</v>
+        <v>1.0946</v>
       </c>
       <c r="F14">
-        <v>1.0104</v>
+        <v>1.0946</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2429,28 +2429,28 @@
         <v>3.08</v>
       </c>
       <c r="M14">
-        <v>0.05082311999999999</v>
+        <v>0.05505838</v>
       </c>
       <c r="N14">
-        <v>3.02917688</v>
+        <v>3.02494162</v>
       </c>
       <c r="O14">
-        <v>0.454376532</v>
+        <v>0.453741243</v>
       </c>
       <c r="P14">
-        <v>2.574800348</v>
+        <v>2.571200377</v>
       </c>
       <c r="Q14">
-        <v>4.954800348</v>
+        <v>4.951200376999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09899983715173337</v>
+        <v>0.09952913300091487</v>
       </c>
       <c r="T14">
-        <v>0.7323157830773982</v>
+        <v>0.7396017396709766</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>60.60234003736883</v>
+        <v>55.94062157295583</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09214849571079593</v>
+        <v>0.09204653472806651</v>
       </c>
       <c r="C15">
-        <v>7.566198519960649</v>
+        <v>7.501093216104029</v>
       </c>
       <c r="D15">
-        <v>8.660798519960649</v>
+        <v>8.679893216104029</v>
       </c>
       <c r="E15">
-        <v>1.0946</v>
+        <v>1.1788</v>
       </c>
       <c r="F15">
-        <v>1.0946</v>
+        <v>1.1788</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2511,28 +2511,28 @@
         <v>3.08</v>
       </c>
       <c r="M15">
-        <v>0.05505838</v>
+        <v>0.05929364</v>
       </c>
       <c r="N15">
-        <v>3.02494162</v>
+        <v>3.02070636</v>
       </c>
       <c r="O15">
-        <v>0.453741243</v>
+        <v>0.453105954</v>
       </c>
       <c r="P15">
-        <v>2.571200377</v>
+        <v>2.567600406</v>
       </c>
       <c r="Q15">
-        <v>4.951200376999999</v>
+        <v>4.947600406</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09952913300091487</v>
+        <v>0.1000707380558913</v>
       </c>
       <c r="T15">
-        <v>0.7396017396709766</v>
+        <v>0.7470571371155685</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>55.94062157295583</v>
+        <v>51.94486288917327</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09204653472806651</v>
+        <v>0.0919445737453371</v>
       </c>
       <c r="C16">
-        <v>7.501093216104029</v>
+        <v>7.436072295472808</v>
       </c>
       <c r="D16">
-        <v>8.679893216104029</v>
+        <v>8.699072295472808</v>
       </c>
       <c r="E16">
-        <v>1.1788</v>
+        <v>1.263</v>
       </c>
       <c r="F16">
-        <v>1.1788</v>
+        <v>1.263</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2593,28 +2593,28 @@
         <v>3.08</v>
       </c>
       <c r="M16">
-        <v>0.05929364</v>
+        <v>0.0635289</v>
       </c>
       <c r="N16">
-        <v>3.02070636</v>
+        <v>3.0164711</v>
       </c>
       <c r="O16">
-        <v>0.453105954</v>
+        <v>0.452470665</v>
       </c>
       <c r="P16">
-        <v>2.567600406</v>
+        <v>2.564000435</v>
       </c>
       <c r="Q16">
-        <v>4.947600406</v>
+        <v>4.944000435</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1000707380558913</v>
+        <v>0.1006250867592201</v>
       </c>
       <c r="T16">
-        <v>0.7470571371155685</v>
+        <v>0.7546879556765039</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>51.94486288917327</v>
+        <v>48.48187202989506</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0919445737453371</v>
+        <v>0.09184261276260769</v>
       </c>
       <c r="C17">
-        <v>7.436072295472808</v>
+        <v>7.371136318664839</v>
       </c>
       <c r="D17">
-        <v>8.699072295472808</v>
+        <v>8.718336318664839</v>
       </c>
       <c r="E17">
-        <v>1.263</v>
+        <v>1.3472</v>
       </c>
       <c r="F17">
-        <v>1.263</v>
+        <v>1.3472</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2675,28 +2675,28 @@
         <v>3.08</v>
       </c>
       <c r="M17">
-        <v>0.06352889999999999</v>
+        <v>0.06776415999999999</v>
       </c>
       <c r="N17">
-        <v>3.0164711</v>
+        <v>3.01223584</v>
       </c>
       <c r="O17">
-        <v>0.452470665</v>
+        <v>0.451835376</v>
       </c>
       <c r="P17">
-        <v>2.564000435</v>
+        <v>2.560400464</v>
       </c>
       <c r="Q17">
-        <v>4.944000435</v>
+        <v>4.940400464</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1006250867592201</v>
+        <v>0.1011926342411996</v>
       </c>
       <c r="T17">
-        <v>0.7546879556765039</v>
+        <v>0.7625004603936522</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>48.48187202989507</v>
+        <v>45.45175502802662</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09184261276260769</v>
+        <v>0.09174065177987828</v>
       </c>
       <c r="C18">
-        <v>7.371136318664839</v>
+        <v>7.306285851254753</v>
       </c>
       <c r="D18">
-        <v>8.718336318664839</v>
+        <v>8.737685851254753</v>
       </c>
       <c r="E18">
-        <v>1.3472</v>
+        <v>1.4314</v>
       </c>
       <c r="F18">
-        <v>1.3472</v>
+        <v>1.4314</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2757,28 +2757,28 @@
         <v>3.08</v>
       </c>
       <c r="M18">
-        <v>0.06776415999999999</v>
+        <v>0.07199941999999999</v>
       </c>
       <c r="N18">
-        <v>3.01223584</v>
+        <v>3.00800058</v>
       </c>
       <c r="O18">
-        <v>0.451835376</v>
+        <v>0.451200087</v>
       </c>
       <c r="P18">
-        <v>2.560400464</v>
+        <v>2.556800493</v>
       </c>
       <c r="Q18">
-        <v>4.940400464</v>
+        <v>4.936800493</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1011926342411996</v>
+        <v>0.1017738575661184</v>
       </c>
       <c r="T18">
-        <v>0.7625004603936522</v>
+        <v>0.7705012182365145</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>45.45175502802662</v>
+        <v>42.77812237931917</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09174065177987828</v>
+        <v>0.09163869079714884</v>
       </c>
       <c r="C19">
-        <v>7.306285851254753</v>
+        <v>7.241521463849309</v>
       </c>
       <c r="D19">
-        <v>8.737685851254753</v>
+        <v>8.757121463849309</v>
       </c>
       <c r="E19">
-        <v>1.4314</v>
+        <v>1.5156</v>
       </c>
       <c r="F19">
-        <v>1.4314</v>
+        <v>1.5156</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2839,28 +2839,28 @@
         <v>3.08</v>
       </c>
       <c r="M19">
-        <v>0.07199941999999999</v>
+        <v>0.07623468</v>
       </c>
       <c r="N19">
-        <v>3.00800058</v>
+        <v>3.00376532</v>
       </c>
       <c r="O19">
-        <v>0.451200087</v>
+        <v>0.450564798</v>
       </c>
       <c r="P19">
-        <v>2.556800493</v>
+        <v>2.553200522</v>
       </c>
       <c r="Q19">
-        <v>4.936800493</v>
+        <v>4.933200522</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1017738575661184</v>
+        <v>0.1023692570696937</v>
       </c>
       <c r="T19">
-        <v>0.7705012182365145</v>
+        <v>0.7786971165145687</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>42.77812237931917</v>
+        <v>40.40156002491255</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09163869079714884</v>
+        <v>0.09153672981441943</v>
       </c>
       <c r="C20">
-        <v>7.241521463849309</v>
+        <v>7.176843732143475</v>
       </c>
       <c r="D20">
-        <v>8.757121463849309</v>
+        <v>8.776643732143475</v>
       </c>
       <c r="E20">
-        <v>1.5156</v>
+        <v>1.5998</v>
       </c>
       <c r="F20">
-        <v>1.5156</v>
+        <v>1.5998</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2921,28 +2921,28 @@
         <v>3.08</v>
       </c>
       <c r="M20">
-        <v>0.07623467999999999</v>
+        <v>0.08046994</v>
       </c>
       <c r="N20">
-        <v>3.00376532</v>
+        <v>2.99953006</v>
       </c>
       <c r="O20">
-        <v>0.450564798</v>
+        <v>0.449929509</v>
       </c>
       <c r="P20">
-        <v>2.553200522</v>
+        <v>2.549600551</v>
       </c>
       <c r="Q20">
-        <v>4.933200522</v>
+        <v>4.929600551</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1023692570696937</v>
+        <v>0.1029793577955795</v>
       </c>
       <c r="T20">
-        <v>0.7786971165145687</v>
+        <v>0.7870953826513404</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>40.40156002491256</v>
+        <v>38.27516212886452</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09153672981441943</v>
+        <v>0.09143476883169002</v>
       </c>
       <c r="C21">
-        <v>7.176843732143475</v>
+        <v>7.112253236977295</v>
       </c>
       <c r="D21">
-        <v>8.776643732143475</v>
+        <v>8.796253236977295</v>
       </c>
       <c r="E21">
-        <v>1.5998</v>
+        <v>1.684</v>
       </c>
       <c r="F21">
-        <v>1.5998</v>
+        <v>1.684</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3003,28 +3003,28 @@
         <v>3.08</v>
       </c>
       <c r="M21">
-        <v>0.08046994</v>
+        <v>0.08470520000000001</v>
       </c>
       <c r="N21">
-        <v>2.99953006</v>
+        <v>2.9952948</v>
       </c>
       <c r="O21">
-        <v>0.449929509</v>
+        <v>0.44929422</v>
       </c>
       <c r="P21">
-        <v>2.549600551</v>
+        <v>2.54600058</v>
       </c>
       <c r="Q21">
-        <v>4.929600551</v>
+        <v>4.92600058</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1029793577955795</v>
+        <v>0.1036047110396125</v>
       </c>
       <c r="T21">
-        <v>0.7870953826513404</v>
+        <v>0.7957036054415313</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>38.27516212886452</v>
+        <v>36.36140402242129</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09143476883169002</v>
+        <v>0.09133280784896061</v>
       </c>
       <c r="C22">
-        <v>7.112253236977295</v>
+        <v>7.047750564393475</v>
       </c>
       <c r="D22">
-        <v>8.796253236977295</v>
+        <v>8.815950564393475</v>
       </c>
       <c r="E22">
-        <v>1.684</v>
+        <v>1.7682</v>
       </c>
       <c r="F22">
-        <v>1.684</v>
+        <v>1.7682</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3085,28 +3085,28 @@
         <v>3.08</v>
       </c>
       <c r="M22">
-        <v>0.08470520000000001</v>
+        <v>0.08894046000000001</v>
       </c>
       <c r="N22">
-        <v>2.9952948</v>
+        <v>2.99105954</v>
       </c>
       <c r="O22">
-        <v>0.44929422</v>
+        <v>0.448658931</v>
       </c>
       <c r="P22">
-        <v>2.54600058</v>
+        <v>2.542400609</v>
       </c>
       <c r="Q22">
-        <v>4.92600058</v>
+        <v>4.922400609</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1036047110396125</v>
+        <v>0.1042458960113425</v>
       </c>
       <c r="T22">
-        <v>0.7957036054415313</v>
+        <v>0.8045297579226133</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>36.36140402242129</v>
+        <v>34.62990859278218</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0913328078489606</v>
+        <v>0.0912308468662312</v>
       </c>
       <c r="C23">
-        <v>7.047750564393477</v>
+        <v>6.983336305695768</v>
       </c>
       <c r="D23">
-        <v>8.815950564393477</v>
+        <v>8.835736305695768</v>
       </c>
       <c r="E23">
-        <v>1.7682</v>
+        <v>1.8524</v>
       </c>
       <c r="F23">
-        <v>1.7682</v>
+        <v>1.8524</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3167,28 +3167,28 @@
         <v>3.08</v>
       </c>
       <c r="M23">
-        <v>0.08894046</v>
+        <v>0.09317572</v>
       </c>
       <c r="N23">
-        <v>2.99105954</v>
+        <v>2.98682428</v>
       </c>
       <c r="O23">
-        <v>0.448658931</v>
+        <v>0.448023642</v>
       </c>
       <c r="P23">
-        <v>2.542400609</v>
+        <v>2.538800638</v>
       </c>
       <c r="Q23">
-        <v>4.922400609</v>
+        <v>4.918800638</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1042458960113425</v>
+        <v>0.1049035216233733</v>
       </c>
       <c r="T23">
-        <v>0.8045297579226132</v>
+        <v>0.8135822220057741</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>34.62990859278219</v>
+        <v>33.05582183856481</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0912308468662312</v>
+        <v>0.09112888588350176</v>
       </c>
       <c r="C24">
-        <v>6.983336305695768</v>
+        <v>6.919011057508161</v>
       </c>
       <c r="D24">
-        <v>8.835736305695768</v>
+        <v>8.855611057508161</v>
       </c>
       <c r="E24">
-        <v>1.8524</v>
+        <v>1.9366</v>
       </c>
       <c r="F24">
-        <v>1.8524</v>
+        <v>1.9366</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3249,28 +3249,28 @@
         <v>3.08</v>
       </c>
       <c r="M24">
-        <v>0.09317572</v>
+        <v>0.09741097999999999</v>
       </c>
       <c r="N24">
-        <v>2.98682428</v>
+        <v>2.98258902</v>
       </c>
       <c r="O24">
-        <v>0.448023642</v>
+        <v>0.447388353</v>
       </c>
       <c r="P24">
-        <v>2.538800638</v>
+        <v>2.535200667</v>
       </c>
       <c r="Q24">
-        <v>4.918800638</v>
+        <v>4.915200667000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1049035216233733</v>
+        <v>0.1055782284201322</v>
       </c>
       <c r="T24">
-        <v>0.8135822220057741</v>
+        <v>0.8228698150261599</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>33.05582183856481</v>
+        <v>31.61861219340982</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09112888588350176</v>
+        <v>0.09102692490077234</v>
       </c>
       <c r="C25">
-        <v>6.919011057508161</v>
+        <v>6.854775421834814</v>
       </c>
       <c r="D25">
-        <v>8.855611057508161</v>
+        <v>8.875575421834814</v>
       </c>
       <c r="E25">
-        <v>1.9366</v>
+        <v>2.0208</v>
       </c>
       <c r="F25">
-        <v>1.9366</v>
+        <v>2.0208</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3331,28 +3331,28 @@
         <v>3.08</v>
       </c>
       <c r="M25">
-        <v>0.09741097999999999</v>
+        <v>0.10164624</v>
       </c>
       <c r="N25">
-        <v>2.98258902</v>
+        <v>2.97835376</v>
       </c>
       <c r="O25">
-        <v>0.447388353</v>
+        <v>0.446753064</v>
       </c>
       <c r="P25">
-        <v>2.535200667</v>
+        <v>2.531600696</v>
       </c>
       <c r="Q25">
-        <v>4.915200667000001</v>
+        <v>4.911600696</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1055782284201322</v>
+        <v>0.106270690658911</v>
       </c>
       <c r="T25">
-        <v>0.8228698150261599</v>
+        <v>0.8324018183891874</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>31.61861219340982</v>
+        <v>30.30117001868441</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09102692490077234</v>
+        <v>0.09092496391804293</v>
       </c>
       <c r="C26">
-        <v>6.854775421834814</v>
+        <v>6.790630006120862</v>
       </c>
       <c r="D26">
-        <v>8.875575421834814</v>
+        <v>8.895630006120863</v>
       </c>
       <c r="E26">
-        <v>2.0208</v>
+        <v>2.105</v>
       </c>
       <c r="F26">
-        <v>2.0208</v>
+        <v>2.105</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3413,28 +3413,28 @@
         <v>3.08</v>
       </c>
       <c r="M26">
-        <v>0.10164624</v>
+        <v>0.1058815</v>
       </c>
       <c r="N26">
-        <v>2.97835376</v>
+        <v>2.9741185</v>
       </c>
       <c r="O26">
-        <v>0.446753064</v>
+        <v>0.446117775</v>
       </c>
       <c r="P26">
-        <v>2.531600696</v>
+        <v>2.528000725</v>
       </c>
       <c r="Q26">
-        <v>4.911600696</v>
+        <v>4.908000725</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.106270690658911</v>
+        <v>0.1069816185573906</v>
       </c>
       <c r="T26">
-        <v>0.8324018183891874</v>
+        <v>0.8421880085085623</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>30.30117001868441</v>
+        <v>29.08912321793704</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09092496391804293</v>
+        <v>0.09082300293531351</v>
       </c>
       <c r="C27">
-        <v>6.790630006120862</v>
+        <v>6.726575423314037</v>
       </c>
       <c r="D27">
-        <v>8.895630006120863</v>
+        <v>8.915775423314036</v>
       </c>
       <c r="E27">
-        <v>2.105</v>
+        <v>2.1892</v>
       </c>
       <c r="F27">
-        <v>2.105</v>
+        <v>2.1892</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3495,28 +3495,28 @@
         <v>3.08</v>
       </c>
       <c r="M27">
-        <v>0.1058815</v>
+        <v>0.11011676</v>
       </c>
       <c r="N27">
-        <v>2.9741185</v>
+        <v>2.96988324</v>
       </c>
       <c r="O27">
-        <v>0.446117775</v>
+        <v>0.445482486</v>
       </c>
       <c r="P27">
-        <v>2.528000725</v>
+        <v>2.524400754</v>
       </c>
       <c r="Q27">
-        <v>4.908000725</v>
+        <v>4.904400754</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1069816185573906</v>
+        <v>0.1077117607233966</v>
       </c>
       <c r="T27">
-        <v>0.8421880085085623</v>
+        <v>0.8522386902527853</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>29.08912321793704</v>
+        <v>27.97031078647792</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09082300293531351</v>
+        <v>0.0907210419525841</v>
       </c>
       <c r="C28">
-        <v>6.726575423314037</v>
+        <v>6.662612291927086</v>
       </c>
       <c r="D28">
-        <v>8.915775423314036</v>
+        <v>8.936012291927087</v>
       </c>
       <c r="E28">
-        <v>2.1892</v>
+        <v>2.2734</v>
       </c>
       <c r="F28">
-        <v>2.1892</v>
+        <v>2.2734</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3577,28 +3577,28 @@
         <v>3.08</v>
       </c>
       <c r="M28">
-        <v>0.11011676</v>
+        <v>0.11435202</v>
       </c>
       <c r="N28">
-        <v>2.96988324</v>
+        <v>2.96564798</v>
       </c>
       <c r="O28">
-        <v>0.445482486</v>
+        <v>0.444847197</v>
       </c>
       <c r="P28">
-        <v>2.524400754</v>
+        <v>2.520800783</v>
       </c>
       <c r="Q28">
-        <v>4.904400754</v>
+        <v>4.900800782999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1077117607233966</v>
+        <v>0.1084619067843618</v>
       </c>
       <c r="T28">
-        <v>0.8522386902527853</v>
+        <v>0.8625647331406857</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>27.97031078647792</v>
+        <v>26.9343733499417</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0907210419525841</v>
+        <v>0.09061908096985469</v>
       </c>
       <c r="C29">
-        <v>6.662612291927086</v>
+        <v>6.598741236101107</v>
       </c>
       <c r="D29">
-        <v>8.936012291927087</v>
+        <v>8.956341236101107</v>
       </c>
       <c r="E29">
-        <v>2.2734</v>
+        <v>2.3576</v>
       </c>
       <c r="F29">
-        <v>2.2734</v>
+        <v>2.3576</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3659,28 +3659,28 @@
         <v>3.08</v>
       </c>
       <c r="M29">
-        <v>0.11435202</v>
+        <v>0.11858728</v>
       </c>
       <c r="N29">
-        <v>2.96564798</v>
+        <v>2.96141272</v>
       </c>
       <c r="O29">
-        <v>0.444847197</v>
+        <v>0.444211908</v>
       </c>
       <c r="P29">
-        <v>2.520800783</v>
+        <v>2.517200812</v>
       </c>
       <c r="Q29">
-        <v>4.900800782999999</v>
+        <v>4.897200811999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1084619067843618</v>
+        <v>0.1092328902359093</v>
       </c>
       <c r="T29">
-        <v>0.8625647331406857</v>
+        <v>0.8731776105532498</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>26.9343733499417</v>
+        <v>25.97243144458664</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09061908096985469</v>
+        <v>0.09051711998712526</v>
       </c>
       <c r="C30">
-        <v>6.598741236101107</v>
+        <v>6.534962885669678</v>
       </c>
       <c r="D30">
-        <v>8.956341236101107</v>
+        <v>8.976762885669679</v>
       </c>
       <c r="E30">
-        <v>2.3576</v>
+        <v>2.4418</v>
       </c>
       <c r="F30">
-        <v>2.3576</v>
+        <v>2.4418</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3741,28 +3741,28 @@
         <v>3.08</v>
       </c>
       <c r="M30">
-        <v>0.11858728</v>
+        <v>0.12282254</v>
       </c>
       <c r="N30">
-        <v>2.96141272</v>
+        <v>2.95717746</v>
       </c>
       <c r="O30">
-        <v>0.444211908</v>
+        <v>0.443576619</v>
       </c>
       <c r="P30">
-        <v>2.517200812</v>
+        <v>2.513600841</v>
       </c>
       <c r="Q30">
-        <v>4.897200811999999</v>
+        <v>4.893600841</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1092328902359093</v>
+        <v>0.1100255915311623</v>
       </c>
       <c r="T30">
-        <v>0.8731776105532498</v>
+        <v>0.8840894422591257</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>25.97243144458664</v>
+        <v>25.07683036029054</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09051711998712525</v>
+        <v>0.09041515900439584</v>
       </c>
       <c r="C31">
-        <v>6.534962885669683</v>
+        <v>6.471277876223938</v>
       </c>
       <c r="D31">
-        <v>8.976762885669682</v>
+        <v>8.997277876223938</v>
       </c>
       <c r="E31">
-        <v>2.4418</v>
+        <v>2.526</v>
       </c>
       <c r="F31">
-        <v>2.4418</v>
+        <v>2.526</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3823,28 +3823,28 @@
         <v>3.08</v>
       </c>
       <c r="M31">
-        <v>0.12282254</v>
+        <v>0.1270578</v>
       </c>
       <c r="N31">
-        <v>2.95717746</v>
+        <v>2.9529422</v>
       </c>
       <c r="O31">
-        <v>0.443576619</v>
+        <v>0.44294133</v>
       </c>
       <c r="P31">
-        <v>2.513600841</v>
+        <v>2.51000087</v>
       </c>
       <c r="Q31">
-        <v>4.893600841</v>
+        <v>4.89000087</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1100255915311623</v>
+        <v>0.1108409414348512</v>
       </c>
       <c r="T31">
-        <v>0.8840894422591257</v>
+        <v>0.8953130405851694</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>25.07683036029055</v>
+        <v>24.24093601494754</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09041515900439584</v>
+        <v>0.09031319802166642</v>
       </c>
       <c r="C32">
-        <v>6.471277876223938</v>
+        <v>6.407686849178499</v>
       </c>
       <c r="D32">
-        <v>8.997277876223938</v>
+        <v>9.017886849178499</v>
       </c>
       <c r="E32">
-        <v>2.526</v>
+        <v>2.6102</v>
       </c>
       <c r="F32">
-        <v>2.526</v>
+        <v>2.6102</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3905,28 +3905,28 @@
         <v>3.08</v>
       </c>
       <c r="M32">
-        <v>0.1270578</v>
+        <v>0.13129306</v>
       </c>
       <c r="N32">
-        <v>2.9529422</v>
+        <v>2.94870694</v>
       </c>
       <c r="O32">
-        <v>0.44294133</v>
+        <v>0.442306041</v>
       </c>
       <c r="P32">
-        <v>2.51000087</v>
+        <v>2.506400899</v>
       </c>
       <c r="Q32">
-        <v>4.89000087</v>
+        <v>4.886400899</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1108409414348512</v>
+        <v>0.1116799246690818</v>
       </c>
       <c r="T32">
-        <v>0.8953130405851694</v>
+        <v>0.906861960601823</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>24.24093601494754</v>
+        <v>23.458970337046</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09031319802166642</v>
+        <v>0.09021123703893701</v>
       </c>
       <c r="C33">
-        <v>6.407686849178499</v>
+        <v>6.344190451838308</v>
       </c>
       <c r="D33">
-        <v>9.017886849178499</v>
+        <v>9.038590451838308</v>
       </c>
       <c r="E33">
-        <v>2.6102</v>
+        <v>2.6944</v>
       </c>
       <c r="F33">
-        <v>2.6102</v>
+        <v>2.6944</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3987,28 +3987,28 @@
         <v>3.08</v>
       </c>
       <c r="M33">
-        <v>0.13129306</v>
+        <v>0.13552832</v>
       </c>
       <c r="N33">
-        <v>2.94870694</v>
+        <v>2.94447168</v>
       </c>
       <c r="O33">
-        <v>0.442306041</v>
+        <v>0.441670752</v>
       </c>
       <c r="P33">
-        <v>2.506400899</v>
+        <v>2.502800928</v>
       </c>
       <c r="Q33">
-        <v>4.886400899</v>
+        <v>4.882800928</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1116799246690818</v>
+        <v>0.1125435838807897</v>
       </c>
       <c r="T33">
-        <v>0.906861960601823</v>
+        <v>0.9187505547366135</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>23.458970337046</v>
+        <v>22.72587751401331</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09021123703893701</v>
+        <v>0.0901092760562076</v>
       </c>
       <c r="C34">
-        <v>6.344190451838308</v>
+        <v>6.280789337466435</v>
       </c>
       <c r="D34">
-        <v>9.038590451838308</v>
+        <v>9.059389337466435</v>
       </c>
       <c r="E34">
-        <v>2.6944</v>
+        <v>2.7786</v>
       </c>
       <c r="F34">
-        <v>2.6944</v>
+        <v>2.7786</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4069,28 +4069,28 @@
         <v>3.08</v>
       </c>
       <c r="M34">
-        <v>0.13552832</v>
+        <v>0.13976358</v>
       </c>
       <c r="N34">
-        <v>2.94447168</v>
+        <v>2.94023642</v>
       </c>
       <c r="O34">
-        <v>0.441670752</v>
+        <v>0.441035463</v>
       </c>
       <c r="P34">
-        <v>2.502800928</v>
+        <v>2.499200957</v>
       </c>
       <c r="Q34">
-        <v>4.882800928</v>
+        <v>4.879200957</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1125435838807897</v>
+        <v>0.113433023964489</v>
       </c>
       <c r="T34">
-        <v>0.9187505547366135</v>
+        <v>0.9309940322784128</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>22.72587751401331</v>
+        <v>22.03721455904321</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0901092760562076</v>
+        <v>0.09000731507347816</v>
       </c>
       <c r="C35">
-        <v>6.280789337466435</v>
+        <v>6.217484165352754</v>
       </c>
       <c r="D35">
-        <v>9.059389337466435</v>
+        <v>9.080284165352754</v>
       </c>
       <c r="E35">
-        <v>2.7786</v>
+        <v>2.8628</v>
       </c>
       <c r="F35">
-        <v>2.7786</v>
+        <v>2.8628</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4151,28 +4151,28 @@
         <v>3.08</v>
       </c>
       <c r="M35">
-        <v>0.13976358</v>
+        <v>0.14399884</v>
       </c>
       <c r="N35">
-        <v>2.94023642</v>
+        <v>2.93600116</v>
       </c>
       <c r="O35">
-        <v>0.441035463</v>
+        <v>0.440400174</v>
       </c>
       <c r="P35">
-        <v>2.499200957</v>
+        <v>2.495600986</v>
       </c>
       <c r="Q35">
-        <v>4.879200957</v>
+        <v>4.875600986</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.113433023964489</v>
+        <v>0.1143494167779972</v>
       </c>
       <c r="T35">
-        <v>0.9309940322784128</v>
+        <v>0.9436085242911757</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>22.03721455904321</v>
+        <v>21.38906118965959</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09000731507347816</v>
+        <v>0.08990535409074875</v>
       </c>
       <c r="C36">
-        <v>6.217484165352754</v>
+        <v>6.154275600883614</v>
       </c>
       <c r="D36">
-        <v>9.080284165352754</v>
+        <v>9.101275600883614</v>
       </c>
       <c r="E36">
-        <v>2.8628</v>
+        <v>2.947</v>
       </c>
       <c r="F36">
-        <v>2.8628</v>
+        <v>2.947</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4233,28 +4233,28 @@
         <v>3.08</v>
       </c>
       <c r="M36">
-        <v>0.14399884</v>
+        <v>0.1482341</v>
       </c>
       <c r="N36">
-        <v>2.93600116</v>
+        <v>2.9317659</v>
       </c>
       <c r="O36">
-        <v>0.440400174</v>
+        <v>0.439764885</v>
       </c>
       <c r="P36">
-        <v>2.495600986</v>
+        <v>2.492001015</v>
       </c>
       <c r="Q36">
-        <v>4.875600986</v>
+        <v>4.872001015</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1143494167779972</v>
+        <v>0.1152940062934596</v>
       </c>
       <c r="T36">
-        <v>0.9436085242911757</v>
+        <v>0.9566111545197158</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>21.38906118965959</v>
+        <v>20.77794515566931</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08990535409074875</v>
+        <v>0.08980339310801932</v>
       </c>
       <c r="C37">
-        <v>6.154275600883614</v>
+        <v>6.091164315612486</v>
       </c>
       <c r="D37">
-        <v>9.101275600883614</v>
+        <v>9.122364315612487</v>
       </c>
       <c r="E37">
-        <v>2.947</v>
+        <v>3.0312</v>
       </c>
       <c r="F37">
-        <v>2.947</v>
+        <v>3.0312</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4315,28 +4315,28 @@
         <v>3.08</v>
       </c>
       <c r="M37">
-        <v>0.1482341</v>
+        <v>0.15246936</v>
       </c>
       <c r="N37">
-        <v>2.9317659</v>
+        <v>2.92753064</v>
       </c>
       <c r="O37">
-        <v>0.439764885</v>
+        <v>0.439129596</v>
       </c>
       <c r="P37">
-        <v>2.492001015</v>
+        <v>2.488401044</v>
       </c>
       <c r="Q37">
-        <v>4.872001015</v>
+        <v>4.868401044000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1152940062934596</v>
+        <v>0.1162681142312802</v>
       </c>
       <c r="T37">
-        <v>0.9566111545197158</v>
+        <v>0.9700201169428979</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>20.77794515566931</v>
+        <v>20.20078001245627</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08980339310801934</v>
+        <v>0.08970143212528991</v>
       </c>
       <c r="C38">
-        <v>6.091164315612483</v>
+        <v>6.028150987331557</v>
       </c>
       <c r="D38">
-        <v>9.122364315612483</v>
+        <v>9.143550987331556</v>
       </c>
       <c r="E38">
-        <v>3.0312</v>
+        <v>3.1154</v>
       </c>
       <c r="F38">
-        <v>3.0312</v>
+        <v>3.1154</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4397,28 +4397,28 @@
         <v>3.08</v>
       </c>
       <c r="M38">
-        <v>0.15246936</v>
+        <v>0.15670462</v>
       </c>
       <c r="N38">
-        <v>2.92753064</v>
+        <v>2.92329538</v>
       </c>
       <c r="O38">
-        <v>0.439129596</v>
+        <v>0.438494307</v>
       </c>
       <c r="P38">
-        <v>2.488401044</v>
+        <v>2.484801073</v>
       </c>
       <c r="Q38">
-        <v>4.868401044000001</v>
+        <v>4.864801073</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1162681142312802</v>
+        <v>0.1172731462306189</v>
       </c>
       <c r="T38">
-        <v>0.9700201169428977</v>
+        <v>0.9838547607128475</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>20.20078001245628</v>
+        <v>19.65481298509259</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08970143212528991</v>
+        <v>0.08959947114256049</v>
       </c>
       <c r="C39">
-        <v>6.028150987331557</v>
+        <v>5.965236300144362</v>
       </c>
       <c r="D39">
-        <v>9.143550987331556</v>
+        <v>9.164836300144362</v>
       </c>
       <c r="E39">
-        <v>3.1154</v>
+        <v>3.1996</v>
       </c>
       <c r="F39">
-        <v>3.1154</v>
+        <v>3.1996</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4479,28 +4479,28 @@
         <v>3.08</v>
       </c>
       <c r="M39">
-        <v>0.15670462</v>
+        <v>0.16093988</v>
       </c>
       <c r="N39">
-        <v>2.92329538</v>
+        <v>2.91906012</v>
       </c>
       <c r="O39">
-        <v>0.438494307</v>
+        <v>0.437859018</v>
       </c>
       <c r="P39">
-        <v>2.484801073</v>
+        <v>2.481201102</v>
       </c>
       <c r="Q39">
-        <v>4.864801073</v>
+        <v>4.861201102</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1172731462306189</v>
+        <v>0.1183105986170331</v>
       </c>
       <c r="T39">
-        <v>0.9838547607128475</v>
+        <v>0.9981356833140859</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>19.65481298509259</v>
+        <v>19.13758106443226</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08959947114256049</v>
+        <v>0.08949751015983108</v>
       </c>
       <c r="C40">
-        <v>5.965236300144362</v>
+        <v>5.902420944539409</v>
       </c>
       <c r="D40">
-        <v>9.164836300144362</v>
+        <v>9.186220944539409</v>
       </c>
       <c r="E40">
-        <v>3.1996</v>
+        <v>3.2838</v>
       </c>
       <c r="F40">
-        <v>3.1996</v>
+        <v>3.2838</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4561,28 +4561,28 @@
         <v>3.08</v>
       </c>
       <c r="M40">
-        <v>0.16093988</v>
+        <v>0.16517514</v>
       </c>
       <c r="N40">
-        <v>2.91906012</v>
+        <v>2.91482486</v>
       </c>
       <c r="O40">
-        <v>0.437859018</v>
+        <v>0.437223729</v>
       </c>
       <c r="P40">
-        <v>2.481201102</v>
+        <v>2.477601131</v>
       </c>
       <c r="Q40">
-        <v>4.861201102</v>
+        <v>4.857601131</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1183105986170331</v>
+        <v>0.1193820658357887</v>
       </c>
       <c r="T40">
-        <v>0.9981356833140859</v>
+        <v>1.012884832885857</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>19.13758106443226</v>
+        <v>18.64687385765194</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08949751015983108</v>
+        <v>0.08939554917710169</v>
       </c>
       <c r="C41">
-        <v>5.902420944539409</v>
+        <v>5.839705617464841</v>
       </c>
       <c r="D41">
-        <v>9.186220944539409</v>
+        <v>9.207705617464841</v>
       </c>
       <c r="E41">
-        <v>3.2838</v>
+        <v>3.368</v>
       </c>
       <c r="F41">
-        <v>3.2838</v>
+        <v>3.368</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4643,28 +4643,28 @@
         <v>3.08</v>
       </c>
       <c r="M41">
-        <v>0.16517514</v>
+        <v>0.1694104</v>
       </c>
       <c r="N41">
-        <v>2.91482486</v>
+        <v>2.9105896</v>
       </c>
       <c r="O41">
-        <v>0.437223729</v>
+        <v>0.43658844</v>
       </c>
       <c r="P41">
-        <v>2.477601131</v>
+        <v>2.47400116</v>
       </c>
       <c r="Q41">
-        <v>4.857601131</v>
+        <v>4.85400116</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1193820658357887</v>
+        <v>0.1204892486285028</v>
       </c>
       <c r="T41">
-        <v>1.012884832885857</v>
+        <v>1.028125620776687</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>18.64687385765194</v>
+        <v>18.18070201121064</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08939554917710169</v>
+        <v>0.08929358819437225</v>
       </c>
       <c r="C42">
-        <v>5.839705617464841</v>
+        <v>5.777091022404172</v>
       </c>
       <c r="D42">
-        <v>9.207705617464841</v>
+        <v>9.229291022404173</v>
       </c>
       <c r="E42">
-        <v>3.368</v>
+        <v>3.4522</v>
       </c>
       <c r="F42">
-        <v>3.368</v>
+        <v>3.4522</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4725,28 +4725,28 @@
         <v>3.08</v>
       </c>
       <c r="M42">
-        <v>0.1694104</v>
+        <v>0.17364566</v>
       </c>
       <c r="N42">
-        <v>2.9105896</v>
+        <v>2.90635434</v>
       </c>
       <c r="O42">
-        <v>0.43658844</v>
+        <v>0.435953151</v>
       </c>
       <c r="P42">
-        <v>2.47400116</v>
+        <v>2.470401189</v>
       </c>
       <c r="Q42">
-        <v>4.85400116</v>
+        <v>4.850401188999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1204892486285028</v>
+        <v>0.1216339630413089</v>
       </c>
       <c r="T42">
-        <v>1.028125620776687</v>
+        <v>1.043883045545172</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>18.18070201121064</v>
+        <v>17.73727025483965</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08929358819437225</v>
+        <v>0.08919162721164282</v>
       </c>
       <c r="C43">
-        <v>5.777091022404172</v>
+        <v>5.714577869453034</v>
       </c>
       <c r="D43">
-        <v>9.229291022404173</v>
+        <v>9.250977869453035</v>
       </c>
       <c r="E43">
-        <v>3.4522</v>
+        <v>3.5364</v>
       </c>
       <c r="F43">
-        <v>3.4522</v>
+        <v>3.5364</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4807,28 +4807,28 @@
         <v>3.08</v>
       </c>
       <c r="M43">
-        <v>0.17364566</v>
+        <v>0.17788092</v>
       </c>
       <c r="N43">
-        <v>2.90635434</v>
+        <v>2.90211908</v>
       </c>
       <c r="O43">
-        <v>0.435953151</v>
+        <v>0.4353178619999999</v>
       </c>
       <c r="P43">
-        <v>2.470401189</v>
+        <v>2.466801218</v>
       </c>
       <c r="Q43">
-        <v>4.850401188999999</v>
+        <v>4.846801218</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1216339630413089</v>
+        <v>0.1228181503649014</v>
       </c>
       <c r="T43">
-        <v>1.043883045545172</v>
+        <v>1.060183829788432</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>17.73727025483965</v>
+        <v>17.31495429639109</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08919162721164284</v>
+        <v>0.08908966622891343</v>
       </c>
       <c r="C44">
-        <v>5.714577869453032</v>
+        <v>5.652166875397077</v>
       </c>
       <c r="D44">
-        <v>9.250977869453033</v>
+        <v>9.272766875397076</v>
       </c>
       <c r="E44">
-        <v>3.5364</v>
+        <v>3.6206</v>
       </c>
       <c r="F44">
-        <v>3.5364</v>
+        <v>3.6206</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4889,28 +4889,28 @@
         <v>3.08</v>
       </c>
       <c r="M44">
-        <v>0.17788092</v>
+        <v>0.18211618</v>
       </c>
       <c r="N44">
-        <v>2.90211908</v>
+        <v>2.89788382</v>
       </c>
       <c r="O44">
-        <v>0.4353178620000001</v>
+        <v>0.434682573</v>
       </c>
       <c r="P44">
-        <v>2.466801218</v>
+        <v>2.463201247</v>
       </c>
       <c r="Q44">
-        <v>4.846801218</v>
+        <v>4.843201247</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1228181503649014</v>
+        <v>0.1240438881209007</v>
       </c>
       <c r="T44">
-        <v>1.060183829788432</v>
+        <v>1.077056571373561</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>17.31495429639109</v>
+        <v>16.91228094066107</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08908966622891343</v>
+        <v>0.08898770524618399</v>
       </c>
       <c r="C45">
-        <v>5.652166875397077</v>
+        <v>5.589858763790938</v>
       </c>
       <c r="D45">
-        <v>9.272766875397076</v>
+        <v>9.294658763790938</v>
       </c>
       <c r="E45">
-        <v>3.6206</v>
+        <v>3.7048</v>
       </c>
       <c r="F45">
-        <v>3.6206</v>
+        <v>3.7048</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4971,28 +4971,28 @@
         <v>3.08</v>
       </c>
       <c r="M45">
-        <v>0.18211618</v>
+        <v>0.18635144</v>
       </c>
       <c r="N45">
-        <v>2.89788382</v>
+        <v>2.89364856</v>
       </c>
       <c r="O45">
-        <v>0.434682573</v>
+        <v>0.434047284</v>
       </c>
       <c r="P45">
-        <v>2.463201247</v>
+        <v>2.459601276</v>
       </c>
       <c r="Q45">
-        <v>4.843201247</v>
+        <v>4.839601276</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1240438881209007</v>
+        <v>0.1253134022253286</v>
       </c>
       <c r="T45">
-        <v>1.077056571373561</v>
+        <v>1.094531910872445</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>16.91228094066107</v>
+        <v>16.52791091928241</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08898770524618399</v>
+        <v>0.08888574426345459</v>
       </c>
       <c r="C46">
-        <v>5.589858763790938</v>
+        <v>5.527654265038304</v>
       </c>
       <c r="D46">
-        <v>9.294658763790938</v>
+        <v>9.316654265038304</v>
       </c>
       <c r="E46">
-        <v>3.7048</v>
+        <v>3.789</v>
       </c>
       <c r="F46">
-        <v>3.7048</v>
+        <v>3.789</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5053,28 +5053,28 @@
         <v>3.08</v>
       </c>
       <c r="M46">
-        <v>0.18635144</v>
+        <v>0.1905867</v>
       </c>
       <c r="N46">
-        <v>2.89364856</v>
+        <v>2.8894133</v>
       </c>
       <c r="O46">
-        <v>0.434047284</v>
+        <v>0.433411995</v>
       </c>
       <c r="P46">
-        <v>2.459601276</v>
+        <v>2.456001305</v>
       </c>
       <c r="Q46">
-        <v>4.839601276</v>
+        <v>4.836001305</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1253134022253286</v>
+        <v>0.1266290804790083</v>
       </c>
       <c r="T46">
-        <v>1.094531910872445</v>
+        <v>1.112642717262198</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>16.52791091928241</v>
+        <v>16.16062400996502</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08888574426345459</v>
+        <v>0.08878378328072517</v>
       </c>
       <c r="C47">
-        <v>5.527654265038304</v>
+        <v>5.465554116473195</v>
       </c>
       <c r="D47">
-        <v>9.316654265038304</v>
+        <v>9.338754116473195</v>
       </c>
       <c r="E47">
-        <v>3.789</v>
+        <v>3.8732</v>
       </c>
       <c r="F47">
-        <v>3.789</v>
+        <v>3.8732</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5135,28 +5135,28 @@
         <v>3.08</v>
       </c>
       <c r="M47">
-        <v>0.1905867</v>
+        <v>0.19482196</v>
       </c>
       <c r="N47">
-        <v>2.8894133</v>
+        <v>2.88517804</v>
       </c>
       <c r="O47">
-        <v>0.433411995</v>
+        <v>0.432776706</v>
       </c>
       <c r="P47">
-        <v>2.456001305</v>
+        <v>2.452401334</v>
       </c>
       <c r="Q47">
-        <v>4.836001305</v>
+        <v>4.832401334</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1266290804790083</v>
+        <v>0.1279934875568985</v>
       </c>
       <c r="T47">
-        <v>1.112642717262198</v>
+        <v>1.131424294258978</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>16.16062400996502</v>
+        <v>15.80930609670491</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08878378328072517</v>
+        <v>0.08868182229799576</v>
       </c>
       <c r="C48">
-        <v>5.465554116473195</v>
+        <v>5.403559062442303</v>
       </c>
       <c r="D48">
-        <v>9.338754116473195</v>
+        <v>9.360959062442303</v>
       </c>
       <c r="E48">
-        <v>3.8732</v>
+        <v>3.9574</v>
       </c>
       <c r="F48">
-        <v>3.8732</v>
+        <v>3.9574</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5217,28 +5217,28 @@
         <v>3.08</v>
       </c>
       <c r="M48">
-        <v>0.19482196</v>
+        <v>0.19905722</v>
       </c>
       <c r="N48">
-        <v>2.88517804</v>
+        <v>2.88094278</v>
       </c>
       <c r="O48">
-        <v>0.432776706</v>
+        <v>0.432141417</v>
       </c>
       <c r="P48">
-        <v>2.452401334</v>
+        <v>2.448801363</v>
       </c>
       <c r="Q48">
-        <v>4.832401334</v>
+        <v>4.828801363</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1279934875568985</v>
+        <v>0.1294093816943316</v>
       </c>
       <c r="T48">
-        <v>1.131424294258978</v>
+        <v>1.150914610010354</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>15.80930609670491</v>
+        <v>15.4729378818814</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08868182229799576</v>
+        <v>0.08857986131526632</v>
       </c>
       <c r="C49">
-        <v>5.403559062442303</v>
+        <v>5.341669854388608</v>
       </c>
       <c r="D49">
-        <v>9.360959062442303</v>
+        <v>9.383269854388608</v>
       </c>
       <c r="E49">
-        <v>3.9574</v>
+        <v>4.0416</v>
       </c>
       <c r="F49">
-        <v>3.9574</v>
+        <v>4.0416</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5299,28 +5299,28 @@
         <v>3.08</v>
       </c>
       <c r="M49">
-        <v>0.19905722</v>
+        <v>0.20329248</v>
       </c>
       <c r="N49">
-        <v>2.88094278</v>
+        <v>2.87670752</v>
       </c>
       <c r="O49">
-        <v>0.432141417</v>
+        <v>0.431506128</v>
       </c>
       <c r="P49">
-        <v>2.448801363</v>
+        <v>2.445201392</v>
       </c>
       <c r="Q49">
-        <v>4.828801363</v>
+        <v>4.825201392</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1294093816943316</v>
+        <v>0.1308797332985891</v>
       </c>
       <c r="T49">
-        <v>1.150914610010354</v>
+        <v>1.171154553290628</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>15.4729378818814</v>
+        <v>15.15058500934221</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08857986131526632</v>
+        <v>0.0884779003325369</v>
       </c>
       <c r="C50">
-        <v>5.341669854388608</v>
+        <v>5.279887250936101</v>
       </c>
       <c r="D50">
-        <v>9.383269854388608</v>
+        <v>9.405687250936101</v>
       </c>
       <c r="E50">
-        <v>4.0416</v>
+        <v>4.1258</v>
       </c>
       <c r="F50">
-        <v>4.0416</v>
+        <v>4.1258</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5381,28 +5381,28 @@
         <v>3.08</v>
       </c>
       <c r="M50">
-        <v>0.20329248</v>
+        <v>0.20752774</v>
       </c>
       <c r="N50">
-        <v>2.87670752</v>
+        <v>2.87247226</v>
       </c>
       <c r="O50">
-        <v>0.431506128</v>
+        <v>0.4308708389999999</v>
       </c>
       <c r="P50">
-        <v>2.445201392</v>
+        <v>2.441601421</v>
       </c>
       <c r="Q50">
-        <v>4.825201392</v>
+        <v>4.821601421</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1308797332985891</v>
+        <v>0.1324077457500724</v>
       </c>
       <c r="T50">
-        <v>1.171154553290628</v>
+        <v>1.192188219836796</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>15.15058500934221</v>
+        <v>14.84138939690665</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0884779003325369</v>
+        <v>0.08837593934980749</v>
       </c>
       <c r="C51">
-        <v>5.279887250936101</v>
+        <v>5.218212017975802</v>
       </c>
       <c r="D51">
-        <v>9.405687250936101</v>
+        <v>9.428212017975802</v>
       </c>
       <c r="E51">
-        <v>4.1258</v>
+        <v>4.21</v>
       </c>
       <c r="F51">
-        <v>4.1258</v>
+        <v>4.21</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5463,28 +5463,28 @@
         <v>3.08</v>
       </c>
       <c r="M51">
-        <v>0.20752774</v>
+        <v>0.211763</v>
       </c>
       <c r="N51">
-        <v>2.87247226</v>
+        <v>2.868237</v>
       </c>
       <c r="O51">
-        <v>0.4308708389999999</v>
+        <v>0.43023555</v>
       </c>
       <c r="P51">
-        <v>2.441601421</v>
+        <v>2.43800145</v>
       </c>
       <c r="Q51">
-        <v>4.821601421</v>
+        <v>4.818001450000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1324077457500724</v>
+        <v>0.133996878699615</v>
       </c>
       <c r="T51">
-        <v>1.192188219836796</v>
+        <v>1.214063233044811</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>14.84138939690665</v>
+        <v>14.54456160896852</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08837593934980749</v>
+        <v>0.08827397836707808</v>
       </c>
       <c r="C52">
-        <v>5.218212017975802</v>
+        <v>5.156644928752986</v>
       </c>
       <c r="D52">
-        <v>9.428212017975802</v>
+        <v>9.450844928752986</v>
       </c>
       <c r="E52">
-        <v>4.21</v>
+        <v>4.2942</v>
       </c>
       <c r="F52">
-        <v>4.21</v>
+        <v>4.2942</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5545,28 +5545,28 @@
         <v>3.08</v>
       </c>
       <c r="M52">
-        <v>0.211763</v>
+        <v>0.21599826</v>
       </c>
       <c r="N52">
-        <v>2.868237</v>
+        <v>2.86400174</v>
       </c>
       <c r="O52">
-        <v>0.43023555</v>
+        <v>0.429600261</v>
       </c>
       <c r="P52">
-        <v>2.43800145</v>
+        <v>2.434401479</v>
       </c>
       <c r="Q52">
-        <v>4.818001450000001</v>
+        <v>4.814401479</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.133996878699615</v>
+        <v>0.1356508742185267</v>
       </c>
       <c r="T52">
-        <v>1.214063233044811</v>
+        <v>1.236831103934785</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>14.54456160896852</v>
+        <v>14.25937412643972</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08827397836707808</v>
+        <v>0.08817201738434866</v>
       </c>
       <c r="C53">
-        <v>5.156644928752986</v>
+        <v>5.095186763955645</v>
       </c>
       <c r="D53">
-        <v>9.450844928752986</v>
+        <v>9.473586763955645</v>
       </c>
       <c r="E53">
-        <v>4.2942</v>
+        <v>4.3784</v>
       </c>
       <c r="F53">
-        <v>4.2942</v>
+        <v>4.3784</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5627,28 +5627,28 @@
         <v>3.08</v>
       </c>
       <c r="M53">
-        <v>0.21599826</v>
+        <v>0.22023352</v>
       </c>
       <c r="N53">
-        <v>2.86400174</v>
+        <v>2.85976648</v>
       </c>
       <c r="O53">
-        <v>0.429600261</v>
+        <v>0.428964972</v>
       </c>
       <c r="P53">
-        <v>2.434401479</v>
+        <v>2.430801508</v>
       </c>
       <c r="Q53">
-        <v>4.814401479</v>
+        <v>4.810801508</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1356508742185267</v>
+        <v>0.137373786217393</v>
       </c>
       <c r="T53">
-        <v>1.236831103934785</v>
+        <v>1.260547636111842</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>14.25937412643972</v>
+        <v>13.98515539323896</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08817201738434866</v>
+        <v>0.08807005640161925</v>
       </c>
       <c r="C54">
-        <v>5.095186763955645</v>
+        <v>5.03383831180426</v>
       </c>
       <c r="D54">
-        <v>9.473586763955645</v>
+        <v>9.49643831180426</v>
       </c>
       <c r="E54">
-        <v>4.3784</v>
+        <v>4.4626</v>
       </c>
       <c r="F54">
-        <v>4.3784</v>
+        <v>4.4626</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5709,28 +5709,28 @@
         <v>3.08</v>
       </c>
       <c r="M54">
-        <v>0.22023352</v>
+        <v>0.22446878</v>
       </c>
       <c r="N54">
-        <v>2.85976648</v>
+        <v>2.85553122</v>
       </c>
       <c r="O54">
-        <v>0.428964972</v>
+        <v>0.428329683</v>
       </c>
       <c r="P54">
-        <v>2.430801508</v>
+        <v>2.427201537</v>
       </c>
       <c r="Q54">
-        <v>4.810801508</v>
+        <v>4.807201537</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.137373786217393</v>
+        <v>0.1391700136204665</v>
       </c>
       <c r="T54">
-        <v>1.260547636111842</v>
+        <v>1.285273382424092</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>13.98515539323896</v>
+        <v>13.72128453676275</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08807005640161925</v>
+        <v>0.08796809541888982</v>
       </c>
       <c r="C55">
-        <v>5.03383831180426</v>
+        <v>4.972600368142881</v>
       </c>
       <c r="D55">
-        <v>9.49643831180426</v>
+        <v>9.519400368142881</v>
       </c>
       <c r="E55">
-        <v>4.4626</v>
+        <v>4.5468</v>
       </c>
       <c r="F55">
-        <v>4.4626</v>
+        <v>4.5468</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5791,28 +5791,28 @@
         <v>3.08</v>
       </c>
       <c r="M55">
-        <v>0.22446878</v>
+        <v>0.22870404</v>
       </c>
       <c r="N55">
-        <v>2.85553122</v>
+        <v>2.85129596</v>
       </c>
       <c r="O55">
-        <v>0.428329683</v>
+        <v>0.427694394</v>
       </c>
       <c r="P55">
-        <v>2.427201537</v>
+        <v>2.423601566</v>
       </c>
       <c r="Q55">
-        <v>4.807201537</v>
+        <v>4.803601565999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1391700136204665</v>
+        <v>0.1410443378671518</v>
       </c>
       <c r="T55">
-        <v>1.285273382424092</v>
+        <v>1.311074161184702</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>13.72128453676275</v>
+        <v>13.46718667497085</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08796809541888982</v>
+        <v>0.08786613443616041</v>
       </c>
       <c r="C56">
-        <v>4.972600368142881</v>
+        <v>4.911473736531496</v>
       </c>
       <c r="D56">
-        <v>9.519400368142881</v>
+        <v>9.542473736531496</v>
       </c>
       <c r="E56">
-        <v>4.5468</v>
+        <v>4.631</v>
       </c>
       <c r="F56">
-        <v>4.5468</v>
+        <v>4.631</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5873,28 +5873,28 @@
         <v>3.08</v>
       </c>
       <c r="M56">
-        <v>0.22870404</v>
+        <v>0.2329393</v>
       </c>
       <c r="N56">
-        <v>2.85129596</v>
+        <v>2.8470607</v>
       </c>
       <c r="O56">
-        <v>0.427694394</v>
+        <v>0.427059105</v>
       </c>
       <c r="P56">
-        <v>2.423601566</v>
+        <v>2.420001595</v>
       </c>
       <c r="Q56">
-        <v>4.803601565999999</v>
+        <v>4.800001594999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1410443378671518</v>
+        <v>0.1430019654136898</v>
       </c>
       <c r="T56">
-        <v>1.311074161184702</v>
+        <v>1.33802164122356</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>13.46718667497085</v>
+        <v>13.22232873542593</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08786613443616041</v>
+        <v>0.08776417345343099</v>
       </c>
       <c r="C57">
-        <v>4.911473736531496</v>
+        <v>4.850459228339793</v>
       </c>
       <c r="D57">
-        <v>9.542473736531496</v>
+        <v>9.565659228339793</v>
       </c>
       <c r="E57">
-        <v>4.631</v>
+        <v>4.7152</v>
       </c>
       <c r="F57">
-        <v>4.631</v>
+        <v>4.7152</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5955,28 +5955,28 @@
         <v>3.08</v>
       </c>
       <c r="M57">
-        <v>0.2329393</v>
+        <v>0.23717456</v>
       </c>
       <c r="N57">
-        <v>2.8470607</v>
+        <v>2.84282544</v>
       </c>
       <c r="O57">
-        <v>0.427059105</v>
+        <v>0.426423816</v>
       </c>
       <c r="P57">
-        <v>2.420001595</v>
+        <v>2.416401624</v>
       </c>
       <c r="Q57">
-        <v>4.800001594999999</v>
+        <v>4.796401624</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1430019654136898</v>
+        <v>0.145048576030525</v>
       </c>
       <c r="T57">
-        <v>1.33802164122356</v>
+        <v>1.366194006718731</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>13.22232873542593</v>
+        <v>12.98621572229332</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08776417345343099</v>
+        <v>0.08838896247070158</v>
       </c>
       <c r="C58">
-        <v>4.850459228339793</v>
+        <v>4.625928999987053</v>
       </c>
       <c r="D58">
-        <v>9.565659228339793</v>
+        <v>9.425328999987054</v>
       </c>
       <c r="E58">
-        <v>4.7152</v>
+        <v>4.7994</v>
       </c>
       <c r="F58">
-        <v>4.7152</v>
+        <v>4.7994</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6037,45 +6037,45 @@
         <v>3.08</v>
       </c>
       <c r="M58">
-        <v>0.23717456</v>
+        <v>0.24860892</v>
       </c>
       <c r="N58">
-        <v>2.84282544</v>
+        <v>2.83139108</v>
       </c>
       <c r="O58">
-        <v>0.426423816</v>
+        <v>0.424708662</v>
       </c>
       <c r="P58">
-        <v>2.416401624</v>
+        <v>2.406682418</v>
       </c>
       <c r="Q58">
-        <v>4.796401624</v>
+        <v>4.786682418</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.145048576030525</v>
+        <v>0.1471903778388409</v>
       </c>
       <c r="T58">
-        <v>1.366194006718731</v>
+        <v>1.395676714795072</v>
       </c>
       <c r="U58">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V58">
         <v>0.15</v>
       </c>
       <c r="W58">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y58">
-        <v>12.98621572229332</v>
+        <v>12.38893600438793</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08838896247070158</v>
+        <v>0.08829975148797214</v>
       </c>
       <c r="C59">
-        <v>4.625928999987053</v>
+        <v>4.561513653619088</v>
       </c>
       <c r="D59">
-        <v>9.425328999987054</v>
+        <v>9.445113653619089</v>
       </c>
       <c r="E59">
-        <v>4.7994</v>
+        <v>4.8836</v>
       </c>
       <c r="F59">
-        <v>4.7994</v>
+        <v>4.8836</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6119,28 +6119,28 @@
         <v>3.08</v>
       </c>
       <c r="M59">
-        <v>0.24860892</v>
+        <v>0.25297048</v>
       </c>
       <c r="N59">
-        <v>2.83139108</v>
+        <v>2.82702952</v>
       </c>
       <c r="O59">
-        <v>0.424708662</v>
+        <v>0.424054428</v>
       </c>
       <c r="P59">
-        <v>2.406682418</v>
+        <v>2.402975092</v>
       </c>
       <c r="Q59">
-        <v>4.786682418</v>
+        <v>4.782975092</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1471903778388409</v>
+        <v>0.1494341702094575</v>
       </c>
       <c r="T59">
-        <v>1.395676714795072</v>
+        <v>1.426563361351239</v>
       </c>
       <c r="U59">
         <v>0.0518</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>12.38893600438793</v>
+        <v>12.1753336594847</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08829975148797214</v>
+        <v>0.08821054050524274</v>
       </c>
       <c r="C60">
-        <v>4.561513653619089</v>
+        <v>4.497181541672206</v>
       </c>
       <c r="D60">
-        <v>9.445113653619089</v>
+        <v>9.464981541672206</v>
       </c>
       <c r="E60">
-        <v>4.883599999999999</v>
+        <v>4.9678</v>
       </c>
       <c r="F60">
-        <v>4.883599999999999</v>
+        <v>4.9678</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6201,28 +6201,28 @@
         <v>3.08</v>
       </c>
       <c r="M60">
-        <v>0.2529704799999999</v>
+        <v>0.25733204</v>
       </c>
       <c r="N60">
-        <v>2.82702952</v>
+        <v>2.82266796</v>
       </c>
       <c r="O60">
-        <v>0.424054428</v>
+        <v>0.423400194</v>
       </c>
       <c r="P60">
-        <v>2.402975092</v>
+        <v>2.399267766</v>
       </c>
       <c r="Q60">
-        <v>4.782975092</v>
+        <v>4.779267766</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1494341702094575</v>
+        <v>0.1517874158664457</v>
       </c>
       <c r="T60">
-        <v>1.426563361351238</v>
+        <v>1.458956673593071</v>
       </c>
       <c r="U60">
         <v>0.0518</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>12.1753336594847</v>
+        <v>11.9689720720358</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08821054050524274</v>
+        <v>0.08812132952251331</v>
       </c>
       <c r="C61">
-        <v>4.497181541672206</v>
+        <v>4.43293319050685</v>
       </c>
       <c r="D61">
-        <v>9.464981541672206</v>
+        <v>9.484933190506849</v>
       </c>
       <c r="E61">
-        <v>4.9678</v>
+        <v>5.052</v>
       </c>
       <c r="F61">
-        <v>4.9678</v>
+        <v>5.052</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6283,28 +6283,28 @@
         <v>3.08</v>
       </c>
       <c r="M61">
-        <v>0.25733204</v>
+        <v>0.2616936</v>
       </c>
       <c r="N61">
-        <v>2.82266796</v>
+        <v>2.8183064</v>
       </c>
       <c r="O61">
-        <v>0.423400194</v>
+        <v>0.42274596</v>
       </c>
       <c r="P61">
-        <v>2.399267766</v>
+        <v>2.39556044</v>
       </c>
       <c r="Q61">
-        <v>4.779267766</v>
+        <v>4.77556044</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1517874158664457</v>
+        <v>0.1542583238062833</v>
       </c>
       <c r="T61">
-        <v>1.458956673593071</v>
+        <v>1.492969651446997</v>
       </c>
       <c r="U61">
         <v>0.0518</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>11.9689720720358</v>
+        <v>11.76948920416854</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08812132952251331</v>
+        <v>0.0880321185397839</v>
       </c>
       <c r="C62">
-        <v>4.43293319050685</v>
+        <v>4.368769130930979</v>
       </c>
       <c r="D62">
-        <v>9.484933190506849</v>
+        <v>9.504969130930979</v>
       </c>
       <c r="E62">
-        <v>5.052</v>
+        <v>5.1362</v>
       </c>
       <c r="F62">
-        <v>5.052</v>
+        <v>5.1362</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6365,28 +6365,28 @@
         <v>3.08</v>
       </c>
       <c r="M62">
-        <v>0.2616936</v>
+        <v>0.26605516</v>
       </c>
       <c r="N62">
-        <v>2.8183064</v>
+        <v>2.81394484</v>
       </c>
       <c r="O62">
-        <v>0.42274596</v>
+        <v>0.422091726</v>
       </c>
       <c r="P62">
-        <v>2.39556044</v>
+        <v>2.391853114</v>
       </c>
       <c r="Q62">
-        <v>4.77556044</v>
+        <v>4.771853114</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1542583238062833</v>
+        <v>0.1568559449738049</v>
       </c>
       <c r="T62">
-        <v>1.492969651446997</v>
+        <v>1.528726884575482</v>
       </c>
       <c r="U62">
         <v>0.0518</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>11.76948920416854</v>
+        <v>11.57654675819856</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0880321185397839</v>
+        <v>0.08794290755705447</v>
       </c>
       <c r="C63">
-        <v>4.368769130930979</v>
+        <v>4.304689898247171</v>
       </c>
       <c r="D63">
-        <v>9.504969130930979</v>
+        <v>9.52508989824717</v>
       </c>
       <c r="E63">
-        <v>5.1362</v>
+        <v>5.2204</v>
       </c>
       <c r="F63">
-        <v>5.1362</v>
+        <v>5.2204</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6447,28 +6447,28 @@
         <v>3.08</v>
       </c>
       <c r="M63">
-        <v>0.26605516</v>
+        <v>0.27041672</v>
       </c>
       <c r="N63">
-        <v>2.81394484</v>
+        <v>2.80958328</v>
       </c>
       <c r="O63">
-        <v>0.422091726</v>
+        <v>0.421437492</v>
       </c>
       <c r="P63">
-        <v>2.391853114</v>
+        <v>2.388145788</v>
       </c>
       <c r="Q63">
-        <v>4.771853114</v>
+        <v>4.768145788</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1568559449738049</v>
+        <v>0.1595902830448802</v>
       </c>
       <c r="T63">
-        <v>1.528726884575482</v>
+        <v>1.566366077342309</v>
       </c>
       <c r="U63">
         <v>0.0518</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>11.57654675819856</v>
+        <v>11.38982826209859</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08794290755705447</v>
+        <v>0.08785369657432507</v>
       </c>
       <c r="C64">
-        <v>4.304689898247171</v>
+        <v>4.240696032300256</v>
       </c>
       <c r="D64">
-        <v>9.52508989824717</v>
+        <v>9.545296032300255</v>
       </c>
       <c r="E64">
-        <v>5.2204</v>
+        <v>5.3046</v>
       </c>
       <c r="F64">
-        <v>5.2204</v>
+        <v>5.3046</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6529,28 +6529,28 @@
         <v>3.08</v>
       </c>
       <c r="M64">
-        <v>0.27041672</v>
+        <v>0.27477828</v>
       </c>
       <c r="N64">
-        <v>2.80958328</v>
+        <v>2.80522172</v>
       </c>
       <c r="O64">
-        <v>0.421437492</v>
+        <v>0.420783258</v>
       </c>
       <c r="P64">
-        <v>2.388145788</v>
+        <v>2.384438462</v>
       </c>
       <c r="Q64">
-        <v>4.768145788</v>
+        <v>4.764438461999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1595902830448802</v>
+        <v>0.1624724231738515</v>
       </c>
       <c r="T64">
-        <v>1.566366077342309</v>
+        <v>1.606039821069505</v>
       </c>
       <c r="U64">
         <v>0.0518</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>11.38982826209859</v>
+        <v>11.20903733730337</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08785369657432507</v>
+        <v>0.08776448559159565</v>
       </c>
       <c r="C65">
-        <v>4.240696032300256</v>
+        <v>4.176788077525641</v>
       </c>
       <c r="D65">
-        <v>9.545296032300255</v>
+        <v>9.565588077525641</v>
       </c>
       <c r="E65">
-        <v>5.3046</v>
+        <v>5.3888</v>
       </c>
       <c r="F65">
-        <v>5.3046</v>
+        <v>5.3888</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6611,28 +6611,28 @@
         <v>3.08</v>
       </c>
       <c r="M65">
-        <v>0.27477828</v>
+        <v>0.27913984</v>
       </c>
       <c r="N65">
-        <v>2.80522172</v>
+        <v>2.80086016</v>
       </c>
       <c r="O65">
-        <v>0.420783258</v>
+        <v>0.420129024</v>
       </c>
       <c r="P65">
-        <v>2.384438462</v>
+        <v>2.380731136</v>
       </c>
       <c r="Q65">
-        <v>4.764438461999999</v>
+        <v>4.760731136</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1624724231738515</v>
+        <v>0.1655146821988768</v>
       </c>
       <c r="T65">
-        <v>1.606039821069505</v>
+        <v>1.647917661670434</v>
       </c>
       <c r="U65">
         <v>0.0518</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>11.20903733730337</v>
+        <v>11.03389612890801</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08776448559159565</v>
+        <v>0.08767527460886623</v>
       </c>
       <c r="C66">
-        <v>4.176788077525641</v>
+        <v>4.112966582998181</v>
       </c>
       <c r="D66">
-        <v>9.565588077525641</v>
+        <v>9.58596658299818</v>
       </c>
       <c r="E66">
-        <v>5.3888</v>
+        <v>5.473</v>
       </c>
       <c r="F66">
-        <v>5.3888</v>
+        <v>5.473</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6693,28 +6693,28 @@
         <v>3.08</v>
       </c>
       <c r="M66">
-        <v>0.27913984</v>
+        <v>0.2835014</v>
       </c>
       <c r="N66">
-        <v>2.80086016</v>
+        <v>2.7964986</v>
       </c>
       <c r="O66">
-        <v>0.420129024</v>
+        <v>0.41947479</v>
       </c>
       <c r="P66">
-        <v>2.380731136</v>
+        <v>2.37702381</v>
       </c>
       <c r="Q66">
-        <v>4.760731136</v>
+        <v>4.75702381</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1655146821988768</v>
+        <v>0.1687307845967607</v>
       </c>
       <c r="T66">
-        <v>1.647917661670434</v>
+        <v>1.692188521734273</v>
       </c>
       <c r="U66">
         <v>0.0518</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>11.03389612890801</v>
+        <v>10.86414388077096</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08767527460886623</v>
+        <v>0.08758606362613681</v>
       </c>
       <c r="C67">
-        <v>4.112966582998181</v>
+        <v>4.049232102481708</v>
       </c>
       <c r="D67">
-        <v>9.58596658299818</v>
+        <v>9.606432102481708</v>
       </c>
       <c r="E67">
-        <v>5.473</v>
+        <v>5.5572</v>
       </c>
       <c r="F67">
-        <v>5.473</v>
+        <v>5.5572</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6775,28 +6775,28 @@
         <v>3.08</v>
       </c>
       <c r="M67">
-        <v>0.2835014</v>
+        <v>0.28786296</v>
       </c>
       <c r="N67">
-        <v>2.7964986</v>
+        <v>2.79213704</v>
       </c>
       <c r="O67">
-        <v>0.41947479</v>
+        <v>0.418820556</v>
       </c>
       <c r="P67">
-        <v>2.37702381</v>
+        <v>2.373316484</v>
       </c>
       <c r="Q67">
-        <v>4.75702381</v>
+        <v>4.753316484</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1687307845967607</v>
+        <v>0.1721360694886377</v>
       </c>
       <c r="T67">
-        <v>1.692188521734273</v>
+        <v>1.739063550037162</v>
       </c>
       <c r="U67">
         <v>0.0518</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>10.86414388077096</v>
+        <v>10.69953564015322</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08758606362613681</v>
+        <v>0.0874968526434074</v>
       </c>
       <c r="C68">
-        <v>4.049232102481708</v>
+        <v>3.9855851944792</v>
       </c>
       <c r="D68">
-        <v>9.606432102481708</v>
+        <v>9.6269851944792</v>
       </c>
       <c r="E68">
-        <v>5.5572</v>
+        <v>5.6414</v>
       </c>
       <c r="F68">
-        <v>5.5572</v>
+        <v>5.6414</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6857,28 +6857,28 @@
         <v>3.08</v>
       </c>
       <c r="M68">
-        <v>0.28786296</v>
+        <v>0.29222452</v>
       </c>
       <c r="N68">
-        <v>2.79213704</v>
+        <v>2.78777548</v>
       </c>
       <c r="O68">
-        <v>0.418820556</v>
+        <v>0.418166322</v>
       </c>
       <c r="P68">
-        <v>2.373316484</v>
+        <v>2.369609158</v>
       </c>
       <c r="Q68">
-        <v>4.753316484</v>
+        <v>4.749609158</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1721360694886377</v>
+        <v>0.1757477352830527</v>
       </c>
       <c r="T68">
-        <v>1.739063550037162</v>
+        <v>1.788779489146286</v>
       </c>
       <c r="U68">
         <v>0.0518</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>10.69953564015322</v>
+        <v>10.53984107835989</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0874968526434074</v>
+        <v>0.08740764166067798</v>
       </c>
       <c r="C69">
-        <v>3.9855851944792</v>
+        <v>3.922026422283579</v>
       </c>
       <c r="D69">
-        <v>9.6269851944792</v>
+        <v>9.647626422283579</v>
       </c>
       <c r="E69">
-        <v>5.6414</v>
+        <v>5.7256</v>
       </c>
       <c r="F69">
-        <v>5.6414</v>
+        <v>5.7256</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6939,28 +6939,28 @@
         <v>3.08</v>
       </c>
       <c r="M69">
-        <v>0.29222452</v>
+        <v>0.29658608</v>
       </c>
       <c r="N69">
-        <v>2.78777548</v>
+        <v>2.78341392</v>
       </c>
       <c r="O69">
-        <v>0.418166322</v>
+        <v>0.417512088</v>
       </c>
       <c r="P69">
-        <v>2.369609158</v>
+        <v>2.365901832</v>
       </c>
       <c r="Q69">
-        <v>4.749609158</v>
+        <v>4.745901831999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1757477352830527</v>
+        <v>0.1795851301896187</v>
       </c>
       <c r="T69">
-        <v>1.788779489146286</v>
+        <v>1.84160267444973</v>
       </c>
       <c r="U69">
         <v>0.0518</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>10.53984107835989</v>
+        <v>10.38484341544283</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08740764166067798</v>
+        <v>0.08731843067794856</v>
       </c>
       <c r="C70">
-        <v>3.922026422283579</v>
+        <v>3.858556354029177</v>
       </c>
       <c r="D70">
-        <v>9.647626422283579</v>
+        <v>9.668356354029177</v>
       </c>
       <c r="E70">
-        <v>5.7256</v>
+        <v>5.8098</v>
       </c>
       <c r="F70">
-        <v>5.7256</v>
+        <v>5.8098</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7021,28 +7021,28 @@
         <v>3.08</v>
       </c>
       <c r="M70">
-        <v>0.29658608</v>
+        <v>0.30094764</v>
       </c>
       <c r="N70">
-        <v>2.78341392</v>
+        <v>2.77905236</v>
       </c>
       <c r="O70">
-        <v>0.417512088</v>
+        <v>0.416857854</v>
       </c>
       <c r="P70">
-        <v>2.365901832</v>
+        <v>2.362194506</v>
       </c>
       <c r="Q70">
-        <v>4.745901831999999</v>
+        <v>4.742194506000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1795851301896187</v>
+        <v>0.1836700989611244</v>
       </c>
       <c r="T70">
-        <v>1.84160267444973</v>
+        <v>1.897833807192106</v>
       </c>
       <c r="U70">
         <v>0.0518</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>10.38484341544283</v>
+        <v>10.23433843840743</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08731843067794856</v>
+        <v>0.08722921969521914</v>
       </c>
       <c r="C71">
-        <v>3.858556354029177</v>
+        <v>3.795175562743859</v>
       </c>
       <c r="D71">
-        <v>9.668356354029177</v>
+        <v>9.689175562743859</v>
       </c>
       <c r="E71">
-        <v>5.8098</v>
+        <v>5.894</v>
       </c>
       <c r="F71">
-        <v>5.8098</v>
+        <v>5.894</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7103,28 +7103,28 @@
         <v>3.08</v>
       </c>
       <c r="M71">
-        <v>0.30094764</v>
+        <v>0.3053092</v>
       </c>
       <c r="N71">
-        <v>2.77905236</v>
+        <v>2.7746908</v>
       </c>
       <c r="O71">
-        <v>0.416857854</v>
+        <v>0.41620362</v>
       </c>
       <c r="P71">
-        <v>2.362194506</v>
+        <v>2.35848718</v>
       </c>
       <c r="Q71">
-        <v>4.742194506000001</v>
+        <v>4.73848718</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1836700989611244</v>
+        <v>0.1880273989840638</v>
       </c>
       <c r="T71">
-        <v>1.897833807192106</v>
+        <v>1.957813682117308</v>
       </c>
       <c r="U71">
         <v>0.0518</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>10.23433843840743</v>
+        <v>10.08813360357303</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08722921969521914</v>
+        <v>0.08714000871248974</v>
       </c>
       <c r="C72">
-        <v>3.795175562743859</v>
+        <v>3.731884626401819</v>
       </c>
       <c r="D72">
-        <v>9.689175562743859</v>
+        <v>9.710084626401819</v>
       </c>
       <c r="E72">
-        <v>5.894</v>
+        <v>5.9782</v>
       </c>
       <c r="F72">
-        <v>5.894</v>
+        <v>5.9782</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7185,28 +7185,28 @@
         <v>3.08</v>
       </c>
       <c r="M72">
-        <v>0.3053092</v>
+        <v>0.30967076</v>
       </c>
       <c r="N72">
-        <v>2.7746908</v>
+        <v>2.77032924</v>
       </c>
       <c r="O72">
-        <v>0.41620362</v>
+        <v>0.415549386</v>
       </c>
       <c r="P72">
-        <v>2.35848718</v>
+        <v>2.354779854</v>
       </c>
       <c r="Q72">
-        <v>4.73848718</v>
+        <v>4.734779854</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1880273989840638</v>
+        <v>0.1926852024568612</v>
       </c>
       <c r="T72">
-        <v>1.957813682117308</v>
+        <v>2.021930100140799</v>
       </c>
       <c r="U72">
         <v>0.0518</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>10.08813360357303</v>
+        <v>9.946047214790315</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08714000871248972</v>
+        <v>0.08809119772976029</v>
       </c>
       <c r="C73">
-        <v>3.731884626401824</v>
+        <v>3.429291051634332</v>
       </c>
       <c r="D73">
-        <v>9.710084626401823</v>
+        <v>9.491691051634332</v>
       </c>
       <c r="E73">
-        <v>5.978199999999999</v>
+        <v>6.062399999999999</v>
       </c>
       <c r="F73">
-        <v>5.978199999999999</v>
+        <v>6.062399999999999</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7267,45 +7267,45 @@
         <v>3.08</v>
       </c>
       <c r="M73">
-        <v>0.3096707599999999</v>
+        <v>0.3243384</v>
       </c>
       <c r="N73">
-        <v>2.77032924</v>
+        <v>2.7556616</v>
       </c>
       <c r="O73">
-        <v>0.415549386</v>
+        <v>0.41334924</v>
       </c>
       <c r="P73">
-        <v>2.354779854</v>
+        <v>2.34231236</v>
       </c>
       <c r="Q73">
-        <v>4.734779854</v>
+        <v>4.72231236</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1926852024568611</v>
+        <v>0.1976757061777153</v>
       </c>
       <c r="T73">
-        <v>2.021930100140799</v>
+        <v>2.090626262308824</v>
       </c>
       <c r="U73">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V73">
         <v>0.15</v>
       </c>
       <c r="W73">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>9.946047214790317</v>
+        <v>9.496254529220099</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08809119772976029</v>
+        <v>0.08801643674703089</v>
       </c>
       <c r="C74">
-        <v>3.429291051634332</v>
+        <v>3.361899863686286</v>
       </c>
       <c r="D74">
-        <v>9.491691051634332</v>
+        <v>9.508499863686286</v>
       </c>
       <c r="E74">
-        <v>6.062399999999999</v>
+        <v>6.146599999999999</v>
       </c>
       <c r="F74">
-        <v>6.062399999999999</v>
+        <v>6.146599999999999</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7349,28 +7349,28 @@
         <v>3.08</v>
       </c>
       <c r="M74">
-        <v>0.3243384</v>
+        <v>0.3288430999999999</v>
       </c>
       <c r="N74">
-        <v>2.7556616</v>
+        <v>2.7511569</v>
       </c>
       <c r="O74">
-        <v>0.41334924</v>
+        <v>0.412673535</v>
       </c>
       <c r="P74">
-        <v>2.34231236</v>
+        <v>2.338483365</v>
       </c>
       <c r="Q74">
-        <v>4.72231236</v>
+        <v>4.718483365</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1976757061777153</v>
+        <v>0.2030358768408551</v>
       </c>
       <c r="T74">
-        <v>2.090626262308824</v>
+        <v>2.16441102908189</v>
       </c>
       <c r="U74">
         <v>0.0535</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>9.496254529220099</v>
+        <v>9.366168850737633</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08801643674703089</v>
+        <v>0.08794167576430145</v>
       </c>
       <c r="C75">
-        <v>3.361899863686286</v>
+        <v>3.294568314719599</v>
       </c>
       <c r="D75">
-        <v>9.508499863686286</v>
+        <v>9.525368314719598</v>
       </c>
       <c r="E75">
-        <v>6.146599999999999</v>
+        <v>6.230799999999999</v>
       </c>
       <c r="F75">
-        <v>6.146599999999999</v>
+        <v>6.230799999999999</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7431,28 +7431,28 @@
         <v>3.08</v>
       </c>
       <c r="M75">
-        <v>0.3288430999999999</v>
+        <v>0.3333478</v>
       </c>
       <c r="N75">
-        <v>2.7511569</v>
+        <v>2.7466522</v>
       </c>
       <c r="O75">
-        <v>0.412673535</v>
+        <v>0.41199783</v>
       </c>
       <c r="P75">
-        <v>2.338483365</v>
+        <v>2.33465437</v>
       </c>
       <c r="Q75">
-        <v>4.718483365</v>
+        <v>4.71465437</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2030358768408551</v>
+        <v>0.2088083683242364</v>
       </c>
       <c r="T75">
-        <v>2.16441102908189</v>
+        <v>2.24387154714519</v>
       </c>
       <c r="U75">
         <v>0.0535</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>9.366168850737633</v>
+        <v>9.23959900140334</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08794167576430145</v>
+        <v>0.08786691478157205</v>
       </c>
       <c r="C76">
-        <v>3.294568314719599</v>
+        <v>3.227296722704011</v>
       </c>
       <c r="D76">
-        <v>9.525368314719598</v>
+        <v>9.542296722704011</v>
       </c>
       <c r="E76">
-        <v>6.230799999999999</v>
+        <v>6.315</v>
       </c>
       <c r="F76">
-        <v>6.230799999999999</v>
+        <v>6.315</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7513,28 +7513,28 @@
         <v>3.08</v>
       </c>
       <c r="M76">
-        <v>0.3333478</v>
+        <v>0.3378524999999999</v>
       </c>
       <c r="N76">
-        <v>2.7466522</v>
+        <v>2.7421475</v>
       </c>
       <c r="O76">
-        <v>0.41199783</v>
+        <v>0.411322125</v>
       </c>
       <c r="P76">
-        <v>2.33465437</v>
+        <v>2.330825375</v>
       </c>
       <c r="Q76">
-        <v>4.71465437</v>
+        <v>4.710825375000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2088083683242364</v>
+        <v>0.2150426591262882</v>
       </c>
       <c r="T76">
-        <v>2.24387154714519</v>
+        <v>2.329688906653556</v>
       </c>
       <c r="U76">
         <v>0.0535</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>9.23959900140334</v>
+        <v>9.116404348051297</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08786691478157205</v>
+        <v>0.08779215379884264</v>
       </c>
       <c r="C77">
-        <v>3.227296722704011</v>
+        <v>3.160085407873684</v>
       </c>
       <c r="D77">
-        <v>9.542296722704011</v>
+        <v>9.559285407873684</v>
       </c>
       <c r="E77">
-        <v>6.315</v>
+        <v>6.3992</v>
       </c>
       <c r="F77">
-        <v>6.315</v>
+        <v>6.3992</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7595,28 +7595,28 @@
         <v>3.08</v>
       </c>
       <c r="M77">
-        <v>0.3378524999999999</v>
+        <v>0.3423572</v>
       </c>
       <c r="N77">
-        <v>2.7421475</v>
+        <v>2.7376428</v>
       </c>
       <c r="O77">
-        <v>0.411322125</v>
+        <v>0.41064642</v>
       </c>
       <c r="P77">
-        <v>2.330825375</v>
+        <v>2.32699638</v>
       </c>
       <c r="Q77">
-        <v>4.710825375000001</v>
+        <v>4.70699638</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2150426591262882</v>
+        <v>0.2217964741618443</v>
       </c>
       <c r="T77">
-        <v>2.329688906653556</v>
+        <v>2.422657712787618</v>
       </c>
       <c r="U77">
         <v>0.0535</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>9.116404348051297</v>
+        <v>8.996451659261146</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08779215379884264</v>
+        <v>0.08771739281611321</v>
       </c>
       <c r="C78">
-        <v>3.160085407873684</v>
+        <v>3.09293469274736</v>
       </c>
       <c r="D78">
-        <v>9.559285407873684</v>
+        <v>9.576334692747361</v>
       </c>
       <c r="E78">
-        <v>6.3992</v>
+        <v>6.4834</v>
       </c>
       <c r="F78">
-        <v>6.3992</v>
+        <v>6.4834</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7677,28 +7677,28 @@
         <v>3.08</v>
       </c>
       <c r="M78">
-        <v>0.3423572</v>
+        <v>0.3468619</v>
       </c>
       <c r="N78">
-        <v>2.7376428</v>
+        <v>2.7331381</v>
       </c>
       <c r="O78">
-        <v>0.41064642</v>
+        <v>0.409970715</v>
       </c>
       <c r="P78">
-        <v>2.32699638</v>
+        <v>2.323167385</v>
       </c>
       <c r="Q78">
-        <v>4.70699638</v>
+        <v>4.703167385</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2217964741618443</v>
+        <v>0.2291375774613618</v>
       </c>
       <c r="T78">
-        <v>2.422657712787618</v>
+        <v>2.523710762933337</v>
       </c>
       <c r="U78">
         <v>0.0535</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>8.996451659261146</v>
+        <v>8.879614624725289</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08771739281611321</v>
+        <v>0.08764263183338379</v>
       </c>
       <c r="C79">
-        <v>3.09293469274736</v>
+        <v>3.025844902148776</v>
       </c>
       <c r="D79">
-        <v>9.576334692747361</v>
+        <v>9.593444902148777</v>
       </c>
       <c r="E79">
-        <v>6.4834</v>
+        <v>6.567600000000001</v>
       </c>
       <c r="F79">
-        <v>6.4834</v>
+        <v>6.567600000000001</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7759,28 +7759,28 @@
         <v>3.08</v>
       </c>
       <c r="M79">
-        <v>0.3468619</v>
+        <v>0.3513666</v>
       </c>
       <c r="N79">
-        <v>2.7331381</v>
+        <v>2.7286334</v>
       </c>
       <c r="O79">
-        <v>0.409970715</v>
+        <v>0.40929501</v>
       </c>
       <c r="P79">
-        <v>2.323167385</v>
+        <v>2.31933839</v>
       </c>
       <c r="Q79">
-        <v>4.703167385</v>
+        <v>4.699338389999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2291375774613618</v>
+        <v>0.2371460537881082</v>
       </c>
       <c r="T79">
-        <v>2.523710762933337</v>
+        <v>2.633950454001395</v>
       </c>
       <c r="U79">
         <v>0.0535</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>8.879614624725289</v>
+        <v>8.765773411587784</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08764263183338379</v>
+        <v>0.08756787085065437</v>
       </c>
       <c r="C80">
-        <v>3.025844902148776</v>
+        <v>2.958816363227309</v>
       </c>
       <c r="D80">
-        <v>9.593444902148777</v>
+        <v>9.61061636322731</v>
       </c>
       <c r="E80">
-        <v>6.567600000000001</v>
+        <v>6.651800000000001</v>
       </c>
       <c r="F80">
-        <v>6.567600000000001</v>
+        <v>6.651800000000001</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7841,28 +7841,28 @@
         <v>3.08</v>
       </c>
       <c r="M80">
-        <v>0.3513666</v>
+        <v>0.3558713</v>
       </c>
       <c r="N80">
-        <v>2.7286334</v>
+        <v>2.7241287</v>
       </c>
       <c r="O80">
-        <v>0.40929501</v>
+        <v>0.408619305</v>
       </c>
       <c r="P80">
-        <v>2.31933839</v>
+        <v>2.315509395</v>
       </c>
       <c r="Q80">
-        <v>4.699338389999999</v>
+        <v>4.695509395</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2371460537881082</v>
+        <v>0.2459172421459733</v>
       </c>
       <c r="T80">
-        <v>2.633950454001395</v>
+        <v>2.754689163266411</v>
       </c>
       <c r="U80">
         <v>0.0535</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>8.765773411587784</v>
+        <v>8.654814254479078</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08756787085065437</v>
+        <v>0.08749310986792495</v>
       </c>
       <c r="C81">
-        <v>2.958816363227309</v>
+        <v>2.891849405478808</v>
       </c>
       <c r="D81">
-        <v>9.61061636322731</v>
+        <v>9.627849405478809</v>
       </c>
       <c r="E81">
-        <v>6.651800000000001</v>
+        <v>6.736000000000001</v>
       </c>
       <c r="F81">
-        <v>6.651800000000001</v>
+        <v>6.736000000000001</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7923,28 +7923,28 @@
         <v>3.08</v>
       </c>
       <c r="M81">
-        <v>0.3558713</v>
+        <v>0.360376</v>
       </c>
       <c r="N81">
-        <v>2.7241287</v>
+        <v>2.719624</v>
       </c>
       <c r="O81">
-        <v>0.408619305</v>
+        <v>0.4079436</v>
       </c>
       <c r="P81">
-        <v>2.315509395</v>
+        <v>2.3116804</v>
       </c>
       <c r="Q81">
-        <v>4.695509395</v>
+        <v>4.6916804</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2459172421459733</v>
+        <v>0.2555655493396248</v>
       </c>
       <c r="T81">
-        <v>2.754689163266411</v>
+        <v>2.887501743457928</v>
       </c>
       <c r="U81">
         <v>0.0535</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>8.654814254479078</v>
+        <v>8.546629076298089</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08749310986792495</v>
+        <v>0.08741834888519553</v>
       </c>
       <c r="C82">
-        <v>2.891849405478808</v>
+        <v>2.824944360766676</v>
       </c>
       <c r="D82">
-        <v>9.627849405478809</v>
+        <v>9.645144360766677</v>
       </c>
       <c r="E82">
-        <v>6.736000000000001</v>
+        <v>6.820200000000001</v>
       </c>
       <c r="F82">
-        <v>6.736000000000001</v>
+        <v>6.820200000000001</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -8005,28 +8005,28 @@
         <v>3.08</v>
       </c>
       <c r="M82">
-        <v>0.360376</v>
+        <v>0.3648807000000001</v>
       </c>
       <c r="N82">
-        <v>2.719624</v>
+        <v>2.7151193</v>
       </c>
       <c r="O82">
-        <v>0.4079436</v>
+        <v>0.407267895</v>
       </c>
       <c r="P82">
-        <v>2.3116804</v>
+        <v>2.307851405</v>
       </c>
       <c r="Q82">
-        <v>4.6916804</v>
+        <v>4.687851405</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2555655493396248</v>
+        <v>0.2662294678168187</v>
       </c>
       <c r="T82">
-        <v>2.887501743457928</v>
+        <v>3.034294595248554</v>
       </c>
       <c r="U82">
         <v>0.0535</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>8.546629076298089</v>
+        <v>8.44111513708453</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08741834888519553</v>
+        <v>0.08734358790246613</v>
       </c>
       <c r="C83">
-        <v>2.824944360766676</v>
+        <v>2.758101563343182</v>
       </c>
       <c r="D83">
-        <v>9.645144360766677</v>
+        <v>9.662501563343183</v>
       </c>
       <c r="E83">
-        <v>6.820200000000001</v>
+        <v>6.904400000000001</v>
       </c>
       <c r="F83">
-        <v>6.820200000000001</v>
+        <v>6.904400000000001</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8087,28 +8087,28 @@
         <v>3.08</v>
       </c>
       <c r="M83">
-        <v>0.3648807000000001</v>
+        <v>0.3693854</v>
       </c>
       <c r="N83">
-        <v>2.7151193</v>
+        <v>2.7106146</v>
       </c>
       <c r="O83">
-        <v>0.407267895</v>
+        <v>0.40659219</v>
       </c>
       <c r="P83">
-        <v>2.307851405</v>
+        <v>2.30402241</v>
       </c>
       <c r="Q83">
-        <v>4.687851405</v>
+        <v>4.68402241</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2662294678168187</v>
+        <v>0.2780782661248119</v>
       </c>
       <c r="T83">
-        <v>3.034294595248554</v>
+        <v>3.197397763904803</v>
       </c>
       <c r="U83">
         <v>0.0535</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>8.44111513708453</v>
+        <v>8.338174708583502</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08734358790246613</v>
+        <v>0.08726882691973671</v>
       </c>
       <c r="C84">
-        <v>2.758101563343182</v>
+        <v>2.691321349870981</v>
       </c>
       <c r="D84">
-        <v>9.662501563343183</v>
+        <v>9.679921349870982</v>
       </c>
       <c r="E84">
-        <v>6.904400000000001</v>
+        <v>6.988600000000001</v>
       </c>
       <c r="F84">
-        <v>6.904400000000001</v>
+        <v>6.988600000000001</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8169,28 +8169,28 @@
         <v>3.08</v>
       </c>
       <c r="M84">
-        <v>0.3693854</v>
+        <v>0.3738901000000001</v>
       </c>
       <c r="N84">
-        <v>2.7106146</v>
+        <v>2.7061099</v>
       </c>
       <c r="O84">
-        <v>0.40659219</v>
+        <v>0.405916485</v>
       </c>
       <c r="P84">
-        <v>2.30402241</v>
+        <v>2.300193415</v>
       </c>
       <c r="Q84">
-        <v>4.68402241</v>
+        <v>4.680193415</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2780782661248119</v>
+        <v>0.2913210407043337</v>
       </c>
       <c r="T84">
-        <v>3.197397763904803</v>
+        <v>3.379689540638259</v>
       </c>
       <c r="U84">
         <v>0.0535</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>8.338174708583502</v>
+        <v>8.237714772335506</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08726882691973671</v>
+        <v>0.08719406593700729</v>
       </c>
       <c r="C85">
-        <v>2.691321349870981</v>
+        <v>2.624604059444888</v>
       </c>
       <c r="D85">
-        <v>9.679921349870982</v>
+        <v>9.697404059444889</v>
       </c>
       <c r="E85">
-        <v>6.988600000000001</v>
+        <v>7.072800000000001</v>
       </c>
       <c r="F85">
-        <v>6.988600000000001</v>
+        <v>7.072800000000001</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8251,28 +8251,28 @@
         <v>3.08</v>
       </c>
       <c r="M85">
-        <v>0.3738901000000001</v>
+        <v>0.3783948</v>
       </c>
       <c r="N85">
-        <v>2.7061099</v>
+        <v>2.7016052</v>
       </c>
       <c r="O85">
-        <v>0.405916485</v>
+        <v>0.40524078</v>
       </c>
       <c r="P85">
-        <v>2.300193415</v>
+        <v>2.29636442</v>
       </c>
       <c r="Q85">
-        <v>4.680193415</v>
+        <v>4.67636442</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2913210407043337</v>
+        <v>0.3062191621062957</v>
       </c>
       <c r="T85">
-        <v>3.379689540638259</v>
+        <v>3.584767789463396</v>
       </c>
       <c r="U85">
         <v>0.0535</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>8.237714772335506</v>
+        <v>8.139646739331512</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08719406593700729</v>
+        <v>0.08711930495427789</v>
       </c>
       <c r="C86">
-        <v>2.624604059444889</v>
+        <v>2.557950033613874</v>
       </c>
       <c r="D86">
-        <v>9.697404059444889</v>
+        <v>9.714950033613874</v>
       </c>
       <c r="E86">
-        <v>7.0728</v>
+        <v>7.157</v>
       </c>
       <c r="F86">
-        <v>7.0728</v>
+        <v>7.157</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8333,28 +8333,28 @@
         <v>3.08</v>
       </c>
       <c r="M86">
-        <v>0.3783948</v>
+        <v>0.3828995</v>
       </c>
       <c r="N86">
-        <v>2.7016052</v>
+        <v>2.6971005</v>
       </c>
       <c r="O86">
-        <v>0.40524078</v>
+        <v>0.404565075</v>
       </c>
       <c r="P86">
-        <v>2.29636442</v>
+        <v>2.292535425</v>
       </c>
       <c r="Q86">
-        <v>4.67636442</v>
+        <v>4.672535425</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3062191621062956</v>
+        <v>0.3231036996951859</v>
       </c>
       <c r="T86">
-        <v>3.584767789463394</v>
+        <v>3.817189804798549</v>
       </c>
       <c r="U86">
         <v>0.0535</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>8.139646739331514</v>
+        <v>8.043886189457023</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08711930495427789</v>
+        <v>0.08704454397154845</v>
       </c>
       <c r="C87">
-        <v>2.557950033613874</v>
+        <v>2.491359616403328</v>
       </c>
       <c r="D87">
-        <v>9.714950033613874</v>
+        <v>9.732559616403329</v>
       </c>
       <c r="E87">
-        <v>7.157</v>
+        <v>7.2412</v>
       </c>
       <c r="F87">
-        <v>7.157</v>
+        <v>7.2412</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8415,28 +8415,28 @@
         <v>3.08</v>
       </c>
       <c r="M87">
-        <v>0.3828995</v>
+        <v>0.3874042</v>
       </c>
       <c r="N87">
-        <v>2.6971005</v>
+        <v>2.6925958</v>
       </c>
       <c r="O87">
-        <v>0.404565075</v>
+        <v>0.40388937</v>
       </c>
       <c r="P87">
-        <v>2.292535425</v>
+        <v>2.28870643</v>
       </c>
       <c r="Q87">
-        <v>4.672535425</v>
+        <v>4.66870643</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3231036996951859</v>
+        <v>0.342400314082489</v>
       </c>
       <c r="T87">
-        <v>3.817189804798549</v>
+        <v>4.082814965181583</v>
       </c>
       <c r="U87">
         <v>0.0535</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>8.043886189457023</v>
+        <v>7.950352629114502</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08704454397154845</v>
+        <v>0.08696978298881905</v>
       </c>
       <c r="C88">
-        <v>2.491359616403328</v>
+        <v>2.424833154337509</v>
       </c>
       <c r="D88">
-        <v>9.732559616403329</v>
+        <v>9.75023315433751</v>
       </c>
       <c r="E88">
-        <v>7.2412</v>
+        <v>7.3254</v>
       </c>
       <c r="F88">
-        <v>7.2412</v>
+        <v>7.3254</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8497,28 +8497,28 @@
         <v>3.08</v>
       </c>
       <c r="M88">
-        <v>0.3874042</v>
+        <v>0.3919089</v>
       </c>
       <c r="N88">
-        <v>2.6925958</v>
+        <v>2.6880911</v>
       </c>
       <c r="O88">
-        <v>0.40388937</v>
+        <v>0.4032136650000001</v>
       </c>
       <c r="P88">
-        <v>2.28870643</v>
+        <v>2.284877435</v>
       </c>
       <c r="Q88">
-        <v>4.66870643</v>
+        <v>4.664877435</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.342400314082489</v>
+        <v>0.3646656383755311</v>
       </c>
       <c r="T88">
-        <v>4.082814965181583</v>
+        <v>4.389305534854316</v>
       </c>
       <c r="U88">
         <v>0.0535</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>7.950352629114502</v>
+        <v>7.858969265561462</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08696978298881905</v>
+        <v>0.08689502200608962</v>
       </c>
       <c r="C89">
-        <v>2.424833154337509</v>
+        <v>2.358370996462313</v>
       </c>
       <c r="D89">
-        <v>9.75023315433751</v>
+        <v>9.767970996462314</v>
       </c>
       <c r="E89">
-        <v>7.3254</v>
+        <v>7.4096</v>
       </c>
       <c r="F89">
-        <v>7.3254</v>
+        <v>7.4096</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8579,28 +8579,28 @@
         <v>3.08</v>
       </c>
       <c r="M89">
-        <v>0.3919089</v>
+        <v>0.3964136</v>
       </c>
       <c r="N89">
-        <v>2.6880911</v>
+        <v>2.6835864</v>
       </c>
       <c r="O89">
-        <v>0.4032136650000001</v>
+        <v>0.40253796</v>
       </c>
       <c r="P89">
-        <v>2.284877435</v>
+        <v>2.28104844</v>
       </c>
       <c r="Q89">
-        <v>4.664877435</v>
+        <v>4.66104844</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3646656383755311</v>
+        <v>0.3906418500507469</v>
       </c>
       <c r="T89">
-        <v>4.389305534854316</v>
+        <v>4.74687786613917</v>
       </c>
       <c r="U89">
         <v>0.0535</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>7.858969265561462</v>
+        <v>7.769662796634627</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08689502200608962</v>
+        <v>0.0868202610233602</v>
       </c>
       <c r="C90">
-        <v>2.358370996462313</v>
+        <v>2.291973494368216</v>
       </c>
       <c r="D90">
-        <v>9.767970996462314</v>
+        <v>9.785773494368216</v>
       </c>
       <c r="E90">
-        <v>7.4096</v>
+        <v>7.4938</v>
       </c>
       <c r="F90">
-        <v>7.4096</v>
+        <v>7.4938</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8661,28 +8661,28 @@
         <v>3.08</v>
       </c>
       <c r="M90">
-        <v>0.3964136</v>
+        <v>0.4009183</v>
       </c>
       <c r="N90">
-        <v>2.6835864</v>
+        <v>2.6790817</v>
       </c>
       <c r="O90">
-        <v>0.40253796</v>
+        <v>0.401862255</v>
       </c>
       <c r="P90">
-        <v>2.28104844</v>
+        <v>2.277219445</v>
       </c>
       <c r="Q90">
-        <v>4.66104844</v>
+        <v>4.657219445</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3906418500507469</v>
+        <v>0.4213410093032746</v>
       </c>
       <c r="T90">
-        <v>4.74687786613917</v>
+        <v>5.169463348566725</v>
       </c>
       <c r="U90">
         <v>0.0535</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>7.769662796634627</v>
+        <v>7.682363214649968</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.0868202610233602</v>
+        <v>0.08735750004063079</v>
       </c>
       <c r="C91">
-        <v>2.291973494368216</v>
+        <v>2.081266863069247</v>
       </c>
       <c r="D91">
-        <v>9.785773494368216</v>
+        <v>9.659266863069247</v>
       </c>
       <c r="E91">
-        <v>7.4938</v>
+        <v>7.578</v>
       </c>
       <c r="F91">
-        <v>7.4938</v>
+        <v>7.578</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8743,45 +8743,45 @@
         <v>3.08</v>
       </c>
       <c r="M91">
-        <v>0.4009183</v>
+        <v>0.4114854</v>
       </c>
       <c r="N91">
-        <v>2.6790817</v>
+        <v>2.6685146</v>
       </c>
       <c r="O91">
-        <v>0.401862255</v>
+        <v>0.40027719</v>
       </c>
       <c r="P91">
-        <v>2.277219445</v>
+        <v>2.26823741</v>
       </c>
       <c r="Q91">
-        <v>4.657219445</v>
+        <v>4.64823741</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4213410093032746</v>
+        <v>0.458180000406308</v>
       </c>
       <c r="T91">
-        <v>5.169463348566725</v>
+        <v>5.676565927479793</v>
       </c>
       <c r="U91">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V91">
         <v>0.15</v>
       </c>
       <c r="W91">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y91">
-        <v>7.682363214649968</v>
+        <v>7.485077234818052</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08735750004063079</v>
+        <v>0.08728953905790136</v>
       </c>
       <c r="C92">
-        <v>2.081266863069247</v>
+        <v>2.012889002417285</v>
       </c>
       <c r="D92">
-        <v>9.659266863069247</v>
+        <v>9.675089002417286</v>
       </c>
       <c r="E92">
-        <v>7.578</v>
+        <v>7.6622</v>
       </c>
       <c r="F92">
-        <v>7.578</v>
+        <v>7.6622</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8825,28 +8825,28 @@
         <v>3.08</v>
       </c>
       <c r="M92">
-        <v>0.4114854</v>
+        <v>0.41605746</v>
       </c>
       <c r="N92">
-        <v>2.6685146</v>
+        <v>2.66394254</v>
       </c>
       <c r="O92">
-        <v>0.40027719</v>
+        <v>0.399591381</v>
       </c>
       <c r="P92">
-        <v>2.26823741</v>
+        <v>2.264351159</v>
       </c>
       <c r="Q92">
-        <v>4.64823741</v>
+        <v>4.644351158999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.458180000406308</v>
+        <v>0.5032054339766819</v>
       </c>
       <c r="T92">
-        <v>5.676565927479793</v>
+        <v>6.296357968373539</v>
       </c>
       <c r="U92">
         <v>0.0543</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>7.485077234818052</v>
+        <v>7.402823638831039</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08728953905790136</v>
+        <v>0.08722157807517195</v>
       </c>
       <c r="C93">
-        <v>2.012889002417285</v>
+        <v>1.944563060991432</v>
       </c>
       <c r="D93">
-        <v>9.675089002417286</v>
+        <v>9.690963060991432</v>
       </c>
       <c r="E93">
-        <v>7.6622</v>
+        <v>7.7464</v>
       </c>
       <c r="F93">
-        <v>7.6622</v>
+        <v>7.7464</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8907,28 +8907,28 @@
         <v>3.08</v>
       </c>
       <c r="M93">
-        <v>0.41605746</v>
+        <v>0.42062952</v>
       </c>
       <c r="N93">
-        <v>2.66394254</v>
+        <v>2.65937048</v>
       </c>
       <c r="O93">
-        <v>0.399591381</v>
+        <v>0.398905572</v>
       </c>
       <c r="P93">
-        <v>2.264351159</v>
+        <v>2.260464908</v>
       </c>
       <c r="Q93">
-        <v>4.644351158999999</v>
+        <v>4.640464908</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5032054339766819</v>
+        <v>0.5594872259396496</v>
       </c>
       <c r="T93">
-        <v>6.296357968373539</v>
+        <v>7.071098019490726</v>
       </c>
       <c r="U93">
         <v>0.0543</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>7.402823638831039</v>
+        <v>7.32235816449592</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08722157807517195</v>
+        <v>0.08715361709244254</v>
       </c>
       <c r="C94">
-        <v>1.944563060991432</v>
+        <v>1.876289294765543</v>
       </c>
       <c r="D94">
-        <v>9.690963060991432</v>
+        <v>9.706889294765544</v>
       </c>
       <c r="E94">
-        <v>7.7464</v>
+        <v>7.8306</v>
       </c>
       <c r="F94">
-        <v>7.7464</v>
+        <v>7.8306</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8989,28 +8989,28 @@
         <v>3.08</v>
       </c>
       <c r="M94">
-        <v>0.42062952</v>
+        <v>0.42520158</v>
       </c>
       <c r="N94">
-        <v>2.65937048</v>
+        <v>2.65479842</v>
       </c>
       <c r="O94">
-        <v>0.398905572</v>
+        <v>0.398219763</v>
       </c>
       <c r="P94">
-        <v>2.260464908</v>
+        <v>2.256578657</v>
       </c>
       <c r="Q94">
-        <v>4.640464908</v>
+        <v>4.636578656999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5594872259396496</v>
+        <v>0.6318495298920367</v>
       </c>
       <c r="T94">
-        <v>7.071098019490726</v>
+        <v>8.067192370927108</v>
       </c>
       <c r="U94">
         <v>0.0543</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>7.32235816449592</v>
+        <v>7.243623130469082</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08715361709244254</v>
+        <v>0.08708565610971311</v>
       </c>
       <c r="C95">
-        <v>1.876289294765543</v>
+        <v>1.808067961398938</v>
       </c>
       <c r="D95">
-        <v>9.706889294765544</v>
+        <v>9.722867961398938</v>
       </c>
       <c r="E95">
-        <v>7.8306</v>
+        <v>7.914800000000001</v>
       </c>
       <c r="F95">
-        <v>7.8306</v>
+        <v>7.914800000000001</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9071,28 +9071,28 @@
         <v>3.08</v>
       </c>
       <c r="M95">
-        <v>0.42520158</v>
+        <v>0.42977364</v>
       </c>
       <c r="N95">
-        <v>2.65479842</v>
+        <v>2.65022636</v>
       </c>
       <c r="O95">
-        <v>0.398219763</v>
+        <v>0.397533954</v>
       </c>
       <c r="P95">
-        <v>2.256578657</v>
+        <v>2.252692406</v>
       </c>
       <c r="Q95">
-        <v>4.636578656999999</v>
+        <v>4.632692406</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6318495298920367</v>
+        <v>0.7283326018285525</v>
       </c>
       <c r="T95">
-        <v>8.067192370927108</v>
+        <v>9.395318172842282</v>
       </c>
       <c r="U95">
         <v>0.0543</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>7.243623130469082</v>
+        <v>7.166563309932177</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08708565610971311</v>
+        <v>0.08701769512698371</v>
       </c>
       <c r="C96">
-        <v>1.808067961398938</v>
+        <v>1.739899320250256</v>
       </c>
       <c r="D96">
-        <v>9.722867961398938</v>
+        <v>9.738899320250257</v>
       </c>
       <c r="E96">
-        <v>7.914800000000001</v>
+        <v>7.999000000000001</v>
       </c>
       <c r="F96">
-        <v>7.914800000000001</v>
+        <v>7.999000000000001</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9153,28 +9153,28 @@
         <v>3.08</v>
       </c>
       <c r="M96">
-        <v>0.42977364</v>
+        <v>0.4343457000000001</v>
       </c>
       <c r="N96">
-        <v>2.65022636</v>
+        <v>2.6456543</v>
       </c>
       <c r="O96">
-        <v>0.397533954</v>
+        <v>0.396848145</v>
       </c>
       <c r="P96">
-        <v>2.252692406</v>
+        <v>2.248806155</v>
       </c>
       <c r="Q96">
-        <v>4.632692406</v>
+        <v>4.628806154999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7283326018285525</v>
+        <v>0.8634089025396752</v>
       </c>
       <c r="T96">
-        <v>9.395318172842282</v>
+        <v>11.25469429552353</v>
       </c>
       <c r="U96">
         <v>0.0543</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>7.166563309932177</v>
+        <v>7.091125801406575</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08701769512698371</v>
+        <v>0.08694973414425428</v>
       </c>
       <c r="C97">
-        <v>1.739899320250256</v>
+        <v>1.671783632391543</v>
       </c>
       <c r="D97">
-        <v>9.738899320250257</v>
+        <v>9.754983632391543</v>
       </c>
       <c r="E97">
-        <v>7.999000000000001</v>
+        <v>8.0832</v>
       </c>
       <c r="F97">
-        <v>7.999000000000001</v>
+        <v>8.0832</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9235,28 +9235,28 @@
         <v>3.08</v>
       </c>
       <c r="M97">
-        <v>0.4343457000000001</v>
+        <v>0.43891776</v>
       </c>
       <c r="N97">
-        <v>2.6456543</v>
+        <v>2.64108224</v>
       </c>
       <c r="O97">
-        <v>0.396848145</v>
+        <v>0.396162336</v>
       </c>
       <c r="P97">
-        <v>2.248806155</v>
+        <v>2.244919904</v>
       </c>
       <c r="Q97">
-        <v>4.628806154999999</v>
+        <v>4.624919904</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8634089025396752</v>
+        <v>1.066023353606359</v>
       </c>
       <c r="T97">
-        <v>11.25469429552353</v>
+        <v>14.0437584795454</v>
       </c>
       <c r="U97">
         <v>0.0543</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>7.091125801406575</v>
+        <v>7.017259907641924</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08694973414425428</v>
+        <v>0.08688177316152487</v>
       </c>
       <c r="C98">
-        <v>1.671783632391543</v>
+        <v>1.603721160622371</v>
       </c>
       <c r="D98">
-        <v>9.754983632391543</v>
+        <v>9.77112116062237</v>
       </c>
       <c r="E98">
-        <v>8.0832</v>
+        <v>8.167399999999999</v>
       </c>
       <c r="F98">
-        <v>8.0832</v>
+        <v>8.167399999999999</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9317,28 +9317,28 @@
         <v>3.08</v>
       </c>
       <c r="M98">
-        <v>0.43891776</v>
+        <v>0.4434898199999999</v>
       </c>
       <c r="N98">
-        <v>2.64108224</v>
+        <v>2.63651018</v>
       </c>
       <c r="O98">
-        <v>0.396162336</v>
+        <v>0.395476527</v>
       </c>
       <c r="P98">
-        <v>2.244919904</v>
+        <v>2.241033653</v>
       </c>
       <c r="Q98">
-        <v>4.624919904</v>
+        <v>4.621033653</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.066023353606356</v>
+        <v>1.403714105384161</v>
       </c>
       <c r="T98">
-        <v>14.04375847954537</v>
+        <v>18.69219878624847</v>
       </c>
       <c r="U98">
         <v>0.0543</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>7.017259907641924</v>
+        <v>6.944917021996132</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08688177316152487</v>
+        <v>0.08681381217879544</v>
       </c>
       <c r="C99">
-        <v>1.603721160622371</v>
+        <v>1.535712169484199</v>
       </c>
       <c r="D99">
-        <v>9.77112116062237</v>
+        <v>9.787312169484199</v>
       </c>
       <c r="E99">
-        <v>8.167399999999999</v>
+        <v>8.2516</v>
       </c>
       <c r="F99">
-        <v>8.167399999999999</v>
+        <v>8.2516</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9399,28 +9399,28 @@
         <v>3.08</v>
       </c>
       <c r="M99">
-        <v>0.4434898199999999</v>
+        <v>0.44806188</v>
       </c>
       <c r="N99">
-        <v>2.63651018</v>
+        <v>2.63193812</v>
       </c>
       <c r="O99">
-        <v>0.395476527</v>
+        <v>0.394790718</v>
       </c>
       <c r="P99">
-        <v>2.241033653</v>
+        <v>2.237147402</v>
       </c>
       <c r="Q99">
-        <v>4.621033653</v>
+        <v>4.617147402000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.403714105384161</v>
+        <v>2.079095608939771</v>
       </c>
       <c r="T99">
-        <v>18.69219878624847</v>
+        <v>27.98907939965467</v>
       </c>
       <c r="U99">
         <v>0.0543</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>6.944917021996132</v>
+        <v>6.874050521771681</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08681381217879544</v>
+        <v>0.08674585119606604</v>
       </c>
       <c r="C100">
-        <v>1.535712169484199</v>
+        <v>1.467756925274783</v>
       </c>
       <c r="D100">
-        <v>9.787312169484199</v>
+        <v>9.803556925274782</v>
       </c>
       <c r="E100">
-        <v>8.2516</v>
+        <v>8.335799999999999</v>
       </c>
       <c r="F100">
-        <v>8.2516</v>
+        <v>8.335799999999999</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9481,28 +9481,28 @@
         <v>3.08</v>
       </c>
       <c r="M100">
-        <v>0.44806188</v>
+        <v>0.45263394</v>
       </c>
       <c r="N100">
-        <v>2.63193812</v>
+        <v>2.62736606</v>
       </c>
       <c r="O100">
-        <v>0.394790718</v>
+        <v>0.394104909</v>
       </c>
       <c r="P100">
-        <v>2.237147402</v>
+        <v>2.233261151</v>
       </c>
       <c r="Q100">
-        <v>4.617147402000001</v>
+        <v>4.613261151</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.079095608939771</v>
+        <v>4.1052401196066</v>
       </c>
       <c r="T100">
-        <v>27.98907939965467</v>
+        <v>55.87972123987326</v>
       </c>
       <c r="U100">
         <v>0.0543</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>6.874050521771681</v>
+        <v>6.804615668016411</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08674585119606604</v>
-      </c>
-      <c r="C101">
-        <v>1.467756925274783</v>
-      </c>
-      <c r="D101">
-        <v>9.803556925274782</v>
-      </c>
-      <c r="E101">
-        <v>8.335799999999999</v>
-      </c>
-      <c r="F101">
-        <v>8.335799999999999</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>8.42</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.46</v>
-      </c>
-      <c r="K101">
-        <v>2.38</v>
-      </c>
-      <c r="L101">
-        <v>3.08</v>
-      </c>
-      <c r="M101">
-        <v>0.45263394</v>
-      </c>
-      <c r="N101">
-        <v>2.62736606</v>
-      </c>
-      <c r="O101">
-        <v>0.394104909</v>
-      </c>
-      <c r="P101">
-        <v>2.233261151</v>
-      </c>
-      <c r="Q101">
-        <v>4.613261151</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.1052401196066</v>
-      </c>
-      <c r="T101">
-        <v>55.87972123987326</v>
-      </c>
-      <c r="U101">
-        <v>0.0543</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.046155</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A2/A</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>6.804615668016411</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
